--- a/google_data/Pobočky/Výroba/Report Vyroba.xlsx
+++ b/google_data/Pobočky/Výroba/Report Vyroba.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="73">
   <si>
     <t>Výroba</t>
   </si>
@@ -60,7 +60,7 @@
     <t>06:00</t>
   </si>
   <si>
-    <t>14:00</t>
+    <t>14:30</t>
   </si>
   <si>
     <t>Suroviny</t>
@@ -70,6 +70,9 @@
   </si>
   <si>
     <t>Ostatní</t>
+  </si>
+  <si>
+    <t>Ahurieva Viktoriia</t>
   </si>
   <si>
     <t>Vyber datum    &lt;----------&gt;</t>
@@ -1396,7 +1399,7 @@
         <v>1</v>
       </c>
       <c r="D1" s="4">
-        <v>46177.0</v>
+        <v>46178.0</v>
       </c>
       <c r="E1" s="5"/>
       <c r="F1" s="6" t="s">
@@ -1415,8 +1418,8 @@
       <c r="D2" s="13"/>
       <c r="E2" s="14"/>
       <c r="F2" s="15">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("SUM(A14:A20) + SUM(FILTER(HR!W5:W48, HR!A5:A48 &lt;&gt; """")) + J13 + J15"),41144.0)</f>
-        <v>41144</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("SUM(A14:A20) + SUM(FILTER(HR!W5:W48, HR!A5:A48 &lt;&gt; """")) + J13 + J15"),40484.25)</f>
+        <v>40484.25</v>
       </c>
       <c r="H2" s="16"/>
       <c r="K2" s="16"/>
@@ -1425,7 +1428,7 @@
       <c r="A3" s="17"/>
       <c r="B3" s="18" t="str">
         <f>CHOOSE(WEEKDAY(D1), "Neděle", "Pondělí", "Úterý", "Středa", "Čtvrtek", "Pátek", "Sobota")</f>
-        <v>Čtvrtek</v>
+        <v>Pátek</v>
       </c>
       <c r="C3" s="10"/>
       <c r="D3" s="10"/>
@@ -1578,7 +1581,7 @@
       <c r="F14" s="42" t="str">
         <f t="shared" ref="F14:F20" si="1">IF(OR(ISBLANK(B14), ISBLANK(D14), D14=0), "0:00", TEXT((IF(AND(TIMEVALUE(IF(ISBLANK(D14), "00:00", D14))&gt;=TIMEVALUE("00:00"), TIMEVALUE(IF(ISBLANK(D14), "00:00", D14))&lt;=TIMEVALUE("06:00")), TIMEVALUE(IF(ISBLANK(D14), "00:00", D14))+1, TIMEVALUE(IF(ISBLANK(D14), "00:00", D14))) - TIMEVALUE(IF(ISBLANK(C14), "00:00", C14)) - TIMEVALUE(IF(ISBLANK(E14), "00:00", E14))), "hh:mm"))
 </f>
-        <v>08:00</v>
+        <v>08:30</v>
       </c>
       <c r="G14" s="43" t="s">
         <v>15</v>
@@ -1591,7 +1594,7 @@
     <row r="15">
       <c r="A15" s="38">
         <f t="array" ref="A15">IF(ISBLANK(B15), 0, IF(ISNUMBER(MATCH(B15, HR!A:A, 0)), 0, IF(ISNUMBER(MATCH(B15, HR!B:B, 0)), INDEX(HR!V:V, MATCH(B15, HR!B:B, 0)) * (F15 * 24), 0)))</f>
-        <v>1140</v>
+        <v>276.25</v>
       </c>
       <c r="B15" s="47" t="s">
         <v>16</v>
@@ -1605,7 +1608,7 @@
       <c r="E15" s="40"/>
       <c r="F15" s="42" t="str">
         <f t="shared" si="1"/>
-        <v>08:00</v>
+        <v>08:30</v>
       </c>
       <c r="G15" s="48" t="s">
         <v>17</v>
@@ -1618,15 +1621,21 @@
     <row r="16">
       <c r="A16" s="38">
         <f t="array" ref="A16">IF(ISBLANK(B16), 0, IF(ISNUMBER(MATCH(B16, HR!A:A, 0)), 0, IF(ISNUMBER(MATCH(B16, HR!B:B, 0)), INDEX(HR!V:V, MATCH(B16, HR!B:B, 0)) * (F16 * 24), 0)))</f>
-        <v>0</v>
-      </c>
-      <c r="B16" s="39"/>
-      <c r="C16" s="40"/>
-      <c r="D16" s="40"/>
+        <v>204</v>
+      </c>
+      <c r="B16" s="39" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="40" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" s="40" t="s">
+        <v>14</v>
+      </c>
       <c r="E16" s="52"/>
       <c r="F16" s="53" t="str">
         <f t="shared" si="1"/>
-        <v>0:00</v>
+        <v>08:30</v>
       </c>
       <c r="G16" s="54"/>
       <c r="K16" s="16"/>
@@ -1761,7 +1770,7 @@
         <v>46143.0</v>
       </c>
       <c r="D1" s="63" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E1" s="62">
         <v>46173.0</v>
@@ -1811,7 +1820,7 @@
     <row r="5">
       <c r="A5" s="68"/>
       <c r="B5" s="69" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C5" s="10"/>
       <c r="D5" s="10"/>
@@ -1884,7 +1893,7 @@
         <v>6</v>
       </c>
       <c r="C9" s="79" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D9" s="79" t="s">
         <v>10</v>
@@ -1906,7 +1915,7 @@
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="71"/>
       <c r="B11" s="80" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C11" s="81">
         <v>16.0</v>
@@ -1930,7 +1939,7 @@
     <row r="13" ht="18.75" customHeight="1">
       <c r="A13" s="71"/>
       <c r="B13" s="80" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C13" s="81">
         <v>11.0</v>
@@ -1942,7 +1951,7 @@
     <row r="14" ht="18.75" customHeight="1">
       <c r="A14" s="71"/>
       <c r="B14" s="80" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C14" s="81">
         <v>1.0</v>
@@ -2057,8 +2066,8 @@
       <c r="T1" s="84"/>
       <c r="U1" s="84"/>
       <c r="V1" s="86">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(""1TpIiNTfR1pnpn85VWQTTdvQ2Xcr0GStmWJ2UvfKxG_A"", ""Mzdy!u1:v200"")"),46143.0)</f>
-        <v>46143</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(""1TpIiNTfR1pnpn85VWQTTdvQ2Xcr0GStmWJ2UvfKxG_A"", ""Mzdy!u1:v200"")"),46174.0)</f>
+        <v>46174</v>
       </c>
       <c r="W1" s="87"/>
       <c r="X1" s="84"/>
@@ -2156,10 +2165,10 @@
     </row>
     <row r="4">
       <c r="A4" s="88" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B4" s="88" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C4" s="84" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Manažer")</f>
@@ -2256,8 +2265,8 @@
       <c r="T5" s="84"/>
       <c r="U5" s="84"/>
       <c r="V5" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),256.5)</f>
-        <v>256.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),13.5)</f>
+        <v>13.5</v>
       </c>
       <c r="W5" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50001.08)</f>
@@ -2322,8 +2331,8 @@
       <c r="T6" s="84"/>
       <c r="U6" s="84"/>
       <c r="V6" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),208.0)</f>
-        <v>208</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),38.5)</f>
+        <v>38.5</v>
       </c>
       <c r="W6" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50001.08)</f>
@@ -2382,8 +2391,8 @@
       <c r="T7" s="84"/>
       <c r="U7" s="84"/>
       <c r="V7" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),119.0)</f>
-        <v>119</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),32.5)</f>
+        <v>32.5</v>
       </c>
       <c r="W7" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40004.0)</f>
@@ -2451,8 +2460,8 @@
       <c r="T8" s="84"/>
       <c r="U8" s="84"/>
       <c r="V8" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),206.5)</f>
-        <v>206.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),24.0)</f>
+        <v>24</v>
       </c>
       <c r="W8" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50001.08)</f>
@@ -2514,8 +2523,8 @@
       <c r="T9" s="84"/>
       <c r="U9" s="84"/>
       <c r="V9" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),193.5)</f>
-        <v>193.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14.5)</f>
+        <v>14.5</v>
       </c>
       <c r="W9" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40004.0)</f>
@@ -2583,8 +2592,8 @@
       <c r="T10" s="84"/>
       <c r="U10" s="84"/>
       <c r="V10" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),178.5)</f>
-        <v>178.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.0)</f>
+        <v>18</v>
       </c>
       <c r="W10" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50001.08)</f>
@@ -2643,12 +2652,12 @@
       <c r="T11" s="84"/>
       <c r="U11" s="84"/>
       <c r="V11" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),117.5)</f>
-        <v>117.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.0)</f>
+        <v>22</v>
       </c>
       <c r="W11" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21630.145)</f>
-        <v>21630.145</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4298.008)</f>
+        <v>4298.008</v>
       </c>
       <c r="X11" s="84"/>
       <c r="Y11" s="84"/>
@@ -2763,8 +2772,8 @@
       <c r="T13" s="84"/>
       <c r="U13" s="84"/>
       <c r="V13" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),148.5)</f>
-        <v>148.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.5)</f>
+        <v>22.5</v>
       </c>
       <c r="W13" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40004.0)</f>
@@ -2829,12 +2838,12 @@
       <c r="T14" s="84"/>
       <c r="U14" s="84"/>
       <c r="V14" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),63.5)</f>
-        <v>63.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.5)</f>
+        <v>9.5</v>
       </c>
       <c r="W14" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10497.058)</f>
-        <v>10497.058</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1570.426)</f>
+        <v>1570.426</v>
       </c>
       <c r="X14" s="84"/>
       <c r="Y14" s="84"/>
@@ -2892,8 +2901,8 @@
       <c r="T15" s="84"/>
       <c r="U15" s="84"/>
       <c r="V15" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),183.0)</f>
-        <v>183</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.0)</f>
+        <v>21</v>
       </c>
       <c r="W15" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40004.0)</f>
@@ -2955,8 +2964,8 @@
       <c r="T16" s="84"/>
       <c r="U16" s="84"/>
       <c r="V16" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),159.0)</f>
-        <v>159</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.0)</f>
+        <v>35</v>
       </c>
       <c r="W16" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40004.0)</f>
@@ -3015,12 +3024,12 @@
       <c r="T17" s="84"/>
       <c r="U17" s="84"/>
       <c r="V17" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),43.5)</f>
-        <v>43.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W17" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7690.8)</f>
-        <v>7690.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="X17" s="84"/>
       <c r="Y17" s="84"/>
@@ -3075,12 +3084,12 @@
       <c r="T18" s="84"/>
       <c r="U18" s="84"/>
       <c r="V18" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),126.5)</f>
-        <v>126.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W18" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22440.113999999998)</f>
-        <v>22440.114</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="X18" s="84"/>
       <c r="Y18" s="84"/>
@@ -3135,12 +3144,12 @@
       <c r="T19" s="84"/>
       <c r="U19" s="84"/>
       <c r="V19" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),184.0)</f>
-        <v>184</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W19" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),37009.28)</f>
-        <v>37009.28</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="X19" s="84"/>
       <c r="Y19" s="84"/>
@@ -3195,12 +3204,12 @@
       <c r="T20" s="84"/>
       <c r="U20" s="84"/>
       <c r="V20" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),59.5)</f>
-        <v>59.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14.0)</f>
+        <v>14</v>
       </c>
       <c r="W20" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10519.6)</f>
-        <v>10519.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2475.2)</f>
+        <v>2475.2</v>
       </c>
       <c r="X20" s="84"/>
       <c r="Y20" s="84"/>
@@ -3264,8 +3273,8 @@
       <c r="T21" s="84"/>
       <c r="U21" s="84"/>
       <c r="V21" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),185.0)</f>
-        <v>185</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27.5)</f>
+        <v>27.5</v>
       </c>
       <c r="W21" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50001.08)</f>
@@ -3324,8 +3333,8 @@
       <c r="T22" s="84"/>
       <c r="U22" s="84"/>
       <c r="V22" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),273.5)</f>
-        <v>273.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),60.5)</f>
+        <v>60.5</v>
       </c>
       <c r="W22" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50001.08)</f>
@@ -3384,12 +3393,12 @@
       <c r="T23" s="84"/>
       <c r="U23" s="84"/>
       <c r="V23" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),52.0)</f>
-        <v>52</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W23" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8596.016)</f>
-        <v>8596.016</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="X23" s="84"/>
       <c r="Y23" s="84"/>
@@ -3447,12 +3456,12 @@
       <c r="T24" s="84"/>
       <c r="U24" s="84"/>
       <c r="V24" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201.5)</f>
-        <v>201.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23.5)</f>
+        <v>23.5</v>
       </c>
       <c r="W24" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),32150.199999999997)</f>
-        <v>32150.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4154.8)</f>
+        <v>4154.8</v>
       </c>
       <c r="X24" s="84"/>
       <c r="Y24" s="84"/>
@@ -3507,12 +3516,12 @@
       <c r="T25" s="84"/>
       <c r="U25" s="84"/>
       <c r="V25" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),33.0)</f>
-        <v>33</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W25" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5046.756)</f>
-        <v>5046.756</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="X25" s="84"/>
       <c r="Y25" s="84"/>
@@ -3621,12 +3630,12 @@
       <c r="T27" s="84"/>
       <c r="U27" s="84"/>
       <c r="V27" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),71.5)</f>
-        <v>71.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W27" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),13526.084)</f>
-        <v>13526.084</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="X27" s="84"/>
       <c r="Y27" s="84"/>
@@ -3690,12 +3699,12 @@
       <c r="T28" s="84"/>
       <c r="U28" s="84"/>
       <c r="V28" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),192.5)</f>
-        <v>192.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.5)</f>
+        <v>35.5</v>
       </c>
       <c r="W28" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),30829.0)</f>
-        <v>30829</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6276.4)</f>
+        <v>6276.4</v>
       </c>
       <c r="X28" s="84"/>
       <c r="Y28" s="84"/>
@@ -3810,12 +3819,12 @@
       <c r="T30" s="84"/>
       <c r="U30" s="84"/>
       <c r="V30" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),185.0)</f>
-        <v>185</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.5)</f>
+        <v>21.5</v>
       </c>
       <c r="W30" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27962.73)</f>
-        <v>27962.73</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3554.122)</f>
+        <v>3554.122</v>
       </c>
       <c r="X30" s="84"/>
       <c r="Y30" s="84"/>
@@ -3876,12 +3885,12 @@
       <c r="T31" s="84"/>
       <c r="U31" s="84"/>
       <c r="V31" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),131.5)</f>
-        <v>131.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W31" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19268.133)</f>
-        <v>19268.133</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="X31" s="84"/>
       <c r="Y31" s="84"/>
@@ -4119,12 +4128,12 @@
       <c r="T35" s="84"/>
       <c r="U35" s="84"/>
       <c r="V35" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),142.5)</f>
-        <v>142.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),32.5)</f>
+        <v>32.5</v>
       </c>
       <c r="W35" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22129.265)</f>
-        <v>22129.265</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5372.51)</f>
+        <v>5372.51</v>
       </c>
       <c r="X35" s="84"/>
       <c r="Y35" s="84"/>
@@ -4179,12 +4188,12 @@
       <c r="T36" s="84"/>
       <c r="U36" s="84"/>
       <c r="V36" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25.0)</f>
-        <v>25</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W36" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4132.7)</f>
-        <v>4132.7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="X36" s="84"/>
       <c r="Y36" s="84"/>
@@ -4239,12 +4248,12 @@
       <c r="T37" s="84"/>
       <c r="U37" s="84"/>
       <c r="V37" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),37.5)</f>
-        <v>37.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W37" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6199.05)</f>
-        <v>6199.05</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="X37" s="84"/>
       <c r="Y37" s="84"/>
@@ -4302,12 +4311,12 @@
       <c r="T38" s="84"/>
       <c r="U38" s="84"/>
       <c r="V38" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),182.5)</f>
-        <v>182.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.0)</f>
+        <v>16</v>
       </c>
       <c r="W38" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27619.585)</f>
-        <v>27619.585</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2644.928)</f>
+        <v>2644.928</v>
       </c>
       <c r="X38" s="84"/>
       <c r="Y38" s="84"/>
@@ -4371,12 +4380,12 @@
       <c r="T39" s="84"/>
       <c r="U39" s="84"/>
       <c r="V39" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),188.5)</f>
-        <v>188.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29.5)</f>
+        <v>29.5</v>
       </c>
       <c r="W39" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28443.133)</f>
-        <v>28443.133</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4876.586)</f>
+        <v>4876.586</v>
       </c>
       <c r="X39" s="84"/>
       <c r="Y39" s="84"/>
@@ -4431,12 +4440,12 @@
       <c r="T40" s="84"/>
       <c r="U40" s="84"/>
       <c r="V40" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40.0)</f>
-        <v>40</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W40" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6612.32)</f>
-        <v>6612.32</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="X40" s="84"/>
       <c r="Y40" s="84"/>
@@ -4491,12 +4500,12 @@
       <c r="T41" s="84"/>
       <c r="U41" s="84"/>
       <c r="V41" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),165.5)</f>
-        <v>165.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),13.0)</f>
+        <v>13</v>
       </c>
       <c r="W41" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25286.199)</f>
-        <v>25286.199</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2149.004)</f>
+        <v>2149.004</v>
       </c>
       <c r="X41" s="84"/>
       <c r="Y41" s="84"/>
@@ -5412,12 +5421,12 @@
       <c r="T60" s="84"/>
       <c r="U60" s="84"/>
       <c r="V60" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4354.0)</f>
-        <v>4354</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),524.5)</f>
+        <v>524.5</v>
       </c>
       <c r="W60" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),945614.6479999999)</f>
-        <v>945614.648</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),615398.4639999999)</f>
+        <v>615398.464</v>
       </c>
       <c r="X60" s="84"/>
       <c r="Y60" s="84"/>
@@ -6099,12 +6108,12 @@
       <c r="T75" s="84"/>
       <c r="U75" s="84"/>
       <c r="V75" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),106.5)</f>
-        <v>106.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W75" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15975.0)</f>
-        <v>15975</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="X75" s="84"/>
       <c r="Y75" s="84"/>
@@ -6156,12 +6165,12 @@
       <c r="T76" s="84"/>
       <c r="U76" s="84"/>
       <c r="V76" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),138.0)</f>
-        <v>138</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.0)</f>
+        <v>31</v>
       </c>
       <c r="W76" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22828.4)</f>
-        <v>22828.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5480.8)</f>
+        <v>5480.8</v>
       </c>
       <c r="X76" s="84"/>
       <c r="Y76" s="84"/>
@@ -6213,12 +6222,12 @@
       <c r="T77" s="84"/>
       <c r="U77" s="84"/>
       <c r="V77" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.0)</f>
-        <v>7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W77" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1070.524)</f>
-        <v>1070.524</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="X77" s="84"/>
       <c r="Y77" s="84"/>
@@ -6270,12 +6279,12 @@
       <c r="T78" s="84"/>
       <c r="U78" s="84"/>
       <c r="V78" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),30.0)</f>
-        <v>30</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
+        <v>10</v>
       </c>
       <c r="W78" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5304.0)</f>
-        <v>5304</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1768.0)</f>
+        <v>1768</v>
       </c>
       <c r="X78" s="84"/>
       <c r="Y78" s="84"/>
@@ -6333,12 +6342,12 @@
       <c r="T79" s="84"/>
       <c r="U79" s="84"/>
       <c r="V79" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23.0)</f>
-        <v>23</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.5)</f>
+        <v>5.5</v>
       </c>
       <c r="W79" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3517.436)</f>
-        <v>3517.436</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),841.126)</f>
+        <v>841.126</v>
       </c>
       <c r="X79" s="84"/>
       <c r="Y79" s="84"/>
@@ -6396,12 +6405,12 @@
       <c r="T80" s="84"/>
       <c r="U80" s="84"/>
       <c r="V80" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),98.0)</f>
-        <v>98</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.5)</f>
+        <v>22.5</v>
       </c>
       <c r="W80" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16021.284000000001)</f>
-        <v>16021.284</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3719.43)</f>
+        <v>3719.43</v>
       </c>
       <c r="X80" s="84"/>
       <c r="Y80" s="84"/>
@@ -6456,12 +6465,12 @@
       <c r="T81" s="84"/>
       <c r="U81" s="84"/>
       <c r="V81" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),168.0)</f>
-        <v>168</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14.0)</f>
+        <v>14</v>
       </c>
       <c r="W81" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23902.976000000002)</f>
-        <v>23902.976</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2141.048)</f>
+        <v>2141.048</v>
       </c>
       <c r="X81" s="84"/>
       <c r="Y81" s="84"/>
@@ -6570,12 +6579,12 @@
       <c r="T83" s="84"/>
       <c r="U83" s="84"/>
       <c r="V83" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),30.5)</f>
-        <v>30.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W83" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4664.426)</f>
-        <v>4664.426</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="X83" s="84"/>
       <c r="Y83" s="84"/>
@@ -6630,12 +6639,12 @@
       <c r="T84" s="84"/>
       <c r="U84" s="84"/>
       <c r="V84" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),58.5)</f>
-        <v>58.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6.0)</f>
+        <v>6</v>
       </c>
       <c r="W84" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9670.518)</f>
-        <v>9670.518</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),991.848)</f>
+        <v>991.848</v>
       </c>
       <c r="X84" s="84"/>
       <c r="Y84" s="84"/>
@@ -6687,12 +6696,12 @@
       <c r="T85" s="84"/>
       <c r="U85" s="84"/>
       <c r="V85" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),44.0)</f>
-        <v>44</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="W85" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6600.0)</f>
-        <v>6600</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),750.0)</f>
+        <v>750</v>
       </c>
       <c r="X85" s="84"/>
       <c r="Y85" s="84"/>
@@ -6801,12 +6810,12 @@
       <c r="T87" s="84"/>
       <c r="U87" s="84"/>
       <c r="V87" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.0)</f>
-        <v>18</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
+        <v>3.5</v>
       </c>
       <c r="W87" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2752.776)</f>
-        <v>2752.776</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),535.262)</f>
+        <v>535.262</v>
       </c>
       <c r="X87" s="84"/>
       <c r="Y87" s="84"/>
@@ -6927,12 +6936,12 @@
       <c r="T89" s="84"/>
       <c r="U89" s="84"/>
       <c r="V89" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),78.0)</f>
-        <v>78</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
       </c>
       <c r="W89" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),13260.0)</f>
-        <v>13260</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),765.0)</f>
+        <v>765</v>
       </c>
       <c r="X89" s="84"/>
       <c r="Y89" s="84"/>
@@ -6987,12 +6996,12 @@
       <c r="T90" s="84"/>
       <c r="U90" s="84"/>
       <c r="V90" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),141.0)</f>
-        <v>141</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14.0)</f>
+        <v>14</v>
       </c>
       <c r="W90" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22560.0)</f>
-        <v>22560</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2240.0)</f>
+        <v>2240</v>
       </c>
       <c r="X90" s="84"/>
       <c r="Y90" s="84"/>
@@ -7152,12 +7161,12 @@
       <c r="T93" s="84"/>
       <c r="U93" s="84"/>
       <c r="V93" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),228.0)</f>
-        <v>228</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14.0)</f>
+        <v>14</v>
       </c>
       <c r="W93" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),33864.824)</f>
-        <v>33864.824</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2314.312)</f>
+        <v>2314.312</v>
       </c>
       <c r="X93" s="84"/>
       <c r="Y93" s="84"/>
@@ -7215,12 +7224,12 @@
       <c r="T94" s="84"/>
       <c r="U94" s="84"/>
       <c r="V94" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),281.0)</f>
-        <v>281</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.0)</f>
+        <v>35</v>
       </c>
       <c r="W94" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),41139.49800000001)</f>
-        <v>41139.498</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5785.78)</f>
+        <v>5785.78</v>
       </c>
       <c r="X94" s="84"/>
       <c r="Y94" s="84"/>
@@ -7332,8 +7341,8 @@
       <c r="T96" s="84"/>
       <c r="U96" s="84"/>
       <c r="V96" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),142.0)</f>
-        <v>142</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.0)</f>
+        <v>20</v>
       </c>
       <c r="W96" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),44995.2)</f>
@@ -7389,12 +7398,12 @@
       <c r="T97" s="84"/>
       <c r="U97" s="84"/>
       <c r="V97" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),75.5)</f>
-        <v>75.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W97" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12480.754)</f>
-        <v>12480.754</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="X97" s="84"/>
       <c r="Y97" s="84"/>
@@ -7455,12 +7464,12 @@
       <c r="T98" s="84"/>
       <c r="U98" s="84"/>
       <c r="V98" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),24.5)</f>
-        <v>24.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6.0)</f>
+        <v>6</v>
       </c>
       <c r="W98" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3465.2799999999997)</f>
-        <v>3465.28</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),848.64)</f>
+        <v>848.64</v>
       </c>
       <c r="X98" s="84"/>
       <c r="Y98" s="84"/>
@@ -7512,12 +7521,12 @@
       <c r="T99" s="84"/>
       <c r="U99" s="84"/>
       <c r="V99" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),53.0)</f>
-        <v>53</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W99" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7496.32)</f>
-        <v>7496.32</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="X99" s="84"/>
       <c r="Y99" s="84"/>
@@ -7845,12 +7854,12 @@
       <c r="T105" s="84"/>
       <c r="U105" s="84"/>
       <c r="V105" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),107.0)</f>
-        <v>107</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="W105" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16157.074)</f>
-        <v>16157.074</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),764.66)</f>
+        <v>764.66</v>
       </c>
       <c r="X105" s="84"/>
       <c r="Y105" s="84"/>
@@ -7953,12 +7962,12 @@
       <c r="T107" s="84"/>
       <c r="U107" s="84"/>
       <c r="V107" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),215.0)</f>
-        <v>215</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W107" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),30100.0)</f>
-        <v>30100</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="X107" s="84"/>
       <c r="Y107" s="84"/>
@@ -8013,12 +8022,12 @@
       <c r="T108" s="84"/>
       <c r="U108" s="84"/>
       <c r="V108" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),76.5)</f>
-        <v>76.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),48.0)</f>
+        <v>48</v>
       </c>
       <c r="W108" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12646.062)</f>
-        <v>12646.062</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7934.784)</f>
+        <v>7934.784</v>
       </c>
       <c r="X108" s="84"/>
       <c r="Y108" s="84"/>
@@ -8070,12 +8079,12 @@
       <c r="T109" s="84"/>
       <c r="U109" s="84"/>
       <c r="V109" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19.0)</f>
-        <v>19</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W109" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2905.708)</f>
-        <v>2905.708</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="X109" s="84"/>
       <c r="Y109" s="84"/>
@@ -8127,12 +8136,12 @@
       <c r="T110" s="84"/>
       <c r="U110" s="84"/>
       <c r="V110" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),60.0)</f>
-        <v>60</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W110" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8486.4)</f>
-        <v>8486.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="X110" s="84"/>
       <c r="Y110" s="84"/>
@@ -8184,12 +8193,12 @@
       <c r="T111" s="84"/>
       <c r="U111" s="84"/>
       <c r="V111" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.0)</f>
-        <v>15</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W111" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2293.98)</f>
-        <v>2293.98</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="X111" s="84"/>
       <c r="Y111" s="84"/>
@@ -8241,12 +8250,12 @@
       <c r="T112" s="84"/>
       <c r="U112" s="84"/>
       <c r="V112" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17.5)</f>
-        <v>17.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19.0)</f>
+        <v>19</v>
       </c>
       <c r="W112" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2475.2)</f>
-        <v>2475.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2687.36)</f>
+        <v>2687.36</v>
       </c>
       <c r="X112" s="84"/>
       <c r="Y112" s="84"/>
@@ -8298,12 +8307,12 @@
       <c r="T113" s="84"/>
       <c r="U113" s="84"/>
       <c r="V113" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),24.0)</f>
-        <v>24</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W113" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3394.56)</f>
-        <v>3394.56</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="X113" s="84"/>
       <c r="Y113" s="84"/>
@@ -8415,12 +8424,12 @@
       <c r="T115" s="84"/>
       <c r="U115" s="84"/>
       <c r="V115" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),58.0)</f>
-        <v>58</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W115" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9587.864)</f>
-        <v>9587.864</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="X115" s="84"/>
       <c r="Y115" s="84"/>
@@ -8472,12 +8481,12 @@
       <c r="T116" s="84"/>
       <c r="U116" s="84"/>
       <c r="V116" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.5)</f>
-        <v>16.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
       </c>
       <c r="W116" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2523.378)</f>
-        <v>2523.378</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),611.728)</f>
+        <v>611.728</v>
       </c>
       <c r="X116" s="84"/>
       <c r="Y116" s="84"/>
@@ -8529,12 +8538,12 @@
       <c r="T117" s="84"/>
       <c r="U117" s="84"/>
       <c r="V117" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),218.0)</f>
-        <v>218</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23.0)</f>
+        <v>23</v>
       </c>
       <c r="W117" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),32492.244)</f>
-        <v>32492.244</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3802.084)</f>
+        <v>3802.084</v>
       </c>
       <c r="X117" s="84"/>
       <c r="Y117" s="84"/>
@@ -8637,12 +8646,12 @@
       <c r="T119" s="84"/>
       <c r="U119" s="84"/>
       <c r="V119" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),48.0)</f>
-        <v>48</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),33.0)</f>
+        <v>33</v>
       </c>
       <c r="W119" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6789.12)</f>
-        <v>6789.12</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4667.52)</f>
+        <v>4667.52</v>
       </c>
       <c r="X119" s="84"/>
       <c r="Y119" s="84"/>
@@ -8694,12 +8703,12 @@
       <c r="T120" s="84"/>
       <c r="U120" s="84"/>
       <c r="V120" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),30.5)</f>
-        <v>30.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W120" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4313.92)</f>
-        <v>4313.92</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="X120" s="84"/>
       <c r="Y120" s="84"/>
@@ -8964,12 +8973,12 @@
       <c r="T125" s="84"/>
       <c r="U125" s="84"/>
       <c r="V125" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),53.0)</f>
-        <v>53</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.0)</f>
+        <v>12</v>
       </c>
       <c r="W125" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8105.396)</f>
-        <v>8105.396</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1835.184)</f>
+        <v>1835.184</v>
       </c>
       <c r="X125" s="84"/>
       <c r="Y125" s="84"/>
@@ -9021,12 +9030,12 @@
       <c r="T126" s="84"/>
       <c r="U126" s="84"/>
       <c r="V126" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),81.5)</f>
-        <v>81.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14.0)</f>
+        <v>14</v>
       </c>
       <c r="W126" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12463.958)</f>
-        <v>12463.958</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2141.048)</f>
+        <v>2141.048</v>
       </c>
       <c r="X126" s="84"/>
       <c r="Y126" s="84"/>
@@ -9078,12 +9087,12 @@
       <c r="T127" s="84"/>
       <c r="U127" s="84"/>
       <c r="V127" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),42.0)</f>
-        <v>42</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.0)</f>
+        <v>12</v>
       </c>
       <c r="W127" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7140.0)</f>
-        <v>7140</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2040.0)</f>
+        <v>2040</v>
       </c>
       <c r="X127" s="84"/>
       <c r="Y127" s="84"/>
@@ -9134,10 +9143,13 @@
       <c r="S128" s="84"/>
       <c r="T128" s="84"/>
       <c r="U128" s="84"/>
-      <c r="V128" s="84"/>
+      <c r="V128" s="90">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14.0)</f>
+        <v>14</v>
+      </c>
       <c r="W128" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2141.048)</f>
+        <v>2141.048</v>
       </c>
       <c r="X128" s="84"/>
       <c r="Y128" s="84"/>
@@ -9188,10 +9200,13 @@
       <c r="S129" s="84"/>
       <c r="T129" s="84"/>
       <c r="U129" s="84"/>
-      <c r="V129" s="84"/>
+      <c r="V129" s="90">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6.0)</f>
+        <v>6</v>
+      </c>
       <c r="W129" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1200.0)</f>
+        <v>1200</v>
       </c>
       <c r="X129" s="84"/>
       <c r="Y129" s="84"/>
@@ -12531,12 +12546,12 @@
       <c r="T196" s="84"/>
       <c r="U196" s="84"/>
       <c r="V196" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2826.0)</f>
-        <v>2826</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),381.0)</f>
+        <v>381</v>
       </c>
       <c r="W196" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),483172.0800000001)</f>
-        <v>483172.08</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),132729.862)</f>
+        <v>132729.862</v>
       </c>
       <c r="X196" s="84"/>
       <c r="Y196" s="84"/>
@@ -43926,7 +43941,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="94" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C1" s="94" t="s">
         <v>4</v>
@@ -43938,16 +43953,16 @@
         <v>8</v>
       </c>
       <c r="F1" s="94" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G1" s="94" t="s">
         <v>10</v>
       </c>
       <c r="H1" s="94" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I1" s="94" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J1" s="94" t="s">
         <v>15</v>
@@ -43961,22 +43976,22 @@
         <v>45528.0</v>
       </c>
       <c r="B2" s="94" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" s="94" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D2" s="96" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E2" s="96" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F2" s="96" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G2" s="96" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H2" s="97">
         <v>3728.0</v>
@@ -43987,22 +44002,22 @@
         <v>45528.0</v>
       </c>
       <c r="B3" s="94" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C3" s="94" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D3" s="96" t="s">
+        <v>37</v>
+      </c>
+      <c r="E3" s="96" t="s">
+        <v>38</v>
+      </c>
+      <c r="F3" s="96" t="s">
+        <v>35</v>
+      </c>
+      <c r="G3" s="96" t="s">
         <v>36</v>
-      </c>
-      <c r="E3" s="96" t="s">
-        <v>37</v>
-      </c>
-      <c r="F3" s="96" t="s">
-        <v>34</v>
-      </c>
-      <c r="G3" s="96" t="s">
-        <v>35</v>
       </c>
       <c r="H3" s="97">
         <v>3728.0</v>
@@ -44013,19 +44028,19 @@
         <v>45528.0</v>
       </c>
       <c r="B4" s="94" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C4" s="94" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D4" s="96" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E4" s="96" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G4" s="96" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H4" s="97">
         <v>3728.0</v>
@@ -44036,7 +44051,7 @@
         <v>45528.0</v>
       </c>
       <c r="B5" s="94" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I5" s="97">
         <v>12.0</v>
@@ -44053,22 +44068,22 @@
         <v>45526.0</v>
       </c>
       <c r="B6" s="94" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C6" s="94" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D6" s="96" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E6" s="96" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F6" s="96" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G6" s="96" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H6" s="97">
         <v>3728.0</v>
@@ -44079,22 +44094,22 @@
         <v>45526.0</v>
       </c>
       <c r="B7" s="94" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C7" s="94" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D7" s="96" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" s="96" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" s="96" t="s">
+        <v>35</v>
+      </c>
+      <c r="G7" s="96" t="s">
         <v>36</v>
-      </c>
-      <c r="E7" s="96" t="s">
-        <v>37</v>
-      </c>
-      <c r="F7" s="96" t="s">
-        <v>34</v>
-      </c>
-      <c r="G7" s="96" t="s">
-        <v>35</v>
       </c>
       <c r="H7" s="97">
         <v>3728.0</v>
@@ -44105,19 +44120,19 @@
         <v>45526.0</v>
       </c>
       <c r="B8" s="94" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" s="94" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="96" t="s">
         <v>39</v>
       </c>
-      <c r="C8" s="94" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" s="96" t="s">
-        <v>38</v>
-      </c>
       <c r="E8" s="96" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G8" s="96" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H8" s="97">
         <v>3728.0</v>
@@ -44128,7 +44143,7 @@
         <v>45526.0</v>
       </c>
       <c r="B9" s="94" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I9" s="97">
         <v>12.0</v>
@@ -44145,22 +44160,22 @@
         <v>45526.0</v>
       </c>
       <c r="B10" s="94" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C10" s="94" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D10" s="96" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E10" s="96" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F10" s="96" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G10" s="96" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H10" s="97">
         <v>3728.0</v>
@@ -44171,22 +44186,22 @@
         <v>45526.0</v>
       </c>
       <c r="B11" s="94" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C11" s="94" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D11" s="96" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" s="96" t="s">
+        <v>38</v>
+      </c>
+      <c r="F11" s="96" t="s">
+        <v>35</v>
+      </c>
+      <c r="G11" s="96" t="s">
         <v>36</v>
-      </c>
-      <c r="E11" s="96" t="s">
-        <v>37</v>
-      </c>
-      <c r="F11" s="96" t="s">
-        <v>34</v>
-      </c>
-      <c r="G11" s="96" t="s">
-        <v>35</v>
       </c>
       <c r="H11" s="97">
         <v>3728.0</v>
@@ -44197,19 +44212,19 @@
         <v>45526.0</v>
       </c>
       <c r="B12" s="94" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" s="94" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" s="96" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="94" t="s">
-        <v>22</v>
-      </c>
-      <c r="D12" s="96" t="s">
-        <v>38</v>
-      </c>
       <c r="E12" s="96" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G12" s="96" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H12" s="97">
         <v>3728.0</v>
@@ -44220,7 +44235,7 @@
         <v>45526.0</v>
       </c>
       <c r="B13" s="94" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I13" s="97">
         <v>12.0</v>
@@ -44237,7 +44252,7 @@
         <v>45532.0</v>
       </c>
       <c r="B14" s="94" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15">
@@ -44245,7 +44260,7 @@
         <v>45533.0</v>
       </c>
       <c r="B15" s="94" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16">
@@ -44253,7 +44268,7 @@
         <v>45534.0</v>
       </c>
       <c r="B16" s="94" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17">
@@ -44261,7 +44276,7 @@
         <v>45535.0</v>
       </c>
       <c r="B17" s="94" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -44295,7 +44310,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="98" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -44499,7 +44514,7 @@
       <c r="Y19" s="100"/>
       <c r="Z19" s="100"/>
       <c r="AA19" s="94" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AB19" s="94">
         <v>-11.0</v>
@@ -44824,7 +44839,7 @@
       <c r="Y30" s="100"/>
       <c r="Z30" s="100"/>
       <c r="AA30" s="94" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AB30" s="94">
         <v>-8.0</v>
@@ -44945,7 +44960,7 @@
       <c r="Y34" s="100"/>
       <c r="Z34" s="100"/>
       <c r="AA34" s="94" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AB34" s="94">
         <v>0.0</v>
@@ -45064,7 +45079,7 @@
       <c r="Y38" s="100"/>
       <c r="Z38" s="100"/>
       <c r="AA38" s="94" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AB38" s="94">
         <v>-12.0</v>
@@ -45098,7 +45113,7 @@
       <c r="Y39" s="100"/>
       <c r="Z39" s="100"/>
       <c r="AA39" s="94" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AB39" s="94">
         <v>0.0</v>
@@ -45190,7 +45205,7 @@
       <c r="Y42" s="100"/>
       <c r="Z42" s="100"/>
       <c r="AA42" s="94" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AB42" s="94">
         <v>6.0</v>
@@ -45369,7 +45384,7 @@
       <c r="Y48" s="100"/>
       <c r="Z48" s="100"/>
       <c r="AA48" s="94" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AB48" s="94">
         <v>-13.0</v>
@@ -45490,7 +45505,7 @@
       <c r="Y52" s="100"/>
       <c r="Z52" s="100"/>
       <c r="AA52" s="94" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AB52" s="94">
         <v>5.0</v>
@@ -45698,7 +45713,7 @@
       <c r="Y59" s="100"/>
       <c r="Z59" s="100"/>
       <c r="AA59" s="94" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AB59" s="94">
         <v>-9.0</v>
@@ -45819,7 +45834,7 @@
       <c r="Y63" s="100"/>
       <c r="Z63" s="100"/>
       <c r="AA63" s="94" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AB63" s="94">
         <v>-19.0</v>
@@ -46027,7 +46042,7 @@
       <c r="Y70" s="100"/>
       <c r="Z70" s="100"/>
       <c r="AA70" s="94" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AB70" s="94">
         <v>-14.0</v>
@@ -46496,7 +46511,7 @@
       <c r="Y86" s="100"/>
       <c r="Z86" s="100"/>
       <c r="AA86" s="94" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AB86" s="94">
         <v>-21.0</v>
@@ -46530,7 +46545,7 @@
       <c r="Y87" s="100"/>
       <c r="Z87" s="100"/>
       <c r="AA87" s="94" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AB87" s="94">
         <v>-7.0</v>
@@ -46564,7 +46579,7 @@
       <c r="Y88" s="100"/>
       <c r="Z88" s="100"/>
       <c r="AA88" s="94" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AB88" s="94">
         <v>-10.0</v>
@@ -46598,7 +46613,7 @@
       <c r="Y89" s="100"/>
       <c r="Z89" s="100"/>
       <c r="AA89" s="94" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AB89" s="94">
         <v>-6.0</v>
@@ -46691,7 +46706,7 @@
       <c r="Y92" s="100"/>
       <c r="Z92" s="100"/>
       <c r="AA92" s="94" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AB92" s="94">
         <v>-17.0</v>
@@ -46957,7 +46972,7 @@
       <c r="Y101" s="100"/>
       <c r="Z101" s="100"/>
       <c r="AA101" s="94" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AB101" s="94">
         <v>-6.0</v>
@@ -46991,7 +47006,7 @@
       <c r="Y102" s="100"/>
       <c r="Z102" s="100"/>
       <c r="AA102" s="94" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AB102" s="94">
         <v>1.0</v>
@@ -47083,7 +47098,7 @@
       <c r="Y105" s="100"/>
       <c r="Z105" s="100"/>
       <c r="AA105" s="94" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AB105" s="94">
         <v>-2.0</v>
@@ -47146,7 +47161,7 @@
       <c r="Y107" s="100"/>
       <c r="Z107" s="100"/>
       <c r="AA107" s="94" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AB107" s="94">
         <v>-12.0</v>
@@ -47238,7 +47253,7 @@
       <c r="Y110" s="100"/>
       <c r="Z110" s="100"/>
       <c r="AA110" s="94" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AB110" s="94">
         <v>-14.0</v>
@@ -47272,7 +47287,7 @@
       <c r="Y111" s="100"/>
       <c r="Z111" s="100"/>
       <c r="AA111" s="94" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AB111" s="94">
         <v>-6.0</v>
@@ -47306,7 +47321,7 @@
       <c r="Y112" s="100"/>
       <c r="Z112" s="100"/>
       <c r="AA112" s="94" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AB112" s="94">
         <v>-11.0</v>
@@ -47369,7 +47384,7 @@
       <c r="Y114" s="100"/>
       <c r="Z114" s="100"/>
       <c r="AA114" s="94" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AB114" s="94">
         <v>-1.0</v>
@@ -47461,7 +47476,7 @@
       <c r="Y117" s="100"/>
       <c r="Z117" s="100"/>
       <c r="AA117" s="94" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AB117" s="94">
         <v>12.0</v>
@@ -47524,7 +47539,7 @@
       <c r="Y119" s="100"/>
       <c r="Z119" s="100"/>
       <c r="AA119" s="94" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AB119" s="94">
         <v>-17.0</v>
@@ -47645,7 +47660,7 @@
       <c r="Y123" s="100"/>
       <c r="Z123" s="100"/>
       <c r="AA123" s="94" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AB123" s="94">
         <v>-15.0</v>
@@ -47796,7 +47811,7 @@
       <c r="Y128" s="100"/>
       <c r="Z128" s="100"/>
       <c r="AA128" s="94" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AB128" s="94">
         <v>-11.0</v>
@@ -48181,7 +48196,7 @@
       <c r="Y141" s="100"/>
       <c r="Z141" s="100"/>
       <c r="AA141" s="94" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AB141" s="94">
         <v>-10.0</v>

--- a/google_data/Pobočky/Výroba/Report Vyroba.xlsx
+++ b/google_data/Pobočky/Výroba/Report Vyroba.xlsx
@@ -60,7 +60,7 @@
     <t>06:00</t>
   </si>
   <si>
-    <t>14:30</t>
+    <t>14:00</t>
   </si>
   <si>
     <t>Suroviny</t>
@@ -1399,7 +1399,7 @@
         <v>1</v>
       </c>
       <c r="D1" s="4">
-        <v>46178.0</v>
+        <v>46183.0</v>
       </c>
       <c r="E1" s="5"/>
       <c r="F1" s="6" t="s">
@@ -1418,8 +1418,8 @@
       <c r="D2" s="13"/>
       <c r="E2" s="14"/>
       <c r="F2" s="15">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("SUM(A14:A20) + SUM(FILTER(HR!W5:W48, HR!A5:A48 &lt;&gt; """")) + J13 + J15"),40484.25)</f>
-        <v>40484.25</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("SUM(A14:A20) + SUM(FILTER(HR!W5:W48, HR!A5:A48 &lt;&gt; """")) + J13 + J15"),40456.0)</f>
+        <v>40456</v>
       </c>
       <c r="H2" s="16"/>
       <c r="K2" s="16"/>
@@ -1428,7 +1428,7 @@
       <c r="A3" s="17"/>
       <c r="B3" s="18" t="str">
         <f>CHOOSE(WEEKDAY(D1), "Neděle", "Pondělí", "Úterý", "Středa", "Čtvrtek", "Pátek", "Sobota")</f>
-        <v>Pátek</v>
+        <v>Středa</v>
       </c>
       <c r="C3" s="10"/>
       <c r="D3" s="10"/>
@@ -1581,7 +1581,7 @@
       <c r="F14" s="42" t="str">
         <f t="shared" ref="F14:F20" si="1">IF(OR(ISBLANK(B14), ISBLANK(D14), D14=0), "0:00", TEXT((IF(AND(TIMEVALUE(IF(ISBLANK(D14), "00:00", D14))&gt;=TIMEVALUE("00:00"), TIMEVALUE(IF(ISBLANK(D14), "00:00", D14))&lt;=TIMEVALUE("06:00")), TIMEVALUE(IF(ISBLANK(D14), "00:00", D14))+1, TIMEVALUE(IF(ISBLANK(D14), "00:00", D14))) - TIMEVALUE(IF(ISBLANK(C14), "00:00", C14)) - TIMEVALUE(IF(ISBLANK(E14), "00:00", E14))), "hh:mm"))
 </f>
-        <v>08:30</v>
+        <v>08:00</v>
       </c>
       <c r="G14" s="43" t="s">
         <v>15</v>
@@ -1594,7 +1594,7 @@
     <row r="15">
       <c r="A15" s="38">
         <f t="array" ref="A15">IF(ISBLANK(B15), 0, IF(ISNUMBER(MATCH(B15, HR!A:A, 0)), 0, IF(ISNUMBER(MATCH(B15, HR!B:B, 0)), INDEX(HR!V:V, MATCH(B15, HR!B:B, 0)) * (F15 * 24), 0)))</f>
-        <v>276.25</v>
+        <v>260</v>
       </c>
       <c r="B15" s="47" t="s">
         <v>16</v>
@@ -1608,7 +1608,7 @@
       <c r="E15" s="40"/>
       <c r="F15" s="42" t="str">
         <f t="shared" si="1"/>
-        <v>08:30</v>
+        <v>08:00</v>
       </c>
       <c r="G15" s="48" t="s">
         <v>17</v>
@@ -1621,7 +1621,7 @@
     <row r="16">
       <c r="A16" s="38">
         <f t="array" ref="A16">IF(ISBLANK(B16), 0, IF(ISNUMBER(MATCH(B16, HR!A:A, 0)), 0, IF(ISNUMBER(MATCH(B16, HR!B:B, 0)), INDEX(HR!V:V, MATCH(B16, HR!B:B, 0)) * (F16 * 24), 0)))</f>
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="B16" s="39" t="s">
         <v>18</v>
@@ -1635,7 +1635,7 @@
       <c r="E16" s="52"/>
       <c r="F16" s="53" t="str">
         <f t="shared" si="1"/>
-        <v>08:30</v>
+        <v>08:00</v>
       </c>
       <c r="G16" s="54"/>
       <c r="K16" s="16"/>
@@ -6562,7 +6562,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
         <v>Libuš</v>
       </c>
-      <c r="F83" s="84"/>
+      <c r="F83" s="84" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Malešice")</f>
+        <v>Malešice</v>
+      </c>
       <c r="G83" s="84"/>
       <c r="H83" s="84"/>
       <c r="I83" s="84"/>

--- a/google_data/Pobočky/Výroba/Report Vyroba.xlsx
+++ b/google_data/Pobočky/Výroba/Report Vyroba.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="72">
   <si>
     <t>Výroba</t>
   </si>
@@ -70,9 +70,6 @@
   </si>
   <si>
     <t>Ostatní</t>
-  </si>
-  <si>
-    <t>Ahurieva Viktoriia</t>
   </si>
   <si>
     <t>Vyber datum    &lt;----------&gt;</t>
@@ -1399,7 +1396,7 @@
         <v>1</v>
       </c>
       <c r="D1" s="4">
-        <v>46183.0</v>
+        <v>46189.0</v>
       </c>
       <c r="E1" s="5"/>
       <c r="F1" s="6" t="s">
@@ -1418,8 +1415,8 @@
       <c r="D2" s="13"/>
       <c r="E2" s="14"/>
       <c r="F2" s="15">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("SUM(A14:A20) + SUM(FILTER(HR!W5:W48, HR!A5:A48 &lt;&gt; """")) + J13 + J15"),40456.0)</f>
-        <v>40456</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("SUM(A14:A20) + SUM(FILTER(HR!W5:W48, HR!A5:A48 &lt;&gt; """")) + J13 + J15"),40672.0)</f>
+        <v>40672</v>
       </c>
       <c r="H2" s="16"/>
       <c r="K2" s="16"/>
@@ -1428,7 +1425,7 @@
       <c r="A3" s="17"/>
       <c r="B3" s="18" t="str">
         <f>CHOOSE(WEEKDAY(D1), "Neděle", "Pondělí", "Úterý", "Středa", "Čtvrtek", "Pátek", "Sobota")</f>
-        <v>Středa</v>
+        <v>Úterý</v>
       </c>
       <c r="C3" s="10"/>
       <c r="D3" s="10"/>
@@ -1594,7 +1591,7 @@
     <row r="15">
       <c r="A15" s="38">
         <f t="array" ref="A15">IF(ISBLANK(B15), 0, IF(ISNUMBER(MATCH(B15, HR!A:A, 0)), 0, IF(ISNUMBER(MATCH(B15, HR!B:B, 0)), INDEX(HR!V:V, MATCH(B15, HR!B:B, 0)) * (F15 * 24), 0)))</f>
-        <v>260</v>
+        <v>668</v>
       </c>
       <c r="B15" s="47" t="s">
         <v>16</v>
@@ -1621,21 +1618,15 @@
     <row r="16">
       <c r="A16" s="38">
         <f t="array" ref="A16">IF(ISBLANK(B16), 0, IF(ISNUMBER(MATCH(B16, HR!A:A, 0)), 0, IF(ISNUMBER(MATCH(B16, HR!B:B, 0)), INDEX(HR!V:V, MATCH(B16, HR!B:B, 0)) * (F16 * 24), 0)))</f>
-        <v>192</v>
-      </c>
-      <c r="B16" s="39" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" s="40" t="s">
-        <v>13</v>
-      </c>
-      <c r="D16" s="40" t="s">
-        <v>14</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="B16" s="39"/>
+      <c r="C16" s="40"/>
+      <c r="D16" s="40"/>
       <c r="E16" s="52"/>
       <c r="F16" s="53" t="str">
         <f t="shared" si="1"/>
-        <v>08:00</v>
+        <v>0:00</v>
       </c>
       <c r="G16" s="54"/>
       <c r="K16" s="16"/>
@@ -1737,7 +1728,7 @@
   </conditionalFormatting>
   <dataValidations>
     <dataValidation type="list" allowBlank="1" sqref="B14:B20">
-      <formula1>"Sova Martin,Paziak Viktoriia,Ahurieva Viktoriia,Stepanenko Solomiia,Kursheva Diana,Lažek Jaroslav,Chlubna Tomáš,Hřebík Martin"</formula1>
+      <formula1>"Sova Martin,Paziak Viktoriia,Ahurieva Viktoriia,Kursheva Diana,Lažek Jaroslav,Chlubna Tomáš,Hřebík Martin"</formula1>
     </dataValidation>
   </dataValidations>
   <drawing r:id="rId1"/>
@@ -1770,7 +1761,7 @@
         <v>46143.0</v>
       </c>
       <c r="D1" s="63" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E1" s="62">
         <v>46173.0</v>
@@ -1820,7 +1811,7 @@
     <row r="5">
       <c r="A5" s="68"/>
       <c r="B5" s="69" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C5" s="10"/>
       <c r="D5" s="10"/>
@@ -1893,7 +1884,7 @@
         <v>6</v>
       </c>
       <c r="C9" s="79" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D9" s="79" t="s">
         <v>10</v>
@@ -1915,7 +1906,7 @@
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="71"/>
       <c r="B11" s="80" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C11" s="81">
         <v>16.0</v>
@@ -1939,7 +1930,7 @@
     <row r="13" ht="18.75" customHeight="1">
       <c r="A13" s="71"/>
       <c r="B13" s="80" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C13" s="81">
         <v>11.0</v>
@@ -1951,7 +1942,7 @@
     <row r="14" ht="18.75" customHeight="1">
       <c r="A14" s="71"/>
       <c r="B14" s="80" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C14" s="81">
         <v>1.0</v>
@@ -2165,10 +2156,10 @@
     </row>
     <row r="4">
       <c r="A4" s="88" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="88" t="s">
         <v>25</v>
-      </c>
-      <c r="B4" s="88" t="s">
-        <v>26</v>
       </c>
       <c r="C4" s="84" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Manažer")</f>
@@ -2265,8 +2256,8 @@
       <c r="T5" s="84"/>
       <c r="U5" s="84"/>
       <c r="V5" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),13.5)</f>
-        <v>13.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),100.0)</f>
+        <v>100</v>
       </c>
       <c r="W5" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50001.08)</f>
@@ -2331,8 +2322,8 @@
       <c r="T6" s="84"/>
       <c r="U6" s="84"/>
       <c r="V6" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),38.5)</f>
-        <v>38.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),112.0)</f>
+        <v>112</v>
       </c>
       <c r="W6" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50001.08)</f>
@@ -2391,8 +2382,8 @@
       <c r="T7" s="84"/>
       <c r="U7" s="84"/>
       <c r="V7" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),32.5)</f>
-        <v>32.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),83.5)</f>
+        <v>83.5</v>
       </c>
       <c r="W7" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40004.0)</f>
@@ -2460,8 +2451,8 @@
       <c r="T8" s="84"/>
       <c r="U8" s="84"/>
       <c r="V8" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),24.0)</f>
-        <v>24</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),106.0)</f>
+        <v>106</v>
       </c>
       <c r="W8" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50001.08)</f>
@@ -2523,8 +2514,8 @@
       <c r="T9" s="84"/>
       <c r="U9" s="84"/>
       <c r="V9" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14.5)</f>
-        <v>14.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),88.0)</f>
+        <v>88</v>
       </c>
       <c r="W9" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40004.0)</f>
@@ -2592,8 +2583,8 @@
       <c r="T10" s="84"/>
       <c r="U10" s="84"/>
       <c r="V10" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.0)</f>
-        <v>18</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),92.5)</f>
+        <v>92.5</v>
       </c>
       <c r="W10" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50001.08)</f>
@@ -2652,12 +2643,12 @@
       <c r="T11" s="84"/>
       <c r="U11" s="84"/>
       <c r="V11" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.0)</f>
-        <v>22</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),39.5)</f>
+        <v>39.5</v>
       </c>
       <c r="W11" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4298.008)</f>
-        <v>4298.008</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7716.878)</f>
+        <v>7716.878</v>
       </c>
       <c r="X11" s="84"/>
       <c r="Y11" s="84"/>
@@ -2772,8 +2763,8 @@
       <c r="T13" s="84"/>
       <c r="U13" s="84"/>
       <c r="V13" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.5)</f>
-        <v>22.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),110.0)</f>
+        <v>110</v>
       </c>
       <c r="W13" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40004.0)</f>
@@ -2838,12 +2829,12 @@
       <c r="T14" s="84"/>
       <c r="U14" s="84"/>
       <c r="V14" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.5)</f>
-        <v>9.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),37.5)</f>
+        <v>37.5</v>
       </c>
       <c r="W14" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1570.426)</f>
-        <v>1570.426</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6199.05)</f>
+        <v>6199.05</v>
       </c>
       <c r="X14" s="84"/>
       <c r="Y14" s="84"/>
@@ -2901,8 +2892,8 @@
       <c r="T15" s="84"/>
       <c r="U15" s="84"/>
       <c r="V15" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.0)</f>
-        <v>21</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),95.0)</f>
+        <v>95</v>
       </c>
       <c r="W15" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40004.0)</f>
@@ -2964,8 +2955,8 @@
       <c r="T16" s="84"/>
       <c r="U16" s="84"/>
       <c r="V16" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.0)</f>
-        <v>35</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),74.0)</f>
+        <v>74</v>
       </c>
       <c r="W16" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40004.0)</f>
@@ -3024,12 +3015,12 @@
       <c r="T17" s="84"/>
       <c r="U17" s="84"/>
       <c r="V17" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),53.0)</f>
+        <v>53</v>
       </c>
       <c r="W17" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9370.4)</f>
+        <v>9370.4</v>
       </c>
       <c r="X17" s="84"/>
       <c r="Y17" s="84"/>
@@ -3053,20 +3044,14 @@
       </c>
       <c r="B18" s="89" t="str">
         <f>IF(OR(E18=Report!$B$1, F18=Report!$B$1, G18=Report!$B$1, H18=Report!$B$1), D18, "")</f>
-        <v>Stepanenko Solomiia</v>
+        <v/>
       </c>
       <c r="C18" s="84" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D18" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Stepanenko Solomiia")</f>
-        <v>Stepanenko Solomiia</v>
-      </c>
-      <c r="E18" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Výroba")</f>
-        <v>Výroba</v>
-      </c>
+      <c r="D18" s="84"/>
+      <c r="E18" s="84"/>
       <c r="F18" s="84"/>
       <c r="G18" s="84"/>
       <c r="H18" s="84"/>
@@ -3119,14 +3104,8 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D19" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Rothová Anastasia")</f>
-        <v>Rothová Anastasia</v>
-      </c>
-      <c r="E19" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bolevec")</f>
-        <v>Bolevec</v>
-      </c>
+      <c r="D19" s="84"/>
+      <c r="E19" s="84"/>
       <c r="F19" s="84"/>
       <c r="G19" s="84"/>
       <c r="H19" s="84"/>
@@ -3204,12 +3183,12 @@
       <c r="T20" s="84"/>
       <c r="U20" s="84"/>
       <c r="V20" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14.0)</f>
-        <v>14</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46.5)</f>
+        <v>46.5</v>
       </c>
       <c r="W20" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2475.2)</f>
-        <v>2475.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8221.2)</f>
+        <v>8221.2</v>
       </c>
       <c r="X20" s="84"/>
       <c r="Y20" s="84"/>
@@ -3273,8 +3252,8 @@
       <c r="T21" s="84"/>
       <c r="U21" s="84"/>
       <c r="V21" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27.5)</f>
-        <v>27.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),118.5)</f>
+        <v>118.5</v>
       </c>
       <c r="W21" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50001.08)</f>
@@ -3333,8 +3312,8 @@
       <c r="T22" s="84"/>
       <c r="U22" s="84"/>
       <c r="V22" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),60.5)</f>
-        <v>60.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),217.0)</f>
+        <v>217</v>
       </c>
       <c r="W22" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50001.08)</f>
@@ -3456,12 +3435,12 @@
       <c r="T24" s="84"/>
       <c r="U24" s="84"/>
       <c r="V24" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23.5)</f>
-        <v>23.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),91.5)</f>
+        <v>91.5</v>
       </c>
       <c r="W24" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4154.8)</f>
-        <v>4154.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16002.2)</f>
+        <v>16002.2</v>
       </c>
       <c r="X24" s="84"/>
       <c r="Y24" s="84"/>
@@ -3630,12 +3609,12 @@
       <c r="T27" s="84"/>
       <c r="U27" s="84"/>
       <c r="V27" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),13.0)</f>
+        <v>13</v>
       </c>
       <c r="W27" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2459.288)</f>
+        <v>2459.288</v>
       </c>
       <c r="X27" s="84"/>
       <c r="Y27" s="84"/>
@@ -3699,12 +3678,12 @@
       <c r="T28" s="84"/>
       <c r="U28" s="84"/>
       <c r="V28" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.5)</f>
-        <v>35.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),102.0)</f>
+        <v>102</v>
       </c>
       <c r="W28" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6276.4)</f>
-        <v>6276.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17543.6)</f>
+        <v>17543.6</v>
       </c>
       <c r="X28" s="84"/>
       <c r="Y28" s="84"/>
@@ -3734,14 +3713,8 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D29" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Raboch Tomáš")</f>
-        <v>Raboch Tomáš</v>
-      </c>
-      <c r="E29" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bolevec")</f>
-        <v>Bolevec</v>
-      </c>
+      <c r="D29" s="84"/>
+      <c r="E29" s="84"/>
       <c r="F29" s="84"/>
       <c r="G29" s="84"/>
       <c r="H29" s="84"/>
@@ -3802,7 +3775,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chodov")</f>
         <v>Chodov</v>
       </c>
-      <c r="F30" s="84"/>
+      <c r="F30" s="84" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Malešice")</f>
+        <v>Malešice</v>
+      </c>
       <c r="G30" s="84"/>
       <c r="H30" s="84"/>
       <c r="I30" s="84"/>
@@ -3819,12 +3795,12 @@
       <c r="T30" s="84"/>
       <c r="U30" s="84"/>
       <c r="V30" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.5)</f>
-        <v>21.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),91.0)</f>
+        <v>91</v>
       </c>
       <c r="W30" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3554.122)</f>
-        <v>3554.122</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15043.028)</f>
+        <v>15043.028</v>
       </c>
       <c r="X30" s="84"/>
       <c r="Y30" s="84"/>
@@ -4128,12 +4104,12 @@
       <c r="T35" s="84"/>
       <c r="U35" s="84"/>
       <c r="V35" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),32.5)</f>
-        <v>32.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),83.5)</f>
+        <v>83.5</v>
       </c>
       <c r="W35" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5372.51)</f>
-        <v>5372.51</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),13803.218)</f>
+        <v>13803.218</v>
       </c>
       <c r="X35" s="84"/>
       <c r="Y35" s="84"/>
@@ -4311,12 +4287,12 @@
       <c r="T38" s="84"/>
       <c r="U38" s="84"/>
       <c r="V38" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.0)</f>
-        <v>16</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),110.0)</f>
+        <v>110</v>
       </c>
       <c r="W38" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2644.928)</f>
-        <v>2644.928</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17668.38)</f>
+        <v>17668.38</v>
       </c>
       <c r="X38" s="84"/>
       <c r="Y38" s="84"/>
@@ -4380,12 +4356,12 @@
       <c r="T39" s="84"/>
       <c r="U39" s="84"/>
       <c r="V39" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29.5)</f>
-        <v>29.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),97.5)</f>
+        <v>97.5</v>
       </c>
       <c r="W39" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4876.586)</f>
-        <v>4876.586</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15952.655)</f>
+        <v>15952.655</v>
       </c>
       <c r="X39" s="84"/>
       <c r="Y39" s="84"/>
@@ -4440,12 +4416,12 @@
       <c r="T40" s="84"/>
       <c r="U40" s="84"/>
       <c r="V40" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.0)</f>
+        <v>8</v>
       </c>
       <c r="W40" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1322.464)</f>
+        <v>1322.464</v>
       </c>
       <c r="X40" s="84"/>
       <c r="Y40" s="84"/>
@@ -4500,12 +4476,12 @@
       <c r="T41" s="84"/>
       <c r="U41" s="84"/>
       <c r="V41" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),13.0)</f>
-        <v>13</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),66.0)</f>
+        <v>66</v>
       </c>
       <c r="W41" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2149.004)</f>
-        <v>2149.004</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10910.328)</f>
+        <v>10910.328</v>
       </c>
       <c r="X41" s="84"/>
       <c r="Y41" s="84"/>
@@ -4535,8 +4511,14 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D42" s="84"/>
-      <c r="E42" s="84"/>
+      <c r="D42" s="84" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Prošek Václav")</f>
+        <v>Prošek Václav</v>
+      </c>
+      <c r="E42" s="84" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
+        <v>Libuš</v>
+      </c>
       <c r="F42" s="84"/>
       <c r="G42" s="84"/>
       <c r="H42" s="84"/>
@@ -4554,12 +4536,12 @@
       <c r="T42" s="84"/>
       <c r="U42" s="84"/>
       <c r="V42" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14.0)</f>
+        <v>14</v>
       </c>
       <c r="W42" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2314.312)</f>
+        <v>2314.312</v>
       </c>
       <c r="X42" s="84"/>
       <c r="Y42" s="84"/>
@@ -5421,12 +5403,12 @@
       <c r="T60" s="84"/>
       <c r="U60" s="84"/>
       <c r="V60" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),524.5)</f>
-        <v>524.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2049.5)</f>
+        <v>2049.5</v>
       </c>
       <c r="W60" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),615398.4639999999)</f>
-        <v>615398.464</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),722553.481)</f>
+        <v>722553.481</v>
       </c>
       <c r="X60" s="84"/>
       <c r="Y60" s="84"/>
@@ -6108,12 +6090,12 @@
       <c r="T75" s="84"/>
       <c r="U75" s="84"/>
       <c r="V75" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23.25)</f>
+        <v>23.25</v>
       </c>
       <c r="W75" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3487.5)</f>
+        <v>3487.5</v>
       </c>
       <c r="X75" s="84"/>
       <c r="Y75" s="84"/>
@@ -6165,12 +6147,12 @@
       <c r="T76" s="84"/>
       <c r="U76" s="84"/>
       <c r="V76" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.0)</f>
-        <v>31</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),76.0)</f>
+        <v>76</v>
       </c>
       <c r="W76" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5480.8)</f>
-        <v>5480.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),13436.8)</f>
+        <v>13436.8</v>
       </c>
       <c r="X76" s="84"/>
       <c r="Y76" s="84"/>
@@ -6279,12 +6261,12 @@
       <c r="T78" s="84"/>
       <c r="U78" s="84"/>
       <c r="V78" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
-        <v>10</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.0)</f>
+        <v>22</v>
       </c>
       <c r="W78" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1768.0)</f>
-        <v>1768</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3889.6)</f>
+        <v>3889.6</v>
       </c>
       <c r="X78" s="84"/>
       <c r="Y78" s="84"/>
@@ -6342,12 +6324,12 @@
       <c r="T79" s="84"/>
       <c r="U79" s="84"/>
       <c r="V79" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.5)</f>
-        <v>5.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23.0)</f>
+        <v>23</v>
       </c>
       <c r="W79" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),841.126)</f>
-        <v>841.126</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3517.436)</f>
+        <v>3517.436</v>
       </c>
       <c r="X79" s="84"/>
       <c r="Y79" s="84"/>
@@ -6405,12 +6387,12 @@
       <c r="T80" s="84"/>
       <c r="U80" s="84"/>
       <c r="V80" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.5)</f>
-        <v>22.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),71.5)</f>
+        <v>71.5</v>
       </c>
       <c r="W80" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3719.43)</f>
-        <v>3719.43</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11819.522)</f>
+        <v>11819.522</v>
       </c>
       <c r="X80" s="84"/>
       <c r="Y80" s="84"/>
@@ -6465,12 +6447,12 @@
       <c r="T81" s="84"/>
       <c r="U81" s="84"/>
       <c r="V81" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14.0)</f>
-        <v>14</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),47.5)</f>
+        <v>47.5</v>
       </c>
       <c r="W81" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2141.048)</f>
-        <v>2141.048</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7264.27)</f>
+        <v>7264.27</v>
       </c>
       <c r="X81" s="84"/>
       <c r="Y81" s="84"/>
@@ -6582,12 +6564,12 @@
       <c r="T83" s="84"/>
       <c r="U83" s="84"/>
       <c r="V83" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.0)</f>
+        <v>22</v>
       </c>
       <c r="W83" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3364.504)</f>
+        <v>3364.504</v>
       </c>
       <c r="X83" s="84"/>
       <c r="Y83" s="84"/>
@@ -6642,12 +6624,12 @@
       <c r="T84" s="84"/>
       <c r="U84" s="84"/>
       <c r="V84" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6.0)</f>
-        <v>6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29.5)</f>
+        <v>29.5</v>
       </c>
       <c r="W84" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),991.848)</f>
-        <v>991.848</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4876.586)</f>
+        <v>4876.586</v>
       </c>
       <c r="X84" s="84"/>
       <c r="Y84" s="84"/>
@@ -6699,12 +6681,12 @@
       <c r="T85" s="84"/>
       <c r="U85" s="84"/>
       <c r="V85" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
-        <v>5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.5)</f>
+        <v>22.5</v>
       </c>
       <c r="W85" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),750.0)</f>
-        <v>750</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3375.0)</f>
+        <v>3375</v>
       </c>
       <c r="X85" s="84"/>
       <c r="Y85" s="84"/>
@@ -6813,12 +6795,12 @@
       <c r="T87" s="84"/>
       <c r="U87" s="84"/>
       <c r="V87" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
-        <v>3.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.5)</f>
+        <v>8.5</v>
       </c>
       <c r="W87" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),535.262)</f>
-        <v>535.262</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1299.922)</f>
+        <v>1299.922</v>
       </c>
       <c r="X87" s="84"/>
       <c r="Y87" s="84"/>
@@ -6939,12 +6921,12 @@
       <c r="T89" s="84"/>
       <c r="U89" s="84"/>
       <c r="V89" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
-        <v>4.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),42.5)</f>
+        <v>42.5</v>
       </c>
       <c r="W89" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),765.0)</f>
-        <v>765</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7225.0)</f>
+        <v>7225</v>
       </c>
       <c r="X89" s="84"/>
       <c r="Y89" s="84"/>
@@ -6999,12 +6981,12 @@
       <c r="T90" s="84"/>
       <c r="U90" s="84"/>
       <c r="V90" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14.0)</f>
-        <v>14</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),75.0)</f>
+        <v>75</v>
       </c>
       <c r="W90" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2240.0)</f>
-        <v>2240</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12000.0)</f>
+        <v>12000</v>
       </c>
       <c r="X90" s="84"/>
       <c r="Y90" s="84"/>
@@ -7164,12 +7146,12 @@
       <c r="T93" s="84"/>
       <c r="U93" s="84"/>
       <c r="V93" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14.0)</f>
-        <v>14</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),78.5)</f>
+        <v>78.5</v>
       </c>
       <c r="W93" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2314.312)</f>
-        <v>2314.312</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12976.678)</f>
+        <v>12976.678</v>
       </c>
       <c r="X93" s="84"/>
       <c r="Y93" s="84"/>
@@ -7227,12 +7209,12 @@
       <c r="T94" s="84"/>
       <c r="U94" s="84"/>
       <c r="V94" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.0)</f>
-        <v>35</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),112.0)</f>
+        <v>112</v>
       </c>
       <c r="W94" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5785.78)</f>
-        <v>5785.78</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17942.896)</f>
+        <v>17942.896</v>
       </c>
       <c r="X94" s="84"/>
       <c r="Y94" s="84"/>
@@ -7344,8 +7326,8 @@
       <c r="T96" s="84"/>
       <c r="U96" s="84"/>
       <c r="V96" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.0)</f>
-        <v>20</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),65.0)</f>
+        <v>65</v>
       </c>
       <c r="W96" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),44995.2)</f>
@@ -7401,12 +7383,12 @@
       <c r="T97" s="84"/>
       <c r="U97" s="84"/>
       <c r="V97" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.75)</f>
+        <v>31.75</v>
       </c>
       <c r="W97" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5248.529)</f>
+        <v>5248.529</v>
       </c>
       <c r="X97" s="84"/>
       <c r="Y97" s="84"/>
@@ -7467,12 +7449,12 @@
       <c r="T98" s="84"/>
       <c r="U98" s="84"/>
       <c r="V98" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6.0)</f>
-        <v>6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.0)</f>
+        <v>12</v>
       </c>
       <c r="W98" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),848.64)</f>
-        <v>848.64</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1697.28)</f>
+        <v>1697.28</v>
       </c>
       <c r="X98" s="84"/>
       <c r="Y98" s="84"/>
@@ -7857,12 +7839,12 @@
       <c r="T105" s="84"/>
       <c r="U105" s="84"/>
       <c r="V105" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
-        <v>5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),33.5)</f>
+        <v>33.5</v>
       </c>
       <c r="W105" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),764.66)</f>
-        <v>764.66</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5123.222)</f>
+        <v>5123.222</v>
       </c>
       <c r="X105" s="84"/>
       <c r="Y105" s="84"/>
@@ -7965,12 +7947,12 @@
       <c r="T107" s="84"/>
       <c r="U107" s="84"/>
       <c r="V107" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),74.5)</f>
+        <v>74.5</v>
       </c>
       <c r="W107" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10430.0)</f>
+        <v>10430</v>
       </c>
       <c r="X107" s="84"/>
       <c r="Y107" s="84"/>
@@ -8025,12 +8007,12 @@
       <c r="T108" s="84"/>
       <c r="U108" s="84"/>
       <c r="V108" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),48.0)</f>
-        <v>48</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),113.5)</f>
+        <v>113.5</v>
       </c>
       <c r="W108" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7934.784)</f>
-        <v>7934.784</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18148.783)</f>
+        <v>18148.783</v>
       </c>
       <c r="X108" s="84"/>
       <c r="Y108" s="84"/>
@@ -8253,12 +8235,12 @@
       <c r="T112" s="84"/>
       <c r="U112" s="84"/>
       <c r="V112" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19.0)</f>
-        <v>19</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29.0)</f>
+        <v>29</v>
       </c>
       <c r="W112" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2687.36)</f>
-        <v>2687.36</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4101.76)</f>
+        <v>4101.76</v>
       </c>
       <c r="X112" s="84"/>
       <c r="Y112" s="84"/>
@@ -8310,12 +8292,12 @@
       <c r="T113" s="84"/>
       <c r="U113" s="84"/>
       <c r="V113" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.0)</f>
+        <v>7</v>
       </c>
       <c r="W113" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),990.08)</f>
+        <v>990.08</v>
       </c>
       <c r="X113" s="84"/>
       <c r="Y113" s="84"/>
@@ -8427,12 +8409,12 @@
       <c r="T115" s="84"/>
       <c r="U115" s="84"/>
       <c r="V115" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),13.0)</f>
+        <v>13</v>
       </c>
       <c r="W115" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2149.004)</f>
+        <v>2149.004</v>
       </c>
       <c r="X115" s="84"/>
       <c r="Y115" s="84"/>
@@ -8541,12 +8523,12 @@
       <c r="T117" s="84"/>
       <c r="U117" s="84"/>
       <c r="V117" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23.0)</f>
-        <v>23</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27.0)</f>
+        <v>27</v>
       </c>
       <c r="W117" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3802.084)</f>
-        <v>3802.084</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4463.316)</f>
+        <v>4463.316</v>
       </c>
       <c r="X117" s="84"/>
       <c r="Y117" s="84"/>
@@ -8649,12 +8631,12 @@
       <c r="T119" s="84"/>
       <c r="U119" s="84"/>
       <c r="V119" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),33.0)</f>
-        <v>33</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),57.5)</f>
+        <v>57.5</v>
       </c>
       <c r="W119" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4667.52)</f>
-        <v>4667.52</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8132.8)</f>
+        <v>8132.8</v>
       </c>
       <c r="X119" s="84"/>
       <c r="Y119" s="84"/>
@@ -8976,12 +8958,12 @@
       <c r="T125" s="84"/>
       <c r="U125" s="84"/>
       <c r="V125" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.0)</f>
-        <v>12</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),24.0)</f>
+        <v>24</v>
       </c>
       <c r="W125" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1835.184)</f>
-        <v>1835.184</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3967.392)</f>
+        <v>3967.392</v>
       </c>
       <c r="X125" s="84"/>
       <c r="Y125" s="84"/>
@@ -9033,12 +9015,12 @@
       <c r="T126" s="84"/>
       <c r="U126" s="84"/>
       <c r="V126" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14.0)</f>
-        <v>14</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49.5)</f>
+        <v>49.5</v>
       </c>
       <c r="W126" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2141.048)</f>
-        <v>2141.048</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7570.134)</f>
+        <v>7570.134</v>
       </c>
       <c r="X126" s="84"/>
       <c r="Y126" s="84"/>
@@ -9090,12 +9072,12 @@
       <c r="T127" s="84"/>
       <c r="U127" s="84"/>
       <c r="V127" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.0)</f>
-        <v>12</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),63.0)</f>
+        <v>63</v>
       </c>
       <c r="W127" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2040.0)</f>
-        <v>2040</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10710.0)</f>
+        <v>10710</v>
       </c>
       <c r="X127" s="84"/>
       <c r="Y127" s="84"/>
@@ -9130,7 +9112,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
         <v>Libuš</v>
       </c>
-      <c r="F128" s="84"/>
+      <c r="F128" s="84" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Malešice")</f>
+        <v>Malešice</v>
+      </c>
       <c r="G128" s="84"/>
       <c r="H128" s="84"/>
       <c r="I128" s="84"/>
@@ -9147,12 +9132,12 @@
       <c r="T128" s="84"/>
       <c r="U128" s="84"/>
       <c r="V128" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14.0)</f>
-        <v>14</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),43.5)</f>
+        <v>43.5</v>
       </c>
       <c r="W128" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2141.048)</f>
-        <v>2141.048</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6652.5419999999995)</f>
+        <v>6652.542</v>
       </c>
       <c r="X128" s="84"/>
       <c r="Y128" s="84"/>
@@ -9204,12 +9189,12 @@
       <c r="T129" s="84"/>
       <c r="U129" s="84"/>
       <c r="V129" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6.0)</f>
-        <v>6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50.5)</f>
+        <v>50.5</v>
       </c>
       <c r="W129" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1200.0)</f>
-        <v>1200</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10100.0)</f>
+        <v>10100</v>
       </c>
       <c r="X129" s="84"/>
       <c r="Y129" s="84"/>
@@ -9236,8 +9221,14 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D130" s="84"/>
-      <c r="E130" s="84"/>
+      <c r="D130" s="84" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Kumar Jatinder")</f>
+        <v>Kumar Jatinder</v>
+      </c>
+      <c r="E130" s="84" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
+        <v>Libuš</v>
+      </c>
       <c r="F130" s="84"/>
       <c r="G130" s="84"/>
       <c r="H130" s="84"/>
@@ -9287,8 +9278,14 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D131" s="84"/>
-      <c r="E131" s="84"/>
+      <c r="D131" s="84" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Stehlíková Magdaléna")</f>
+        <v>Stehlíková Magdaléna</v>
+      </c>
+      <c r="E131" s="84" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bolevec")</f>
+        <v>Bolevec</v>
+      </c>
       <c r="F131" s="84"/>
       <c r="G131" s="84"/>
       <c r="H131" s="84"/>
@@ -9305,10 +9302,13 @@
       <c r="S131" s="84"/>
       <c r="T131" s="84"/>
       <c r="U131" s="84"/>
-      <c r="V131" s="84"/>
+      <c r="V131" s="90">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.0)</f>
+        <v>12</v>
+      </c>
       <c r="W131" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1697.28)</f>
+        <v>1697.28</v>
       </c>
       <c r="X131" s="84"/>
       <c r="Y131" s="84"/>
@@ -9335,8 +9335,14 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D132" s="84"/>
-      <c r="E132" s="84"/>
+      <c r="D132" s="84" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Dragoun Alfréd")</f>
+        <v>Dragoun Alfréd</v>
+      </c>
+      <c r="E132" s="84" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Zličín")</f>
+        <v>Zličín</v>
+      </c>
       <c r="F132" s="84"/>
       <c r="G132" s="84"/>
       <c r="H132" s="84"/>
@@ -9353,10 +9359,13 @@
       <c r="S132" s="84"/>
       <c r="T132" s="84"/>
       <c r="U132" s="84"/>
-      <c r="V132" s="84"/>
+      <c r="V132" s="90">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="W132" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),826.54)</f>
+        <v>826.54</v>
       </c>
       <c r="X132" s="84"/>
       <c r="Y132" s="84"/>
@@ -12549,12 +12558,12 @@
       <c r="T196" s="84"/>
       <c r="U196" s="84"/>
       <c r="V196" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),381.0)</f>
-        <v>381</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1369.0)</f>
+        <v>1369</v>
       </c>
       <c r="W196" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),132729.862)</f>
-        <v>132729.862</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),283819.30399999995)</f>
+        <v>283819.304</v>
       </c>
       <c r="X196" s="84"/>
       <c r="Y196" s="84"/>
@@ -43944,7 +43953,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="94" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C1" s="94" t="s">
         <v>4</v>
@@ -43956,16 +43965,16 @@
         <v>8</v>
       </c>
       <c r="F1" s="94" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G1" s="94" t="s">
         <v>10</v>
       </c>
       <c r="H1" s="94" t="s">
+        <v>28</v>
+      </c>
+      <c r="I1" s="94" t="s">
         <v>29</v>
-      </c>
-      <c r="I1" s="94" t="s">
-        <v>30</v>
       </c>
       <c r="J1" s="94" t="s">
         <v>15</v>
@@ -43979,22 +43988,22 @@
         <v>45528.0</v>
       </c>
       <c r="B2" s="94" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" s="94" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="94" t="s">
+      <c r="D2" s="96" t="s">
         <v>32</v>
       </c>
-      <c r="D2" s="96" t="s">
+      <c r="E2" s="96" t="s">
         <v>33</v>
       </c>
-      <c r="E2" s="96" t="s">
+      <c r="F2" s="96" t="s">
         <v>34</v>
       </c>
-      <c r="F2" s="96" t="s">
+      <c r="G2" s="96" t="s">
         <v>35</v>
-      </c>
-      <c r="G2" s="96" t="s">
-        <v>36</v>
       </c>
       <c r="H2" s="97">
         <v>3728.0</v>
@@ -44005,22 +44014,22 @@
         <v>45528.0</v>
       </c>
       <c r="B3" s="94" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C3" s="94" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D3" s="96" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" s="96" t="s">
         <v>37</v>
       </c>
-      <c r="E3" s="96" t="s">
-        <v>38</v>
-      </c>
       <c r="F3" s="96" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3" s="96" t="s">
         <v>35</v>
-      </c>
-      <c r="G3" s="96" t="s">
-        <v>36</v>
       </c>
       <c r="H3" s="97">
         <v>3728.0</v>
@@ -44031,19 +44040,19 @@
         <v>45528.0</v>
       </c>
       <c r="B4" s="94" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C4" s="94" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D4" s="96" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E4" s="96" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G4" s="96" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H4" s="97">
         <v>3728.0</v>
@@ -44054,7 +44063,7 @@
         <v>45528.0</v>
       </c>
       <c r="B5" s="94" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I5" s="97">
         <v>12.0</v>
@@ -44071,22 +44080,22 @@
         <v>45526.0</v>
       </c>
       <c r="B6" s="94" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C6" s="94" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="96" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="96" t="s">
+      <c r="E6" s="96" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="96" t="s">
+      <c r="F6" s="96" t="s">
         <v>34</v>
       </c>
-      <c r="F6" s="96" t="s">
+      <c r="G6" s="96" t="s">
         <v>35</v>
-      </c>
-      <c r="G6" s="96" t="s">
-        <v>36</v>
       </c>
       <c r="H6" s="97">
         <v>3728.0</v>
@@ -44097,22 +44106,22 @@
         <v>45526.0</v>
       </c>
       <c r="B7" s="94" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C7" s="94" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D7" s="96" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" s="96" t="s">
         <v>37</v>
       </c>
-      <c r="E7" s="96" t="s">
-        <v>38</v>
-      </c>
       <c r="F7" s="96" t="s">
+        <v>34</v>
+      </c>
+      <c r="G7" s="96" t="s">
         <v>35</v>
-      </c>
-      <c r="G7" s="96" t="s">
-        <v>36</v>
       </c>
       <c r="H7" s="97">
         <v>3728.0</v>
@@ -44123,19 +44132,19 @@
         <v>45526.0</v>
       </c>
       <c r="B8" s="94" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C8" s="94" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D8" s="96" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E8" s="96" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G8" s="96" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H8" s="97">
         <v>3728.0</v>
@@ -44146,7 +44155,7 @@
         <v>45526.0</v>
       </c>
       <c r="B9" s="94" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I9" s="97">
         <v>12.0</v>
@@ -44163,22 +44172,22 @@
         <v>45526.0</v>
       </c>
       <c r="B10" s="94" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C10" s="94" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" s="96" t="s">
         <v>32</v>
       </c>
-      <c r="D10" s="96" t="s">
+      <c r="E10" s="96" t="s">
         <v>33</v>
       </c>
-      <c r="E10" s="96" t="s">
+      <c r="F10" s="96" t="s">
         <v>34</v>
       </c>
-      <c r="F10" s="96" t="s">
+      <c r="G10" s="96" t="s">
         <v>35</v>
-      </c>
-      <c r="G10" s="96" t="s">
-        <v>36</v>
       </c>
       <c r="H10" s="97">
         <v>3728.0</v>
@@ -44189,22 +44198,22 @@
         <v>45526.0</v>
       </c>
       <c r="B11" s="94" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C11" s="94" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D11" s="96" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11" s="96" t="s">
         <v>37</v>
       </c>
-      <c r="E11" s="96" t="s">
-        <v>38</v>
-      </c>
       <c r="F11" s="96" t="s">
+        <v>34</v>
+      </c>
+      <c r="G11" s="96" t="s">
         <v>35</v>
-      </c>
-      <c r="G11" s="96" t="s">
-        <v>36</v>
       </c>
       <c r="H11" s="97">
         <v>3728.0</v>
@@ -44215,19 +44224,19 @@
         <v>45526.0</v>
       </c>
       <c r="B12" s="94" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C12" s="94" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D12" s="96" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E12" s="96" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G12" s="96" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H12" s="97">
         <v>3728.0</v>
@@ -44238,7 +44247,7 @@
         <v>45526.0</v>
       </c>
       <c r="B13" s="94" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I13" s="97">
         <v>12.0</v>
@@ -44255,7 +44264,7 @@
         <v>45532.0</v>
       </c>
       <c r="B14" s="94" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15">
@@ -44263,7 +44272,7 @@
         <v>45533.0</v>
       </c>
       <c r="B15" s="94" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16">
@@ -44271,7 +44280,7 @@
         <v>45534.0</v>
       </c>
       <c r="B16" s="94" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17">
@@ -44279,7 +44288,7 @@
         <v>45535.0</v>
       </c>
       <c r="B17" s="94" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -44313,7 +44322,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="98" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -44517,7 +44526,7 @@
       <c r="Y19" s="100"/>
       <c r="Z19" s="100"/>
       <c r="AA19" s="94" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AB19" s="94">
         <v>-11.0</v>
@@ -44842,7 +44851,7 @@
       <c r="Y30" s="100"/>
       <c r="Z30" s="100"/>
       <c r="AA30" s="94" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AB30" s="94">
         <v>-8.0</v>
@@ -44963,7 +44972,7 @@
       <c r="Y34" s="100"/>
       <c r="Z34" s="100"/>
       <c r="AA34" s="94" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AB34" s="94">
         <v>0.0</v>
@@ -45082,7 +45091,7 @@
       <c r="Y38" s="100"/>
       <c r="Z38" s="100"/>
       <c r="AA38" s="94" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AB38" s="94">
         <v>-12.0</v>
@@ -45116,7 +45125,7 @@
       <c r="Y39" s="100"/>
       <c r="Z39" s="100"/>
       <c r="AA39" s="94" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AB39" s="94">
         <v>0.0</v>
@@ -45208,7 +45217,7 @@
       <c r="Y42" s="100"/>
       <c r="Z42" s="100"/>
       <c r="AA42" s="94" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AB42" s="94">
         <v>6.0</v>
@@ -45387,7 +45396,7 @@
       <c r="Y48" s="100"/>
       <c r="Z48" s="100"/>
       <c r="AA48" s="94" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AB48" s="94">
         <v>-13.0</v>
@@ -45508,7 +45517,7 @@
       <c r="Y52" s="100"/>
       <c r="Z52" s="100"/>
       <c r="AA52" s="94" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AB52" s="94">
         <v>5.0</v>
@@ -45716,7 +45725,7 @@
       <c r="Y59" s="100"/>
       <c r="Z59" s="100"/>
       <c r="AA59" s="94" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AB59" s="94">
         <v>-9.0</v>
@@ -45837,7 +45846,7 @@
       <c r="Y63" s="100"/>
       <c r="Z63" s="100"/>
       <c r="AA63" s="94" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AB63" s="94">
         <v>-19.0</v>
@@ -46045,7 +46054,7 @@
       <c r="Y70" s="100"/>
       <c r="Z70" s="100"/>
       <c r="AA70" s="94" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="AB70" s="94">
         <v>-14.0</v>
@@ -46514,7 +46523,7 @@
       <c r="Y86" s="100"/>
       <c r="Z86" s="100"/>
       <c r="AA86" s="94" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AB86" s="94">
         <v>-21.0</v>
@@ -46548,7 +46557,7 @@
       <c r="Y87" s="100"/>
       <c r="Z87" s="100"/>
       <c r="AA87" s="94" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="AB87" s="94">
         <v>-7.0</v>
@@ -46582,7 +46591,7 @@
       <c r="Y88" s="100"/>
       <c r="Z88" s="100"/>
       <c r="AA88" s="94" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AB88" s="94">
         <v>-10.0</v>
@@ -46616,7 +46625,7 @@
       <c r="Y89" s="100"/>
       <c r="Z89" s="100"/>
       <c r="AA89" s="94" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AB89" s="94">
         <v>-6.0</v>
@@ -46709,7 +46718,7 @@
       <c r="Y92" s="100"/>
       <c r="Z92" s="100"/>
       <c r="AA92" s="94" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="AB92" s="94">
         <v>-17.0</v>
@@ -46975,7 +46984,7 @@
       <c r="Y101" s="100"/>
       <c r="Z101" s="100"/>
       <c r="AA101" s="94" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AB101" s="94">
         <v>-6.0</v>
@@ -47009,7 +47018,7 @@
       <c r="Y102" s="100"/>
       <c r="Z102" s="100"/>
       <c r="AA102" s="94" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AB102" s="94">
         <v>1.0</v>
@@ -47101,7 +47110,7 @@
       <c r="Y105" s="100"/>
       <c r="Z105" s="100"/>
       <c r="AA105" s="94" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AB105" s="94">
         <v>-2.0</v>
@@ -47164,7 +47173,7 @@
       <c r="Y107" s="100"/>
       <c r="Z107" s="100"/>
       <c r="AA107" s="94" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AB107" s="94">
         <v>-12.0</v>
@@ -47256,7 +47265,7 @@
       <c r="Y110" s="100"/>
       <c r="Z110" s="100"/>
       <c r="AA110" s="94" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AB110" s="94">
         <v>-14.0</v>
@@ -47290,7 +47299,7 @@
       <c r="Y111" s="100"/>
       <c r="Z111" s="100"/>
       <c r="AA111" s="94" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AB111" s="94">
         <v>-6.0</v>
@@ -47324,7 +47333,7 @@
       <c r="Y112" s="100"/>
       <c r="Z112" s="100"/>
       <c r="AA112" s="94" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AB112" s="94">
         <v>-11.0</v>
@@ -47387,7 +47396,7 @@
       <c r="Y114" s="100"/>
       <c r="Z114" s="100"/>
       <c r="AA114" s="94" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AB114" s="94">
         <v>-1.0</v>
@@ -47479,7 +47488,7 @@
       <c r="Y117" s="100"/>
       <c r="Z117" s="100"/>
       <c r="AA117" s="94" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AB117" s="94">
         <v>12.0</v>
@@ -47542,7 +47551,7 @@
       <c r="Y119" s="100"/>
       <c r="Z119" s="100"/>
       <c r="AA119" s="94" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AB119" s="94">
         <v>-17.0</v>
@@ -47663,7 +47672,7 @@
       <c r="Y123" s="100"/>
       <c r="Z123" s="100"/>
       <c r="AA123" s="94" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AB123" s="94">
         <v>-15.0</v>
@@ -47814,7 +47823,7 @@
       <c r="Y128" s="100"/>
       <c r="Z128" s="100"/>
       <c r="AA128" s="94" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AB128" s="94">
         <v>-11.0</v>
@@ -48199,7 +48208,7 @@
       <c r="Y141" s="100"/>
       <c r="Z141" s="100"/>
       <c r="AA141" s="94" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AB141" s="94">
         <v>-10.0</v>

--- a/google_data/Pobočky/Výroba/Report Vyroba.xlsx
+++ b/google_data/Pobočky/Výroba/Report Vyroba.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="73">
   <si>
     <t>Výroba</t>
   </si>
@@ -60,16 +60,19 @@
     <t>06:00</t>
   </si>
   <si>
-    <t>14:00</t>
+    <t>12:30</t>
   </si>
   <si>
     <t>Suroviny</t>
   </si>
   <si>
-    <t>Kursheva Diana</t>
+    <t>Ahurieva Viktoriia</t>
   </si>
   <si>
     <t>Ostatní</t>
+  </si>
+  <si>
+    <t>Kursheva Diana</t>
   </si>
   <si>
     <t>Vyber datum    &lt;----------&gt;</t>
@@ -1396,7 +1399,7 @@
         <v>1</v>
       </c>
       <c r="D1" s="4">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="E1" s="5"/>
       <c r="F1" s="6" t="s">
@@ -1415,8 +1418,8 @@
       <c r="D2" s="13"/>
       <c r="E2" s="14"/>
       <c r="F2" s="15">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("SUM(A14:A20) + SUM(FILTER(HR!W5:W48, HR!A5:A48 &lt;&gt; """")) + J13 + J15"),40672.0)</f>
-        <v>40672</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("SUM(A14:A20) + SUM(FILTER(HR!W5:W48, HR!A5:A48 &lt;&gt; """")) + J13 + J15"),41235.75)</f>
+        <v>41235.75</v>
       </c>
       <c r="H2" s="16"/>
       <c r="K2" s="16"/>
@@ -1425,7 +1428,7 @@
       <c r="A3" s="17"/>
       <c r="B3" s="18" t="str">
         <f>CHOOSE(WEEKDAY(D1), "Neděle", "Pondělí", "Úterý", "Středa", "Čtvrtek", "Pátek", "Sobota")</f>
-        <v>Úterý</v>
+        <v>Čtvrtek</v>
       </c>
       <c r="C3" s="10"/>
       <c r="D3" s="10"/>
@@ -1578,7 +1581,7 @@
       <c r="F14" s="42" t="str">
         <f t="shared" ref="F14:F20" si="1">IF(OR(ISBLANK(B14), ISBLANK(D14), D14=0), "0:00", TEXT((IF(AND(TIMEVALUE(IF(ISBLANK(D14), "00:00", D14))&gt;=TIMEVALUE("00:00"), TIMEVALUE(IF(ISBLANK(D14), "00:00", D14))&lt;=TIMEVALUE("06:00")), TIMEVALUE(IF(ISBLANK(D14), "00:00", D14))+1, TIMEVALUE(IF(ISBLANK(D14), "00:00", D14))) - TIMEVALUE(IF(ISBLANK(C14), "00:00", C14)) - TIMEVALUE(IF(ISBLANK(E14), "00:00", E14))), "hh:mm"))
 </f>
-        <v>08:00</v>
+        <v>06:30</v>
       </c>
       <c r="G14" s="43" t="s">
         <v>15</v>
@@ -1591,7 +1594,7 @@
     <row r="15">
       <c r="A15" s="38">
         <f t="array" ref="A15">IF(ISBLANK(B15), 0, IF(ISNUMBER(MATCH(B15, HR!A:A, 0)), 0, IF(ISNUMBER(MATCH(B15, HR!B:B, 0)), INDEX(HR!V:V, MATCH(B15, HR!B:B, 0)) * (F15 * 24), 0)))</f>
-        <v>668</v>
+        <v>689</v>
       </c>
       <c r="B15" s="47" t="s">
         <v>16</v>
@@ -1605,7 +1608,7 @@
       <c r="E15" s="40"/>
       <c r="F15" s="42" t="str">
         <f t="shared" si="1"/>
-        <v>08:00</v>
+        <v>06:30</v>
       </c>
       <c r="G15" s="48" t="s">
         <v>17</v>
@@ -1618,15 +1621,21 @@
     <row r="16">
       <c r="A16" s="38">
         <f t="array" ref="A16">IF(ISBLANK(B16), 0, IF(ISNUMBER(MATCH(B16, HR!A:A, 0)), 0, IF(ISNUMBER(MATCH(B16, HR!B:B, 0)), INDEX(HR!V:V, MATCH(B16, HR!B:B, 0)) * (F16 * 24), 0)))</f>
-        <v>0</v>
-      </c>
-      <c r="B16" s="39"/>
-      <c r="C16" s="40"/>
-      <c r="D16" s="40"/>
+        <v>542.75</v>
+      </c>
+      <c r="B16" s="39" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="40" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" s="40" t="s">
+        <v>14</v>
+      </c>
       <c r="E16" s="52"/>
       <c r="F16" s="53" t="str">
         <f t="shared" si="1"/>
-        <v>0:00</v>
+        <v>06:30</v>
       </c>
       <c r="G16" s="54"/>
       <c r="K16" s="16"/>
@@ -1761,7 +1770,7 @@
         <v>46143.0</v>
       </c>
       <c r="D1" s="63" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E1" s="62">
         <v>46173.0</v>
@@ -1811,7 +1820,7 @@
     <row r="5">
       <c r="A5" s="68"/>
       <c r="B5" s="69" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C5" s="10"/>
       <c r="D5" s="10"/>
@@ -1884,7 +1893,7 @@
         <v>6</v>
       </c>
       <c r="C9" s="79" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D9" s="79" t="s">
         <v>10</v>
@@ -1906,7 +1915,7 @@
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="71"/>
       <c r="B11" s="80" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C11" s="81">
         <v>16.0</v>
@@ -1918,7 +1927,7 @@
     <row r="12" ht="18.75" customHeight="1">
       <c r="A12" s="71"/>
       <c r="B12" s="80" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C12" s="81">
         <v>18.0</v>
@@ -1930,7 +1939,7 @@
     <row r="13" ht="18.75" customHeight="1">
       <c r="A13" s="71"/>
       <c r="B13" s="80" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C13" s="81">
         <v>11.0</v>
@@ -1942,7 +1951,7 @@
     <row r="14" ht="18.75" customHeight="1">
       <c r="A14" s="71"/>
       <c r="B14" s="80" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C14" s="81">
         <v>1.0</v>
@@ -2156,10 +2165,10 @@
     </row>
     <row r="4">
       <c r="A4" s="88" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B4" s="88" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C4" s="84" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Manažer")</f>
@@ -43953,7 +43962,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="94" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C1" s="94" t="s">
         <v>4</v>
@@ -43965,16 +43974,16 @@
         <v>8</v>
       </c>
       <c r="F1" s="94" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G1" s="94" t="s">
         <v>10</v>
       </c>
       <c r="H1" s="94" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I1" s="94" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J1" s="94" t="s">
         <v>15</v>
@@ -43988,22 +43997,22 @@
         <v>45528.0</v>
       </c>
       <c r="B2" s="94" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" s="94" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D2" s="96" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E2" s="96" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F2" s="96" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G2" s="96" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H2" s="97">
         <v>3728.0</v>
@@ -44014,22 +44023,22 @@
         <v>45528.0</v>
       </c>
       <c r="B3" s="94" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C3" s="94" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D3" s="96" t="s">
+        <v>37</v>
+      </c>
+      <c r="E3" s="96" t="s">
+        <v>38</v>
+      </c>
+      <c r="F3" s="96" t="s">
+        <v>35</v>
+      </c>
+      <c r="G3" s="96" t="s">
         <v>36</v>
-      </c>
-      <c r="E3" s="96" t="s">
-        <v>37</v>
-      </c>
-      <c r="F3" s="96" t="s">
-        <v>34</v>
-      </c>
-      <c r="G3" s="96" t="s">
-        <v>35</v>
       </c>
       <c r="H3" s="97">
         <v>3728.0</v>
@@ -44040,19 +44049,19 @@
         <v>45528.0</v>
       </c>
       <c r="B4" s="94" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C4" s="94" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D4" s="96" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E4" s="96" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G4" s="96" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H4" s="97">
         <v>3728.0</v>
@@ -44063,7 +44072,7 @@
         <v>45528.0</v>
       </c>
       <c r="B5" s="94" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I5" s="97">
         <v>12.0</v>
@@ -44080,22 +44089,22 @@
         <v>45526.0</v>
       </c>
       <c r="B6" s="94" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C6" s="94" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D6" s="96" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E6" s="96" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F6" s="96" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G6" s="96" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H6" s="97">
         <v>3728.0</v>
@@ -44106,22 +44115,22 @@
         <v>45526.0</v>
       </c>
       <c r="B7" s="94" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C7" s="94" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D7" s="96" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" s="96" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" s="96" t="s">
+        <v>35</v>
+      </c>
+      <c r="G7" s="96" t="s">
         <v>36</v>
-      </c>
-      <c r="E7" s="96" t="s">
-        <v>37</v>
-      </c>
-      <c r="F7" s="96" t="s">
-        <v>34</v>
-      </c>
-      <c r="G7" s="96" t="s">
-        <v>35</v>
       </c>
       <c r="H7" s="97">
         <v>3728.0</v>
@@ -44132,19 +44141,19 @@
         <v>45526.0</v>
       </c>
       <c r="B8" s="94" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" s="94" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="96" t="s">
         <v>39</v>
       </c>
-      <c r="C8" s="94" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" s="96" t="s">
-        <v>38</v>
-      </c>
       <c r="E8" s="96" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G8" s="96" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H8" s="97">
         <v>3728.0</v>
@@ -44155,7 +44164,7 @@
         <v>45526.0</v>
       </c>
       <c r="B9" s="94" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I9" s="97">
         <v>12.0</v>
@@ -44172,22 +44181,22 @@
         <v>45526.0</v>
       </c>
       <c r="B10" s="94" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C10" s="94" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D10" s="96" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E10" s="96" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F10" s="96" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G10" s="96" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H10" s="97">
         <v>3728.0</v>
@@ -44198,22 +44207,22 @@
         <v>45526.0</v>
       </c>
       <c r="B11" s="94" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C11" s="94" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D11" s="96" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" s="96" t="s">
+        <v>38</v>
+      </c>
+      <c r="F11" s="96" t="s">
+        <v>35</v>
+      </c>
+      <c r="G11" s="96" t="s">
         <v>36</v>
-      </c>
-      <c r="E11" s="96" t="s">
-        <v>37</v>
-      </c>
-      <c r="F11" s="96" t="s">
-        <v>34</v>
-      </c>
-      <c r="G11" s="96" t="s">
-        <v>35</v>
       </c>
       <c r="H11" s="97">
         <v>3728.0</v>
@@ -44224,19 +44233,19 @@
         <v>45526.0</v>
       </c>
       <c r="B12" s="94" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" s="94" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" s="96" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="94" t="s">
-        <v>22</v>
-      </c>
-      <c r="D12" s="96" t="s">
-        <v>38</v>
-      </c>
       <c r="E12" s="96" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G12" s="96" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H12" s="97">
         <v>3728.0</v>
@@ -44247,7 +44256,7 @@
         <v>45526.0</v>
       </c>
       <c r="B13" s="94" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I13" s="97">
         <v>12.0</v>
@@ -44264,7 +44273,7 @@
         <v>45532.0</v>
       </c>
       <c r="B14" s="94" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15">
@@ -44272,7 +44281,7 @@
         <v>45533.0</v>
       </c>
       <c r="B15" s="94" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16">
@@ -44280,7 +44289,7 @@
         <v>45534.0</v>
       </c>
       <c r="B16" s="94" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17">
@@ -44288,7 +44297,7 @@
         <v>45535.0</v>
       </c>
       <c r="B17" s="94" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -44322,7 +44331,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="98" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -44526,7 +44535,7 @@
       <c r="Y19" s="100"/>
       <c r="Z19" s="100"/>
       <c r="AA19" s="94" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AB19" s="94">
         <v>-11.0</v>
@@ -44851,7 +44860,7 @@
       <c r="Y30" s="100"/>
       <c r="Z30" s="100"/>
       <c r="AA30" s="94" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AB30" s="94">
         <v>-8.0</v>
@@ -44972,7 +44981,7 @@
       <c r="Y34" s="100"/>
       <c r="Z34" s="100"/>
       <c r="AA34" s="94" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AB34" s="94">
         <v>0.0</v>
@@ -45091,7 +45100,7 @@
       <c r="Y38" s="100"/>
       <c r="Z38" s="100"/>
       <c r="AA38" s="94" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AB38" s="94">
         <v>-12.0</v>
@@ -45125,7 +45134,7 @@
       <c r="Y39" s="100"/>
       <c r="Z39" s="100"/>
       <c r="AA39" s="94" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AB39" s="94">
         <v>0.0</v>
@@ -45217,7 +45226,7 @@
       <c r="Y42" s="100"/>
       <c r="Z42" s="100"/>
       <c r="AA42" s="94" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AB42" s="94">
         <v>6.0</v>
@@ -45396,7 +45405,7 @@
       <c r="Y48" s="100"/>
       <c r="Z48" s="100"/>
       <c r="AA48" s="94" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AB48" s="94">
         <v>-13.0</v>
@@ -45517,7 +45526,7 @@
       <c r="Y52" s="100"/>
       <c r="Z52" s="100"/>
       <c r="AA52" s="94" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AB52" s="94">
         <v>5.0</v>
@@ -45725,7 +45734,7 @@
       <c r="Y59" s="100"/>
       <c r="Z59" s="100"/>
       <c r="AA59" s="94" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AB59" s="94">
         <v>-9.0</v>
@@ -45846,7 +45855,7 @@
       <c r="Y63" s="100"/>
       <c r="Z63" s="100"/>
       <c r="AA63" s="94" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AB63" s="94">
         <v>-19.0</v>
@@ -46054,7 +46063,7 @@
       <c r="Y70" s="100"/>
       <c r="Z70" s="100"/>
       <c r="AA70" s="94" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AB70" s="94">
         <v>-14.0</v>
@@ -46523,7 +46532,7 @@
       <c r="Y86" s="100"/>
       <c r="Z86" s="100"/>
       <c r="AA86" s="94" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AB86" s="94">
         <v>-21.0</v>
@@ -46557,7 +46566,7 @@
       <c r="Y87" s="100"/>
       <c r="Z87" s="100"/>
       <c r="AA87" s="94" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AB87" s="94">
         <v>-7.0</v>
@@ -46591,7 +46600,7 @@
       <c r="Y88" s="100"/>
       <c r="Z88" s="100"/>
       <c r="AA88" s="94" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AB88" s="94">
         <v>-10.0</v>
@@ -46625,7 +46634,7 @@
       <c r="Y89" s="100"/>
       <c r="Z89" s="100"/>
       <c r="AA89" s="94" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AB89" s="94">
         <v>-6.0</v>
@@ -46718,7 +46727,7 @@
       <c r="Y92" s="100"/>
       <c r="Z92" s="100"/>
       <c r="AA92" s="94" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AB92" s="94">
         <v>-17.0</v>
@@ -46984,7 +46993,7 @@
       <c r="Y101" s="100"/>
       <c r="Z101" s="100"/>
       <c r="AA101" s="94" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AB101" s="94">
         <v>-6.0</v>
@@ -47018,7 +47027,7 @@
       <c r="Y102" s="100"/>
       <c r="Z102" s="100"/>
       <c r="AA102" s="94" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AB102" s="94">
         <v>1.0</v>
@@ -47110,7 +47119,7 @@
       <c r="Y105" s="100"/>
       <c r="Z105" s="100"/>
       <c r="AA105" s="94" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AB105" s="94">
         <v>-2.0</v>
@@ -47173,7 +47182,7 @@
       <c r="Y107" s="100"/>
       <c r="Z107" s="100"/>
       <c r="AA107" s="94" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AB107" s="94">
         <v>-12.0</v>
@@ -47265,7 +47274,7 @@
       <c r="Y110" s="100"/>
       <c r="Z110" s="100"/>
       <c r="AA110" s="94" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AB110" s="94">
         <v>-14.0</v>
@@ -47299,7 +47308,7 @@
       <c r="Y111" s="100"/>
       <c r="Z111" s="100"/>
       <c r="AA111" s="94" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AB111" s="94">
         <v>-6.0</v>
@@ -47333,7 +47342,7 @@
       <c r="Y112" s="100"/>
       <c r="Z112" s="100"/>
       <c r="AA112" s="94" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AB112" s="94">
         <v>-11.0</v>
@@ -47396,7 +47405,7 @@
       <c r="Y114" s="100"/>
       <c r="Z114" s="100"/>
       <c r="AA114" s="94" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AB114" s="94">
         <v>-1.0</v>
@@ -47488,7 +47497,7 @@
       <c r="Y117" s="100"/>
       <c r="Z117" s="100"/>
       <c r="AA117" s="94" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AB117" s="94">
         <v>12.0</v>
@@ -47551,7 +47560,7 @@
       <c r="Y119" s="100"/>
       <c r="Z119" s="100"/>
       <c r="AA119" s="94" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AB119" s="94">
         <v>-17.0</v>
@@ -47672,7 +47681,7 @@
       <c r="Y123" s="100"/>
       <c r="Z123" s="100"/>
       <c r="AA123" s="94" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AB123" s="94">
         <v>-15.0</v>
@@ -47823,7 +47832,7 @@
       <c r="Y128" s="100"/>
       <c r="Z128" s="100"/>
       <c r="AA128" s="94" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AB128" s="94">
         <v>-11.0</v>
@@ -48208,7 +48217,7 @@
       <c r="Y141" s="100"/>
       <c r="Z141" s="100"/>
       <c r="AA141" s="94" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AB141" s="94">
         <v>-10.0</v>

--- a/google_data/Pobočky/Výroba/Report Vyroba.xlsx
+++ b/google_data/Pobočky/Výroba/Report Vyroba.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="70">
   <si>
     <t>Výroba</t>
   </si>
@@ -54,25 +54,10 @@
     <t>Benzín / nafta</t>
   </si>
   <si>
-    <t>Paziak Viktoriia</t>
-  </si>
-  <si>
-    <t>06:00</t>
-  </si>
-  <si>
-    <t>12:30</t>
-  </si>
-  <si>
     <t>Suroviny</t>
   </si>
   <si>
-    <t>Ahurieva Viktoriia</t>
-  </si>
-  <si>
     <t>Ostatní</t>
-  </si>
-  <si>
-    <t>Kursheva Diana</t>
   </si>
   <si>
     <t>Vyber datum    &lt;----------&gt;</t>
@@ -84,7 +69,13 @@
     <t>Počet dní</t>
   </si>
   <si>
+    <t>Paziak Viktoriia</t>
+  </si>
+  <si>
     <t>Stepanenko Solomiia</t>
+  </si>
+  <si>
+    <t>Kursheva Diana</t>
   </si>
   <si>
     <t>Hřebík Martin</t>
@@ -1399,7 +1390,7 @@
         <v>1</v>
       </c>
       <c r="D1" s="4">
-        <v>46191.0</v>
+        <v>46194.0</v>
       </c>
       <c r="E1" s="5"/>
       <c r="F1" s="6" t="s">
@@ -1418,8 +1409,8 @@
       <c r="D2" s="13"/>
       <c r="E2" s="14"/>
       <c r="F2" s="15">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("SUM(A14:A20) + SUM(FILTER(HR!W5:W48, HR!A5:A48 &lt;&gt; """")) + J13 + J15"),41235.75)</f>
-        <v>41235.75</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("SUM(A14:A20) + SUM(FILTER(HR!W5:W48, HR!A5:A48 &lt;&gt; """")) + J13 + J15"),40004.0)</f>
+        <v>40004</v>
       </c>
       <c r="H2" s="16"/>
       <c r="K2" s="16"/>
@@ -1428,7 +1419,7 @@
       <c r="A3" s="17"/>
       <c r="B3" s="18" t="str">
         <f>CHOOSE(WEEKDAY(D1), "Neděle", "Pondělí", "Úterý", "Středa", "Čtvrtek", "Pátek", "Sobota")</f>
-        <v>Čtvrtek</v>
+        <v>Neděle</v>
       </c>
       <c r="C3" s="10"/>
       <c r="D3" s="10"/>
@@ -1568,23 +1559,17 @@
         <f t="array" ref="A14">IF(ISBLANK(B14), 0, IF(ISNUMBER(MATCH(B14, HR!A:A, 0)), 0, IF(ISNUMBER(MATCH(B14, HR!B:B, 0)), INDEX(HR!V:V, MATCH(B14, HR!B:B, 0)) * (F14 * 24), 0)))</f>
         <v>0</v>
       </c>
-      <c r="B14" s="39" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" s="40" t="s">
-        <v>13</v>
-      </c>
-      <c r="D14" s="40" t="s">
-        <v>14</v>
-      </c>
+      <c r="B14" s="39"/>
+      <c r="C14" s="40"/>
+      <c r="D14" s="40"/>
       <c r="E14" s="41"/>
       <c r="F14" s="42" t="str">
         <f t="shared" ref="F14:F20" si="1">IF(OR(ISBLANK(B14), ISBLANK(D14), D14=0), "0:00", TEXT((IF(AND(TIMEVALUE(IF(ISBLANK(D14), "00:00", D14))&gt;=TIMEVALUE("00:00"), TIMEVALUE(IF(ISBLANK(D14), "00:00", D14))&lt;=TIMEVALUE("06:00")), TIMEVALUE(IF(ISBLANK(D14), "00:00", D14))+1, TIMEVALUE(IF(ISBLANK(D14), "00:00", D14))) - TIMEVALUE(IF(ISBLANK(C14), "00:00", C14)) - TIMEVALUE(IF(ISBLANK(E14), "00:00", E14))), "hh:mm"))
 </f>
-        <v>06:30</v>
+        <v>0:00</v>
       </c>
       <c r="G14" s="43" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H14" s="44"/>
       <c r="I14" s="45"/>
@@ -1594,24 +1579,18 @@
     <row r="15">
       <c r="A15" s="38">
         <f t="array" ref="A15">IF(ISBLANK(B15), 0, IF(ISNUMBER(MATCH(B15, HR!A:A, 0)), 0, IF(ISNUMBER(MATCH(B15, HR!B:B, 0)), INDEX(HR!V:V, MATCH(B15, HR!B:B, 0)) * (F15 * 24), 0)))</f>
-        <v>689</v>
-      </c>
-      <c r="B15" s="47" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" s="40" t="s">
-        <v>13</v>
-      </c>
-      <c r="D15" s="40" t="s">
-        <v>14</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="B15" s="47"/>
+      <c r="C15" s="40"/>
+      <c r="D15" s="40"/>
       <c r="E15" s="40"/>
       <c r="F15" s="42" t="str">
         <f t="shared" si="1"/>
-        <v>06:30</v>
+        <v>0:00</v>
       </c>
       <c r="G15" s="48" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H15" s="49"/>
       <c r="I15" s="50"/>
@@ -1621,21 +1600,15 @@
     <row r="16">
       <c r="A16" s="38">
         <f t="array" ref="A16">IF(ISBLANK(B16), 0, IF(ISNUMBER(MATCH(B16, HR!A:A, 0)), 0, IF(ISNUMBER(MATCH(B16, HR!B:B, 0)), INDEX(HR!V:V, MATCH(B16, HR!B:B, 0)) * (F16 * 24), 0)))</f>
-        <v>542.75</v>
-      </c>
-      <c r="B16" s="39" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" s="40" t="s">
-        <v>13</v>
-      </c>
-      <c r="D16" s="40" t="s">
-        <v>14</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="B16" s="39"/>
+      <c r="C16" s="40"/>
+      <c r="D16" s="40"/>
       <c r="E16" s="52"/>
       <c r="F16" s="53" t="str">
         <f t="shared" si="1"/>
-        <v>06:30</v>
+        <v>0:00</v>
       </c>
       <c r="G16" s="54"/>
       <c r="K16" s="16"/>
@@ -1770,7 +1743,7 @@
         <v>46143.0</v>
       </c>
       <c r="D1" s="63" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E1" s="62">
         <v>46173.0</v>
@@ -1820,7 +1793,7 @@
     <row r="5">
       <c r="A5" s="68"/>
       <c r="B5" s="69" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C5" s="10"/>
       <c r="D5" s="10"/>
@@ -1860,7 +1833,7 @@
       <c r="D7" s="19"/>
       <c r="E7" s="14"/>
       <c r="F7" s="74" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G7" s="44"/>
       <c r="H7" s="45"/>
@@ -1878,7 +1851,7 @@
       <c r="D8" s="8"/>
       <c r="E8" s="76"/>
       <c r="F8" s="77" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G8" s="49"/>
       <c r="H8" s="50"/>
@@ -1893,7 +1866,7 @@
         <v>6</v>
       </c>
       <c r="C9" s="79" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D9" s="79" t="s">
         <v>10</v>
@@ -1903,7 +1876,7 @@
     <row r="10" ht="18.75" customHeight="1">
       <c r="A10" s="71"/>
       <c r="B10" s="80" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C10" s="81">
         <v>15.0</v>
@@ -1915,7 +1888,7 @@
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="71"/>
       <c r="B11" s="80" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C11" s="81">
         <v>16.0</v>
@@ -1927,7 +1900,7 @@
     <row r="12" ht="18.75" customHeight="1">
       <c r="A12" s="71"/>
       <c r="B12" s="80" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" s="81">
         <v>18.0</v>
@@ -1939,7 +1912,7 @@
     <row r="13" ht="18.75" customHeight="1">
       <c r="A13" s="71"/>
       <c r="B13" s="80" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C13" s="81">
         <v>11.0</v>
@@ -1951,7 +1924,7 @@
     <row r="14" ht="18.75" customHeight="1">
       <c r="A14" s="71"/>
       <c r="B14" s="80" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C14" s="81">
         <v>1.0</v>
@@ -2165,10 +2138,10 @@
     </row>
     <row r="4">
       <c r="A4" s="88" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B4" s="88" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C4" s="84" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Manažer")</f>
@@ -2443,8 +2416,8 @@
         <v>Výroba</v>
       </c>
       <c r="H8" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Prosek")</f>
-        <v>Prosek</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Zličín")</f>
+        <v>Zličín</v>
       </c>
       <c r="I8" s="84"/>
       <c r="J8" s="84"/>
@@ -2882,8 +2855,8 @@
         <v>Malešice</v>
       </c>
       <c r="F15" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Zličín")</f>
-        <v>Zličín</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bolevec")</f>
+        <v>Bolevec</v>
       </c>
       <c r="G15" s="84"/>
       <c r="H15" s="84"/>
@@ -43962,7 +43935,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="94" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C1" s="94" t="s">
         <v>4</v>
@@ -43974,22 +43947,22 @@
         <v>8</v>
       </c>
       <c r="F1" s="94" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G1" s="94" t="s">
         <v>10</v>
       </c>
       <c r="H1" s="94" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="I1" s="94" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J1" s="94" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K1" s="94" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2">
@@ -43997,22 +43970,22 @@
         <v>45528.0</v>
       </c>
       <c r="B2" s="94" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="94" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" s="96" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" s="96" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="94" t="s">
+      <c r="F2" s="96" t="s">
         <v>32</v>
       </c>
-      <c r="D2" s="96" t="s">
+      <c r="G2" s="96" t="s">
         <v>33</v>
-      </c>
-      <c r="E2" s="96" t="s">
-        <v>34</v>
-      </c>
-      <c r="F2" s="96" t="s">
-        <v>35</v>
-      </c>
-      <c r="G2" s="96" t="s">
-        <v>36</v>
       </c>
       <c r="H2" s="97">
         <v>3728.0</v>
@@ -44023,22 +43996,22 @@
         <v>45528.0</v>
       </c>
       <c r="B3" s="94" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C3" s="94" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D3" s="96" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E3" s="96" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F3" s="96" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G3" s="96" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H3" s="97">
         <v>3728.0</v>
@@ -44049,19 +44022,19 @@
         <v>45528.0</v>
       </c>
       <c r="B4" s="94" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C4" s="94" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D4" s="96" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E4" s="96" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G4" s="96" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H4" s="97">
         <v>3728.0</v>
@@ -44072,7 +44045,7 @@
         <v>45528.0</v>
       </c>
       <c r="B5" s="94" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I5" s="97">
         <v>12.0</v>
@@ -44089,22 +44062,22 @@
         <v>45526.0</v>
       </c>
       <c r="B6" s="94" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C6" s="94" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="96" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="96" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" s="96" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="96" t="s">
+      <c r="G6" s="96" t="s">
         <v>33</v>
-      </c>
-      <c r="E6" s="96" t="s">
-        <v>34</v>
-      </c>
-      <c r="F6" s="96" t="s">
-        <v>35</v>
-      </c>
-      <c r="G6" s="96" t="s">
-        <v>36</v>
       </c>
       <c r="H6" s="97">
         <v>3728.0</v>
@@ -44115,22 +44088,22 @@
         <v>45526.0</v>
       </c>
       <c r="B7" s="94" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C7" s="94" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D7" s="96" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E7" s="96" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F7" s="96" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G7" s="96" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H7" s="97">
         <v>3728.0</v>
@@ -44141,19 +44114,19 @@
         <v>45526.0</v>
       </c>
       <c r="B8" s="94" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C8" s="94" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D8" s="96" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E8" s="96" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G8" s="96" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H8" s="97">
         <v>3728.0</v>
@@ -44164,7 +44137,7 @@
         <v>45526.0</v>
       </c>
       <c r="B9" s="94" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="I9" s="97">
         <v>12.0</v>
@@ -44181,22 +44154,22 @@
         <v>45526.0</v>
       </c>
       <c r="B10" s="94" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C10" s="94" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="96" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" s="96" t="s">
+        <v>31</v>
+      </c>
+      <c r="F10" s="96" t="s">
         <v>32</v>
       </c>
-      <c r="D10" s="96" t="s">
+      <c r="G10" s="96" t="s">
         <v>33</v>
-      </c>
-      <c r="E10" s="96" t="s">
-        <v>34</v>
-      </c>
-      <c r="F10" s="96" t="s">
-        <v>35</v>
-      </c>
-      <c r="G10" s="96" t="s">
-        <v>36</v>
       </c>
       <c r="H10" s="97">
         <v>3728.0</v>
@@ -44207,22 +44180,22 @@
         <v>45526.0</v>
       </c>
       <c r="B11" s="94" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C11" s="94" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D11" s="96" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E11" s="96" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F11" s="96" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G11" s="96" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H11" s="97">
         <v>3728.0</v>
@@ -44233,19 +44206,19 @@
         <v>45526.0</v>
       </c>
       <c r="B12" s="94" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C12" s="94" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D12" s="96" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E12" s="96" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G12" s="96" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H12" s="97">
         <v>3728.0</v>
@@ -44256,7 +44229,7 @@
         <v>45526.0</v>
       </c>
       <c r="B13" s="94" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="I13" s="97">
         <v>12.0</v>
@@ -44273,7 +44246,7 @@
         <v>45532.0</v>
       </c>
       <c r="B14" s="94" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15">
@@ -44281,7 +44254,7 @@
         <v>45533.0</v>
       </c>
       <c r="B15" s="94" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16">
@@ -44289,7 +44262,7 @@
         <v>45534.0</v>
       </c>
       <c r="B16" s="94" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17">
@@ -44297,7 +44270,7 @@
         <v>45535.0</v>
       </c>
       <c r="B17" s="94" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -44331,7 +44304,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="98" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -44535,7 +44508,7 @@
       <c r="Y19" s="100"/>
       <c r="Z19" s="100"/>
       <c r="AA19" s="94" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="AB19" s="94">
         <v>-11.0</v>
@@ -44860,7 +44833,7 @@
       <c r="Y30" s="100"/>
       <c r="Z30" s="100"/>
       <c r="AA30" s="94" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="AB30" s="94">
         <v>-8.0</v>
@@ -44981,7 +44954,7 @@
       <c r="Y34" s="100"/>
       <c r="Z34" s="100"/>
       <c r="AA34" s="94" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="AB34" s="94">
         <v>0.0</v>
@@ -45100,7 +45073,7 @@
       <c r="Y38" s="100"/>
       <c r="Z38" s="100"/>
       <c r="AA38" s="94" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AB38" s="94">
         <v>-12.0</v>
@@ -45134,7 +45107,7 @@
       <c r="Y39" s="100"/>
       <c r="Z39" s="100"/>
       <c r="AA39" s="94" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="AB39" s="94">
         <v>0.0</v>
@@ -45226,7 +45199,7 @@
       <c r="Y42" s="100"/>
       <c r="Z42" s="100"/>
       <c r="AA42" s="94" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="AB42" s="94">
         <v>6.0</v>
@@ -45405,7 +45378,7 @@
       <c r="Y48" s="100"/>
       <c r="Z48" s="100"/>
       <c r="AA48" s="94" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="AB48" s="94">
         <v>-13.0</v>
@@ -45526,7 +45499,7 @@
       <c r="Y52" s="100"/>
       <c r="Z52" s="100"/>
       <c r="AA52" s="94" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="AB52" s="94">
         <v>5.0</v>
@@ -45734,7 +45707,7 @@
       <c r="Y59" s="100"/>
       <c r="Z59" s="100"/>
       <c r="AA59" s="94" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="AB59" s="94">
         <v>-9.0</v>
@@ -45855,7 +45828,7 @@
       <c r="Y63" s="100"/>
       <c r="Z63" s="100"/>
       <c r="AA63" s="94" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="AB63" s="94">
         <v>-19.0</v>
@@ -46063,7 +46036,7 @@
       <c r="Y70" s="100"/>
       <c r="Z70" s="100"/>
       <c r="AA70" s="94" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="AB70" s="94">
         <v>-14.0</v>
@@ -46532,7 +46505,7 @@
       <c r="Y86" s="100"/>
       <c r="Z86" s="100"/>
       <c r="AA86" s="94" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="AB86" s="94">
         <v>-21.0</v>
@@ -46566,7 +46539,7 @@
       <c r="Y87" s="100"/>
       <c r="Z87" s="100"/>
       <c r="AA87" s="94" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="AB87" s="94">
         <v>-7.0</v>
@@ -46600,7 +46573,7 @@
       <c r="Y88" s="100"/>
       <c r="Z88" s="100"/>
       <c r="AA88" s="94" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="AB88" s="94">
         <v>-10.0</v>
@@ -46634,7 +46607,7 @@
       <c r="Y89" s="100"/>
       <c r="Z89" s="100"/>
       <c r="AA89" s="94" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="AB89" s="94">
         <v>-6.0</v>
@@ -46727,7 +46700,7 @@
       <c r="Y92" s="100"/>
       <c r="Z92" s="100"/>
       <c r="AA92" s="94" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="AB92" s="94">
         <v>-17.0</v>
@@ -46993,7 +46966,7 @@
       <c r="Y101" s="100"/>
       <c r="Z101" s="100"/>
       <c r="AA101" s="94" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="AB101" s="94">
         <v>-6.0</v>
@@ -47027,7 +47000,7 @@
       <c r="Y102" s="100"/>
       <c r="Z102" s="100"/>
       <c r="AA102" s="94" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="AB102" s="94">
         <v>1.0</v>
@@ -47119,7 +47092,7 @@
       <c r="Y105" s="100"/>
       <c r="Z105" s="100"/>
       <c r="AA105" s="94" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="AB105" s="94">
         <v>-2.0</v>
@@ -47182,7 +47155,7 @@
       <c r="Y107" s="100"/>
       <c r="Z107" s="100"/>
       <c r="AA107" s="94" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="AB107" s="94">
         <v>-12.0</v>
@@ -47274,7 +47247,7 @@
       <c r="Y110" s="100"/>
       <c r="Z110" s="100"/>
       <c r="AA110" s="94" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="AB110" s="94">
         <v>-14.0</v>
@@ -47308,7 +47281,7 @@
       <c r="Y111" s="100"/>
       <c r="Z111" s="100"/>
       <c r="AA111" s="94" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="AB111" s="94">
         <v>-6.0</v>
@@ -47342,7 +47315,7 @@
       <c r="Y112" s="100"/>
       <c r="Z112" s="100"/>
       <c r="AA112" s="94" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="AB112" s="94">
         <v>-11.0</v>
@@ -47405,7 +47378,7 @@
       <c r="Y114" s="100"/>
       <c r="Z114" s="100"/>
       <c r="AA114" s="94" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="AB114" s="94">
         <v>-1.0</v>
@@ -47497,7 +47470,7 @@
       <c r="Y117" s="100"/>
       <c r="Z117" s="100"/>
       <c r="AA117" s="94" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="AB117" s="94">
         <v>12.0</v>
@@ -47560,7 +47533,7 @@
       <c r="Y119" s="100"/>
       <c r="Z119" s="100"/>
       <c r="AA119" s="94" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="AB119" s="94">
         <v>-17.0</v>
@@ -47681,7 +47654,7 @@
       <c r="Y123" s="100"/>
       <c r="Z123" s="100"/>
       <c r="AA123" s="94" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="AB123" s="94">
         <v>-15.0</v>
@@ -47832,7 +47805,7 @@
       <c r="Y128" s="100"/>
       <c r="Z128" s="100"/>
       <c r="AA128" s="94" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AB128" s="94">
         <v>-11.0</v>
@@ -48217,7 +48190,7 @@
       <c r="Y141" s="100"/>
       <c r="Z141" s="100"/>
       <c r="AA141" s="94" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="AB141" s="94">
         <v>-10.0</v>

--- a/google_data/Pobočky/Výroba/Report Vyroba.xlsx
+++ b/google_data/Pobočky/Výroba/Report Vyroba.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="72">
   <si>
     <t>Výroba</t>
   </si>
@@ -54,10 +54,25 @@
     <t>Benzín / nafta</t>
   </si>
   <si>
+    <t>Koteliuk Maryna</t>
+  </si>
+  <si>
+    <t>06:00</t>
+  </si>
+  <si>
+    <t>14:00</t>
+  </si>
+  <si>
     <t>Suroviny</t>
   </si>
   <si>
+    <t>Kursheva Diana</t>
+  </si>
+  <si>
     <t>Ostatní</t>
+  </si>
+  <si>
+    <t>Paziak Viktoriia</t>
   </si>
   <si>
     <t>Vyber datum    &lt;----------&gt;</t>
@@ -69,19 +84,7 @@
     <t>Počet dní</t>
   </si>
   <si>
-    <t>Paziak Viktoriia</t>
-  </si>
-  <si>
-    <t>Stepanenko Solomiia</t>
-  </si>
-  <si>
-    <t>Kursheva Diana</t>
-  </si>
-  <si>
     <t>Hřebík Martin</t>
-  </si>
-  <si>
-    <t>Lažek Jaroslav</t>
   </si>
   <si>
     <t>Manažeři</t>
@@ -118,6 +121,9 @@
   </si>
   <si>
     <t>01:00</t>
+  </si>
+  <si>
+    <t>Stepanenko Solomiia</t>
   </si>
   <si>
     <t>10:00</t>
@@ -1390,7 +1396,7 @@
         <v>1</v>
       </c>
       <c r="D1" s="4">
-        <v>46194.0</v>
+        <v>46204.0</v>
       </c>
       <c r="E1" s="5"/>
       <c r="F1" s="6" t="s">
@@ -1419,7 +1425,7 @@
       <c r="A3" s="17"/>
       <c r="B3" s="18" t="str">
         <f>CHOOSE(WEEKDAY(D1), "Neděle", "Pondělí", "Úterý", "Středa", "Čtvrtek", "Pátek", "Sobota")</f>
-        <v>Neděle</v>
+        <v>Středa</v>
       </c>
       <c r="C3" s="10"/>
       <c r="D3" s="10"/>
@@ -1559,17 +1565,23 @@
         <f t="array" ref="A14">IF(ISBLANK(B14), 0, IF(ISNUMBER(MATCH(B14, HR!A:A, 0)), 0, IF(ISNUMBER(MATCH(B14, HR!B:B, 0)), INDEX(HR!V:V, MATCH(B14, HR!B:B, 0)) * (F14 * 24), 0)))</f>
         <v>0</v>
       </c>
-      <c r="B14" s="39"/>
-      <c r="C14" s="40"/>
-      <c r="D14" s="40"/>
+      <c r="B14" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="40" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="40" t="s">
+        <v>14</v>
+      </c>
       <c r="E14" s="41"/>
       <c r="F14" s="42" t="str">
         <f t="shared" ref="F14:F20" si="1">IF(OR(ISBLANK(B14), ISBLANK(D14), D14=0), "0:00", TEXT((IF(AND(TIMEVALUE(IF(ISBLANK(D14), "00:00", D14))&gt;=TIMEVALUE("00:00"), TIMEVALUE(IF(ISBLANK(D14), "00:00", D14))&lt;=TIMEVALUE("06:00")), TIMEVALUE(IF(ISBLANK(D14), "00:00", D14))+1, TIMEVALUE(IF(ISBLANK(D14), "00:00", D14))) - TIMEVALUE(IF(ISBLANK(C14), "00:00", C14)) - TIMEVALUE(IF(ISBLANK(E14), "00:00", E14))), "hh:mm"))
 </f>
-        <v>0:00</v>
+        <v>08:00</v>
       </c>
       <c r="G14" s="43" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H14" s="44"/>
       <c r="I14" s="45"/>
@@ -1581,16 +1593,22 @@
         <f t="array" ref="A15">IF(ISBLANK(B15), 0, IF(ISNUMBER(MATCH(B15, HR!A:A, 0)), 0, IF(ISNUMBER(MATCH(B15, HR!B:B, 0)), INDEX(HR!V:V, MATCH(B15, HR!B:B, 0)) * (F15 * 24), 0)))</f>
         <v>0</v>
       </c>
-      <c r="B15" s="47"/>
-      <c r="C15" s="40"/>
-      <c r="D15" s="40"/>
+      <c r="B15" s="47" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="40" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="40" t="s">
+        <v>14</v>
+      </c>
       <c r="E15" s="40"/>
       <c r="F15" s="42" t="str">
         <f t="shared" si="1"/>
-        <v>0:00</v>
+        <v>08:00</v>
       </c>
       <c r="G15" s="48" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H15" s="49"/>
       <c r="I15" s="50"/>
@@ -1602,13 +1620,19 @@
         <f t="array" ref="A16">IF(ISBLANK(B16), 0, IF(ISNUMBER(MATCH(B16, HR!A:A, 0)), 0, IF(ISNUMBER(MATCH(B16, HR!B:B, 0)), INDEX(HR!V:V, MATCH(B16, HR!B:B, 0)) * (F16 * 24), 0)))</f>
         <v>0</v>
       </c>
-      <c r="B16" s="39"/>
-      <c r="C16" s="40"/>
-      <c r="D16" s="40"/>
+      <c r="B16" s="39" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="40" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" s="40" t="s">
+        <v>14</v>
+      </c>
       <c r="E16" s="52"/>
       <c r="F16" s="53" t="str">
         <f t="shared" si="1"/>
-        <v>0:00</v>
+        <v>08:00</v>
       </c>
       <c r="G16" s="54"/>
       <c r="K16" s="16"/>
@@ -1710,7 +1734,7 @@
   </conditionalFormatting>
   <dataValidations>
     <dataValidation type="list" allowBlank="1" sqref="B14:B20">
-      <formula1>"Sova Martin,Paziak Viktoriia,Ahurieva Viktoriia,Kursheva Diana,Lažek Jaroslav,Chlubna Tomáš,Hřebík Martin"</formula1>
+      <formula1>"Sova Martin,Paziak Viktoriia,Ahurieva Viktoriia,Kursheva Diana,Koteliuk Maryna,Lažek Jaroslav,Chlubna Tomáš,Hřebík Martin"</formula1>
     </dataValidation>
   </dataValidations>
   <drawing r:id="rId1"/>
@@ -1740,13 +1764,13 @@
         <v>Výroba</v>
       </c>
       <c r="C1" s="62">
-        <v>46143.0</v>
+        <v>46203.0</v>
       </c>
       <c r="D1" s="63" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E1" s="62">
-        <v>46173.0</v>
+        <v>46203.0</v>
       </c>
       <c r="F1" s="6" t="s">
         <v>2</v>
@@ -1762,7 +1786,7 @@
       <c r="D2" s="12"/>
       <c r="E2" s="13"/>
       <c r="F2" s="65">
-        <v>1224796.0</v>
+        <v>43210.0</v>
       </c>
       <c r="H2" s="16"/>
     </row>
@@ -1770,12 +1794,12 @@
       <c r="A3" s="66"/>
       <c r="B3" s="67" t="str">
         <f>CHOOSE(WEEKDAY(C1), "Neděle", "Pondělí", "Úterý", "Středa", "Čtvrtek", "Pátek", "Sobota")</f>
-        <v>Pátek</v>
+        <v>Úterý</v>
       </c>
       <c r="C3" s="10"/>
       <c r="D3" s="67" t="str">
         <f>CHOOSE(WEEKDAY(E1), "Neděle", "Pondělí", "Úterý", "Středa", "Čtvrtek", "Pátek", "Sobota")</f>
-        <v>Neděle</v>
+        <v>Úterý</v>
       </c>
       <c r="E3" s="5"/>
       <c r="H3" s="16"/>
@@ -1793,7 +1817,7 @@
     <row r="5">
       <c r="A5" s="68"/>
       <c r="B5" s="69" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C5" s="10"/>
       <c r="D5" s="10"/>
@@ -1833,7 +1857,7 @@
       <c r="D7" s="19"/>
       <c r="E7" s="14"/>
       <c r="F7" s="74" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G7" s="44"/>
       <c r="H7" s="45"/>
@@ -1851,7 +1875,7 @@
       <c r="D8" s="8"/>
       <c r="E8" s="76"/>
       <c r="F8" s="77" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G8" s="49"/>
       <c r="H8" s="50"/>
@@ -1866,7 +1890,7 @@
         <v>6</v>
       </c>
       <c r="C9" s="79" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D9" s="79" t="s">
         <v>10</v>
@@ -1876,62 +1900,56 @@
     <row r="10" ht="18.75" customHeight="1">
       <c r="A10" s="71"/>
       <c r="B10" s="80" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C10" s="81">
-        <v>15.0</v>
+        <v>1.0</v>
       </c>
       <c r="D10" s="82">
-        <v>118.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="71"/>
       <c r="B11" s="80" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C11" s="81">
-        <v>16.0</v>
+        <v>1.0</v>
       </c>
       <c r="D11" s="82">
-        <v>126.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="12" ht="18.75" customHeight="1">
       <c r="A12" s="71"/>
       <c r="B12" s="80" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C12" s="81">
-        <v>18.0</v>
+        <v>1.0</v>
       </c>
       <c r="D12" s="82">
-        <v>142.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="13" ht="18.75" customHeight="1">
       <c r="A13" s="71"/>
       <c r="B13" s="80" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C13" s="81">
-        <v>11.0</v>
+        <v>1.0</v>
       </c>
       <c r="D13" s="83">
-        <v>116.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="14" ht="18.75" customHeight="1">
       <c r="A14" s="71"/>
-      <c r="B14" s="80" t="s">
-        <v>21</v>
-      </c>
-      <c r="C14" s="81">
-        <v>1.0</v>
-      </c>
-      <c r="D14" s="83">
-        <v>13.0</v>
-      </c>
+      <c r="B14" s="80"/>
+      <c r="C14" s="81"/>
+      <c r="D14" s="83"/>
     </row>
     <row r="15" ht="18.75" customHeight="1">
       <c r="A15" s="71"/>
@@ -2039,8 +2057,8 @@
       <c r="T1" s="84"/>
       <c r="U1" s="84"/>
       <c r="V1" s="86">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(""1TpIiNTfR1pnpn85VWQTTdvQ2Xcr0GStmWJ2UvfKxG_A"", ""Mzdy!u1:v200"")"),46174.0)</f>
-        <v>46174</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(""1TpIiNTfR1pnpn85VWQTTdvQ2Xcr0GStmWJ2UvfKxG_A"", ""Mzdy!u1:v200"")"),46204.0)</f>
+        <v>46204</v>
       </c>
       <c r="W1" s="87"/>
       <c r="X1" s="84"/>
@@ -2138,10 +2156,10 @@
     </row>
     <row r="4">
       <c r="A4" s="88" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4" s="88" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C4" s="84" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Manažer")</f>
@@ -2238,8 +2256,8 @@
       <c r="T5" s="84"/>
       <c r="U5" s="84"/>
       <c r="V5" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),100.0)</f>
-        <v>100</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W5" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50001.08)</f>
@@ -2304,8 +2322,8 @@
       <c r="T6" s="84"/>
       <c r="U6" s="84"/>
       <c r="V6" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),112.0)</f>
-        <v>112</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W6" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50001.08)</f>
@@ -2364,8 +2382,8 @@
       <c r="T7" s="84"/>
       <c r="U7" s="84"/>
       <c r="V7" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),83.5)</f>
-        <v>83.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W7" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40004.0)</f>
@@ -2416,8 +2434,8 @@
         <v>Výroba</v>
       </c>
       <c r="H8" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Zličín")</f>
-        <v>Zličín</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Prosek")</f>
+        <v>Prosek</v>
       </c>
       <c r="I8" s="84"/>
       <c r="J8" s="84"/>
@@ -2433,8 +2451,8 @@
       <c r="T8" s="84"/>
       <c r="U8" s="84"/>
       <c r="V8" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),106.0)</f>
-        <v>106</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W8" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50001.08)</f>
@@ -2496,8 +2514,8 @@
       <c r="T9" s="84"/>
       <c r="U9" s="84"/>
       <c r="V9" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),88.0)</f>
-        <v>88</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W9" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40004.0)</f>
@@ -2565,8 +2583,8 @@
       <c r="T10" s="84"/>
       <c r="U10" s="84"/>
       <c r="V10" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),92.5)</f>
-        <v>92.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W10" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50001.08)</f>
@@ -2625,12 +2643,12 @@
       <c r="T11" s="84"/>
       <c r="U11" s="84"/>
       <c r="V11" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),39.5)</f>
-        <v>39.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W11" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7716.878)</f>
-        <v>7716.878</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="X11" s="84"/>
       <c r="Y11" s="84"/>
@@ -2745,8 +2763,8 @@
       <c r="T13" s="84"/>
       <c r="U13" s="84"/>
       <c r="V13" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),110.0)</f>
-        <v>110</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W13" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40004.0)</f>
@@ -2811,12 +2829,12 @@
       <c r="T14" s="84"/>
       <c r="U14" s="84"/>
       <c r="V14" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),37.5)</f>
-        <v>37.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W14" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6199.05)</f>
-        <v>6199.05</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="X14" s="84"/>
       <c r="Y14" s="84"/>
@@ -2874,8 +2892,8 @@
       <c r="T15" s="84"/>
       <c r="U15" s="84"/>
       <c r="V15" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),95.0)</f>
-        <v>95</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W15" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40004.0)</f>
@@ -2937,8 +2955,8 @@
       <c r="T16" s="84"/>
       <c r="U16" s="84"/>
       <c r="V16" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),74.0)</f>
-        <v>74</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W16" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40004.0)</f>
@@ -2997,12 +3015,12 @@
       <c r="T17" s="84"/>
       <c r="U17" s="84"/>
       <c r="V17" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),53.0)</f>
-        <v>53</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W17" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9370.4)</f>
-        <v>9370.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="X17" s="84"/>
       <c r="Y17" s="84"/>
@@ -3032,8 +3050,14 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D18" s="84"/>
-      <c r="E18" s="84"/>
+      <c r="D18" s="84" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Pánková Vendula")</f>
+        <v>Pánková Vendula</v>
+      </c>
+      <c r="E18" s="84" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Zličín")</f>
+        <v>Zličín</v>
+      </c>
       <c r="F18" s="84"/>
       <c r="G18" s="84"/>
       <c r="H18" s="84"/>
@@ -3083,14 +3107,29 @@
         <v/>
       </c>
       <c r="C19" s="84" t="b">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D19" s="84"/>
-      <c r="E19" s="84"/>
-      <c r="F19" s="84"/>
-      <c r="G19" s="84"/>
-      <c r="H19" s="84"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),TRUE)</f>
+        <v>1</v>
+      </c>
+      <c r="D19" s="84" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Hegedüs Erik")</f>
+        <v>Hegedüs Erik</v>
+      </c>
+      <c r="E19" s="84" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
+        <v>Libuš</v>
+      </c>
+      <c r="F19" s="84" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chodov")</f>
+        <v>Chodov</v>
+      </c>
+      <c r="G19" s="84" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Malešice")</f>
+        <v>Malešice</v>
+      </c>
+      <c r="H19" s="84" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Zličín")</f>
+        <v>Zličín</v>
+      </c>
       <c r="I19" s="84"/>
       <c r="J19" s="84"/>
       <c r="K19" s="84"/>
@@ -3109,8 +3148,8 @@
         <v>0</v>
       </c>
       <c r="W19" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50001.08)</f>
+        <v>50001.08</v>
       </c>
       <c r="X19" s="84"/>
       <c r="Y19" s="84"/>
@@ -3137,16 +3176,16 @@
         <v/>
       </c>
       <c r="C20" s="84" t="b">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),TRUE)</f>
+        <v>1</v>
       </c>
       <c r="D20" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Pánková Vendula")</f>
-        <v>Pánková Vendula</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Roth Stanislav ml.")</f>
+        <v>Roth Stanislav ml.</v>
       </c>
       <c r="E20" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Zličín")</f>
-        <v>Zličín</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bolevec")</f>
+        <v>Bolevec</v>
       </c>
       <c r="F20" s="84"/>
       <c r="G20" s="84"/>
@@ -3165,12 +3204,12 @@
       <c r="T20" s="84"/>
       <c r="U20" s="84"/>
       <c r="V20" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46.5)</f>
-        <v>46.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W20" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8221.2)</f>
-        <v>8221.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50001.08)</f>
+        <v>50001.08</v>
       </c>
       <c r="X20" s="84"/>
       <c r="Y20" s="84"/>
@@ -3197,29 +3236,23 @@
         <v/>
       </c>
       <c r="C21" s="84" t="b">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),TRUE)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
+        <v>0</v>
       </c>
       <c r="D21" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Hegedüs Erik")</f>
-        <v>Hegedüs Erik</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bubník Martin")</f>
+        <v>Bubník Martin</v>
       </c>
       <c r="E21" s="84" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
         <v>Libuš</v>
       </c>
       <c r="F21" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chodov")</f>
-        <v>Chodov</v>
-      </c>
-      <c r="G21" s="84" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Malešice")</f>
         <v>Malešice</v>
       </c>
-      <c r="H21" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Zličín")</f>
-        <v>Zličín</v>
-      </c>
+      <c r="G21" s="84"/>
+      <c r="H21" s="84"/>
       <c r="I21" s="84"/>
       <c r="J21" s="84"/>
       <c r="K21" s="84"/>
@@ -3234,12 +3267,12 @@
       <c r="T21" s="84"/>
       <c r="U21" s="84"/>
       <c r="V21" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),118.5)</f>
-        <v>118.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W21" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50001.08)</f>
-        <v>50001.08</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="X21" s="84"/>
       <c r="Y21" s="84"/>
@@ -3266,16 +3299,16 @@
         <v/>
       </c>
       <c r="C22" s="84" t="b">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),TRUE)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
+        <v>0</v>
       </c>
       <c r="D22" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Roth Stanislav ml.")</f>
-        <v>Roth Stanislav ml.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Berdar Vasyl")</f>
+        <v>Berdar Vasyl</v>
       </c>
       <c r="E22" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bolevec")</f>
-        <v>Bolevec</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
+        <v>Libuš</v>
       </c>
       <c r="F22" s="84"/>
       <c r="G22" s="84"/>
@@ -3294,12 +3327,12 @@
       <c r="T22" s="84"/>
       <c r="U22" s="84"/>
       <c r="V22" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),217.0)</f>
-        <v>217</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W22" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50001.08)</f>
-        <v>50001.08</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="X22" s="84"/>
       <c r="Y22" s="84"/>
@@ -3330,16 +3363,25 @@
         <v>0</v>
       </c>
       <c r="D23" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Makula Radek")</f>
-        <v>Makula Radek</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Yarushynskyi Vladyslav")</f>
+        <v>Yarushynskyi Vladyslav</v>
       </c>
       <c r="E23" s="84" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Malešice")</f>
+        <v>Malešice</v>
+      </c>
+      <c r="F23" s="84" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chodov")</f>
+        <v>Chodov</v>
+      </c>
+      <c r="G23" s="84" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Zličín")</f>
+        <v>Zličín</v>
+      </c>
+      <c r="H23" s="84" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Prosek")</f>
         <v>Prosek</v>
       </c>
-      <c r="F23" s="84"/>
-      <c r="G23" s="84"/>
-      <c r="H23" s="84"/>
       <c r="I23" s="84"/>
       <c r="J23" s="84"/>
       <c r="K23" s="84"/>
@@ -3390,12 +3432,12 @@
         <v>0</v>
       </c>
       <c r="D24" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bubník Martin")</f>
-        <v>Bubník Martin</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Židek Petr")</f>
+        <v>Židek Petr</v>
       </c>
       <c r="E24" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
-        <v>Libuš</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chodov")</f>
+        <v>Chodov</v>
       </c>
       <c r="F24" s="84" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Malešice")</f>
@@ -3417,12 +3459,12 @@
       <c r="T24" s="84"/>
       <c r="U24" s="84"/>
       <c r="V24" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),91.5)</f>
-        <v>91.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W24" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16002.2)</f>
-        <v>16002.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="X24" s="84"/>
       <c r="Y24" s="84"/>
@@ -3453,15 +3495,21 @@
         <v>0</v>
       </c>
       <c r="D25" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Mirga Simon")</f>
-        <v>Mirga Simon</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Gorol Patrik")</f>
+        <v>Gorol Patrik</v>
       </c>
       <c r="E25" s="84" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Malešice")</f>
         <v>Malešice</v>
       </c>
-      <c r="F25" s="84"/>
-      <c r="G25" s="84"/>
+      <c r="F25" s="84" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
+        <v>Libuš</v>
+      </c>
+      <c r="G25" s="84" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Prosek")</f>
+        <v>Prosek</v>
+      </c>
       <c r="H25" s="84"/>
       <c r="I25" s="84"/>
       <c r="J25" s="84"/>
@@ -3512,8 +3560,14 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D26" s="84"/>
-      <c r="E26" s="84"/>
+      <c r="D26" s="84" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Hegedüs Gergö")</f>
+        <v>Hegedüs Gergö</v>
+      </c>
+      <c r="E26" s="84" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
+        <v>Libuš</v>
+      </c>
       <c r="F26" s="84"/>
       <c r="G26" s="84"/>
       <c r="H26" s="84"/>
@@ -3567,8 +3621,8 @@
         <v>0</v>
       </c>
       <c r="D27" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Berdar Vasyl")</f>
-        <v>Berdar Vasyl</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Barvínková Eliška")</f>
+        <v>Barvínková Eliška</v>
       </c>
       <c r="E27" s="84" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
@@ -3591,12 +3645,12 @@
       <c r="T27" s="84"/>
       <c r="U27" s="84"/>
       <c r="V27" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),13.0)</f>
-        <v>13</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W27" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2459.288)</f>
-        <v>2459.288</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="X27" s="84"/>
       <c r="Y27" s="84"/>
@@ -3620,32 +3674,26 @@
       </c>
       <c r="B28" s="89" t="str">
         <f>IF(OR(E28=Report!$B$1, F28=Report!$B$1, G28=Report!$B$1, H28=Report!$B$1), D28, "")</f>
-        <v/>
+        <v>Kursheva Diana</v>
       </c>
       <c r="C28" s="84" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
       <c r="D28" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Yarushynskyi Vladyslav")</f>
-        <v>Yarushynskyi Vladyslav</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Kursheva Diana")</f>
+        <v>Kursheva Diana</v>
       </c>
       <c r="E28" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Malešice")</f>
-        <v>Malešice</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Výroba")</f>
+        <v>Výroba</v>
       </c>
       <c r="F28" s="84" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chodov")</f>
         <v>Chodov</v>
       </c>
-      <c r="G28" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Zličín")</f>
-        <v>Zličín</v>
-      </c>
-      <c r="H28" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Prosek")</f>
-        <v>Prosek</v>
-      </c>
+      <c r="G28" s="84"/>
+      <c r="H28" s="84"/>
       <c r="I28" s="84"/>
       <c r="J28" s="84"/>
       <c r="K28" s="84"/>
@@ -3660,12 +3708,12 @@
       <c r="T28" s="84"/>
       <c r="U28" s="84"/>
       <c r="V28" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),102.0)</f>
-        <v>102</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W28" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17543.6)</f>
-        <v>17543.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="X28" s="84"/>
       <c r="Y28" s="84"/>
@@ -3695,8 +3743,14 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D29" s="84"/>
-      <c r="E29" s="84"/>
+      <c r="D29" s="84" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Kubík Martin")</f>
+        <v>Kubík Martin</v>
+      </c>
+      <c r="E29" s="84" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
+        <v>Libuš</v>
+      </c>
       <c r="F29" s="84"/>
       <c r="G29" s="84"/>
       <c r="H29" s="84"/>
@@ -3750,16 +3804,16 @@
         <v>0</v>
       </c>
       <c r="D30" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Židek Petr")</f>
-        <v>Židek Petr</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Putna Jaroslav")</f>
+        <v>Putna Jaroslav</v>
       </c>
       <c r="E30" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chodov")</f>
-        <v>Chodov</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Zličín")</f>
+        <v>Zličín</v>
       </c>
       <c r="F30" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Malešice")</f>
-        <v>Malešice</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Prosek")</f>
+        <v>Prosek</v>
       </c>
       <c r="G30" s="84"/>
       <c r="H30" s="84"/>
@@ -3777,12 +3831,12 @@
       <c r="T30" s="84"/>
       <c r="U30" s="84"/>
       <c r="V30" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),91.0)</f>
-        <v>91</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W30" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15043.028)</f>
-        <v>15043.028</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="X30" s="84"/>
       <c r="Y30" s="84"/>
@@ -3813,22 +3867,25 @@
         <v>0</v>
       </c>
       <c r="D31" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Gorol Patrik")</f>
-        <v>Gorol Patrik</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Kopic Jakub")</f>
+        <v>Kopic Jakub</v>
       </c>
       <c r="E31" s="84" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Malešice")</f>
         <v>Malešice</v>
       </c>
       <c r="F31" s="84" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Prosek")</f>
+        <v>Prosek</v>
+      </c>
+      <c r="G31" s="84" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
         <v>Libuš</v>
       </c>
-      <c r="G31" s="84" t="str">
+      <c r="H31" s="84" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Prosek")</f>
         <v>Prosek</v>
       </c>
-      <c r="H31" s="84"/>
       <c r="I31" s="84"/>
       <c r="J31" s="84"/>
       <c r="K31" s="84"/>
@@ -3879,12 +3936,12 @@
         <v>0</v>
       </c>
       <c r="D32" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Kratochvíl Kryštof")</f>
-        <v>Kratochvíl Kryštof</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Fáberová Kateřina")</f>
+        <v>Fáberová Kateřina</v>
       </c>
       <c r="E32" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bolevec")</f>
-        <v>Bolevec</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Prosek")</f>
+        <v>Prosek</v>
       </c>
       <c r="F32" s="84"/>
       <c r="G32" s="84"/>
@@ -3939,12 +3996,12 @@
         <v>0</v>
       </c>
       <c r="D33" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Hegedüs Gergö")</f>
-        <v>Hegedüs Gergö</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chlubnová Adéla")</f>
+        <v>Chlubnová Adéla</v>
       </c>
       <c r="E33" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
-        <v>Libuš</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chodov")</f>
+        <v>Chodov</v>
       </c>
       <c r="F33" s="84"/>
       <c r="G33" s="84"/>
@@ -3999,8 +4056,8 @@
         <v>0</v>
       </c>
       <c r="D34" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Barvínková Eliška")</f>
-        <v>Barvínková Eliška</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Prošek Václav")</f>
+        <v>Prošek Václav</v>
       </c>
       <c r="E34" s="84" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
@@ -4052,24 +4109,21 @@
       </c>
       <c r="B35" s="89" t="str">
         <f>IF(OR(E35=Report!$B$1, F35=Report!$B$1, G35=Report!$B$1, H35=Report!$B$1), D35, "")</f>
-        <v>Kursheva Diana</v>
+        <v/>
       </c>
       <c r="C35" s="84" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
       <c r="D35" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Kursheva Diana")</f>
-        <v>Kursheva Diana</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Millington Emmanuel")</f>
+        <v>Millington Emmanuel</v>
       </c>
       <c r="E35" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Výroba")</f>
-        <v>Výroba</v>
-      </c>
-      <c r="F35" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chodov")</f>
-        <v>Chodov</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
+        <v>Libuš</v>
+      </c>
+      <c r="F35" s="84"/>
       <c r="G35" s="84"/>
       <c r="H35" s="84"/>
       <c r="I35" s="84"/>
@@ -4086,12 +4140,12 @@
       <c r="T35" s="84"/>
       <c r="U35" s="84"/>
       <c r="V35" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),83.5)</f>
-        <v>83.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W35" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),13803.218)</f>
-        <v>13803.218</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="X35" s="84"/>
       <c r="Y35" s="84"/>
@@ -4122,12 +4176,12 @@
         <v>0</v>
       </c>
       <c r="D36" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Tůma Vladimír")</f>
-        <v>Tůma Vladimír</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Kašpárek Jan")</f>
+        <v>Kašpárek Jan</v>
       </c>
       <c r="E36" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bolevec")</f>
-        <v>Bolevec</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
+        <v>Libuš</v>
       </c>
       <c r="F36" s="84"/>
       <c r="G36" s="84"/>
@@ -4175,19 +4229,19 @@
       </c>
       <c r="B37" s="89" t="str">
         <f>IF(OR(E37=Report!$B$1, F37=Report!$B$1, G37=Report!$B$1, H37=Report!$B$1), D37, "")</f>
-        <v/>
+        <v>Koteliuk Maryna</v>
       </c>
       <c r="C37" s="84" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
       <c r="D37" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Kubík Martin")</f>
-        <v>Kubík Martin</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Koteliuk Maryna")</f>
+        <v>Koteliuk Maryna</v>
       </c>
       <c r="E37" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
-        <v>Libuš</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Výroba")</f>
+        <v>Výroba</v>
       </c>
       <c r="F37" s="84"/>
       <c r="G37" s="84"/>
@@ -4242,17 +4296,14 @@
         <v>0</v>
       </c>
       <c r="D38" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Putna Jaroslav")</f>
-        <v>Putna Jaroslav</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Remač Jiří")</f>
+        <v>Remač Jiří</v>
       </c>
       <c r="E38" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Zličín")</f>
-        <v>Zličín</v>
-      </c>
-      <c r="F38" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Prosek")</f>
-        <v>Prosek</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
+        <v>Libuš</v>
+      </c>
+      <c r="F38" s="84"/>
       <c r="G38" s="84"/>
       <c r="H38" s="84"/>
       <c r="I38" s="84"/>
@@ -4269,12 +4320,12 @@
       <c r="T38" s="84"/>
       <c r="U38" s="84"/>
       <c r="V38" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),110.0)</f>
-        <v>110</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W38" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17668.38)</f>
-        <v>17668.38</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="X38" s="84"/>
       <c r="Y38" s="84"/>
@@ -4304,26 +4355,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D39" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Kopic Jakub")</f>
-        <v>Kopic Jakub</v>
-      </c>
-      <c r="E39" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Malešice")</f>
-        <v>Malešice</v>
-      </c>
-      <c r="F39" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Prosek")</f>
-        <v>Prosek</v>
-      </c>
-      <c r="G39" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
-        <v>Libuš</v>
-      </c>
-      <c r="H39" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Prosek")</f>
-        <v>Prosek</v>
-      </c>
+      <c r="D39" s="84"/>
+      <c r="E39" s="84"/>
+      <c r="F39" s="84"/>
+      <c r="G39" s="84"/>
+      <c r="H39" s="84"/>
       <c r="I39" s="84"/>
       <c r="J39" s="84"/>
       <c r="K39" s="84"/>
@@ -4338,12 +4374,12 @@
       <c r="T39" s="84"/>
       <c r="U39" s="84"/>
       <c r="V39" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),97.5)</f>
-        <v>97.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W39" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15952.655)</f>
-        <v>15952.655</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="X39" s="84"/>
       <c r="Y39" s="84"/>
@@ -4373,14 +4409,8 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D40" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Fáberová Kateřina")</f>
-        <v>Fáberová Kateřina</v>
-      </c>
-      <c r="E40" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Prosek")</f>
-        <v>Prosek</v>
-      </c>
+      <c r="D40" s="84"/>
+      <c r="E40" s="84"/>
       <c r="F40" s="84"/>
       <c r="G40" s="84"/>
       <c r="H40" s="84"/>
@@ -4398,12 +4428,12 @@
       <c r="T40" s="84"/>
       <c r="U40" s="84"/>
       <c r="V40" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.0)</f>
-        <v>8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W40" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1322.464)</f>
-        <v>1322.464</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="X40" s="84"/>
       <c r="Y40" s="84"/>
@@ -4433,14 +4463,8 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D41" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chlubnová Adéla")</f>
-        <v>Chlubnová Adéla</v>
-      </c>
-      <c r="E41" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chodov")</f>
-        <v>Chodov</v>
-      </c>
+      <c r="D41" s="84"/>
+      <c r="E41" s="84"/>
       <c r="F41" s="84"/>
       <c r="G41" s="84"/>
       <c r="H41" s="84"/>
@@ -4458,12 +4482,12 @@
       <c r="T41" s="84"/>
       <c r="U41" s="84"/>
       <c r="V41" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),66.0)</f>
-        <v>66</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W41" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10910.328)</f>
-        <v>10910.328</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="X41" s="84"/>
       <c r="Y41" s="84"/>
@@ -4493,14 +4517,8 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D42" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Prošek Václav")</f>
-        <v>Prošek Václav</v>
-      </c>
-      <c r="E42" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
-        <v>Libuš</v>
-      </c>
+      <c r="D42" s="84"/>
+      <c r="E42" s="84"/>
       <c r="F42" s="84"/>
       <c r="G42" s="84"/>
       <c r="H42" s="84"/>
@@ -4518,12 +4536,12 @@
       <c r="T42" s="84"/>
       <c r="U42" s="84"/>
       <c r="V42" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14.0)</f>
-        <v>14</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W42" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2314.312)</f>
-        <v>2314.312</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="X42" s="84"/>
       <c r="Y42" s="84"/>
@@ -4571,7 +4589,10 @@
       <c r="S43" s="84"/>
       <c r="T43" s="84"/>
       <c r="U43" s="84"/>
-      <c r="V43" s="84"/>
+      <c r="V43" s="90">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="W43" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
@@ -4619,7 +4640,10 @@
       <c r="S44" s="84"/>
       <c r="T44" s="84"/>
       <c r="U44" s="84"/>
-      <c r="V44" s="84"/>
+      <c r="V44" s="90">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="W44" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
@@ -4667,7 +4691,10 @@
       <c r="S45" s="84"/>
       <c r="T45" s="84"/>
       <c r="U45" s="84"/>
-      <c r="V45" s="84"/>
+      <c r="V45" s="90">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="W45" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
@@ -4715,7 +4742,10 @@
       <c r="S46" s="84"/>
       <c r="T46" s="84"/>
       <c r="U46" s="84"/>
-      <c r="V46" s="84"/>
+      <c r="V46" s="90">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="W46" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
@@ -4763,7 +4793,10 @@
       <c r="S47" s="84"/>
       <c r="T47" s="84"/>
       <c r="U47" s="84"/>
-      <c r="V47" s="84"/>
+      <c r="V47" s="90">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),374.0)</f>
+        <v>374</v>
+      </c>
       <c r="W47" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
@@ -5385,12 +5418,12 @@
       <c r="T60" s="84"/>
       <c r="U60" s="84"/>
       <c r="V60" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2049.5)</f>
-        <v>2049.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),374.0)</f>
+        <v>374</v>
       </c>
       <c r="W60" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),722553.481)</f>
-        <v>722553.481</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),578026.48)</f>
+        <v>578026.48</v>
       </c>
       <c r="X60" s="84"/>
       <c r="Y60" s="84"/>
@@ -5613,12 +5646,12 @@
       <c r="T65" s="84"/>
       <c r="U65" s="84"/>
       <c r="V65" s="84">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),30462.0)</f>
-        <v>30462</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31930.0)</f>
+        <v>31930</v>
       </c>
       <c r="W65" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),152.31)</f>
-        <v>152.31</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),159.65)</f>
+        <v>159.65</v>
       </c>
       <c r="X65" s="84"/>
       <c r="Y65" s="84"/>
@@ -6072,12 +6105,12 @@
       <c r="T75" s="84"/>
       <c r="U75" s="84"/>
       <c r="V75" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23.25)</f>
-        <v>23.25</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W75" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3487.5)</f>
-        <v>3487.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="X75" s="84"/>
       <c r="Y75" s="84"/>
@@ -6129,12 +6162,12 @@
       <c r="T76" s="84"/>
       <c r="U76" s="84"/>
       <c r="V76" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),76.0)</f>
-        <v>76</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W76" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),13436.8)</f>
-        <v>13436.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="X76" s="84"/>
       <c r="Y76" s="84"/>
@@ -6243,12 +6276,12 @@
       <c r="T78" s="84"/>
       <c r="U78" s="84"/>
       <c r="V78" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.0)</f>
-        <v>22</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W78" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3889.6)</f>
-        <v>3889.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="X78" s="84"/>
       <c r="Y78" s="84"/>
@@ -6306,12 +6339,12 @@
       <c r="T79" s="84"/>
       <c r="U79" s="84"/>
       <c r="V79" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23.0)</f>
-        <v>23</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W79" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3517.436)</f>
-        <v>3517.436</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="X79" s="84"/>
       <c r="Y79" s="84"/>
@@ -6369,12 +6402,12 @@
       <c r="T80" s="84"/>
       <c r="U80" s="84"/>
       <c r="V80" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),71.5)</f>
-        <v>71.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W80" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11819.522)</f>
-        <v>11819.522</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="X80" s="84"/>
       <c r="Y80" s="84"/>
@@ -6429,12 +6462,12 @@
       <c r="T81" s="84"/>
       <c r="U81" s="84"/>
       <c r="V81" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),47.5)</f>
-        <v>47.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W81" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7264.27)</f>
-        <v>7264.27</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="X81" s="84"/>
       <c r="Y81" s="84"/>
@@ -6546,12 +6579,12 @@
       <c r="T83" s="84"/>
       <c r="U83" s="84"/>
       <c r="V83" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.0)</f>
-        <v>22</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W83" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3364.504)</f>
-        <v>3364.504</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="X83" s="84"/>
       <c r="Y83" s="84"/>
@@ -6606,12 +6639,12 @@
       <c r="T84" s="84"/>
       <c r="U84" s="84"/>
       <c r="V84" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29.5)</f>
-        <v>29.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W84" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4876.586)</f>
-        <v>4876.586</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="X84" s="84"/>
       <c r="Y84" s="84"/>
@@ -6663,12 +6696,12 @@
       <c r="T85" s="84"/>
       <c r="U85" s="84"/>
       <c r="V85" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.5)</f>
-        <v>22.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W85" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3375.0)</f>
-        <v>3375</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="X85" s="84"/>
       <c r="Y85" s="84"/>
@@ -6696,12 +6729,12 @@
         <v>0</v>
       </c>
       <c r="D86" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Mikuš Pavel")</f>
-        <v>Mikuš Pavel</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Hyský Aleš")</f>
+        <v>Hyský Aleš</v>
       </c>
       <c r="E86" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Prosek")</f>
-        <v>Prosek</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chodov")</f>
+        <v>Chodov</v>
       </c>
       <c r="F86" s="84"/>
       <c r="G86" s="84"/>
@@ -6746,23 +6779,32 @@
       <c r="A87" s="84"/>
       <c r="B87" s="89" t="str">
         <f>IF(OR(E87=Report!$B$1, F87=Report!$B$1, G87=Report!$B$1, H87=Report!$B$1), D87, "")</f>
-        <v/>
+        <v>Lažek Jaroslav</v>
       </c>
       <c r="C87" s="84" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
       <c r="D87" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Hyský Aleš")</f>
-        <v>Hyský Aleš</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Lažek Jaroslav")</f>
+        <v>Lažek Jaroslav</v>
       </c>
       <c r="E87" s="84" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
+        <v>Libuš</v>
+      </c>
+      <c r="F87" s="84" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chodov")</f>
         <v>Chodov</v>
       </c>
-      <c r="F87" s="84"/>
-      <c r="G87" s="84"/>
-      <c r="H87" s="84"/>
+      <c r="G87" s="84" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Malešice")</f>
+        <v>Malešice</v>
+      </c>
+      <c r="H87" s="84" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Výroba")</f>
+        <v>Výroba</v>
+      </c>
       <c r="I87" s="84"/>
       <c r="J87" s="84"/>
       <c r="K87" s="84"/>
@@ -6777,12 +6819,12 @@
       <c r="T87" s="84"/>
       <c r="U87" s="84"/>
       <c r="V87" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.5)</f>
-        <v>8.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W87" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1299.922)</f>
-        <v>1299.922</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="X87" s="84"/>
       <c r="Y87" s="84"/>
@@ -6810,12 +6852,12 @@
         <v>0</v>
       </c>
       <c r="D88" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Šmídová Sabina")</f>
-        <v>Šmídová Sabina</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Kormash Liubov")</f>
+        <v>Kormash Liubov</v>
       </c>
       <c r="E88" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chodov")</f>
-        <v>Chodov</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Zličín")</f>
+        <v>Zličín</v>
       </c>
       <c r="F88" s="84" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Prosek")</f>
@@ -6863,32 +6905,29 @@
       <c r="A89" s="84"/>
       <c r="B89" s="89" t="str">
         <f>IF(OR(E89=Report!$B$1, F89=Report!$B$1, G89=Report!$B$1, H89=Report!$B$1), D89, "")</f>
-        <v>Lažek Jaroslav</v>
+        <v>Chlubna Tomáš</v>
       </c>
       <c r="C89" s="84" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
       <c r="D89" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Lažek Jaroslav")</f>
-        <v>Lažek Jaroslav</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chlubna Tomáš")</f>
+        <v>Chlubna Tomáš</v>
       </c>
       <c r="E89" s="84" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chodov")</f>
+        <v>Chodov</v>
+      </c>
+      <c r="F89" s="84" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
         <v>Libuš</v>
       </c>
-      <c r="F89" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chodov")</f>
-        <v>Chodov</v>
-      </c>
       <c r="G89" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Malešice")</f>
-        <v>Malešice</v>
-      </c>
-      <c r="H89" s="84" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Výroba")</f>
         <v>Výroba</v>
       </c>
+      <c r="H89" s="84"/>
       <c r="I89" s="84"/>
       <c r="J89" s="84"/>
       <c r="K89" s="84"/>
@@ -6903,12 +6942,12 @@
       <c r="T89" s="84"/>
       <c r="U89" s="84"/>
       <c r="V89" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),42.5)</f>
-        <v>42.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W89" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7225.0)</f>
-        <v>7225</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="X89" s="84"/>
       <c r="Y89" s="84"/>
@@ -6936,18 +6975,21 @@
         <v>0</v>
       </c>
       <c r="D90" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Kormash Liubov")</f>
-        <v>Kormash Liubov</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Vychivskyi Volodymyr")</f>
+        <v>Vychivskyi Volodymyr</v>
       </c>
       <c r="E90" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Zličín")</f>
-        <v>Zličín</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Malešice")</f>
+        <v>Malešice</v>
       </c>
       <c r="F90" s="84" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Prosek")</f>
         <v>Prosek</v>
       </c>
-      <c r="G90" s="84"/>
+      <c r="G90" s="84" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Zličín")</f>
+        <v>Zličín</v>
+      </c>
       <c r="H90" s="84"/>
       <c r="I90" s="84"/>
       <c r="J90" s="84"/>
@@ -6963,12 +7005,12 @@
       <c r="T90" s="84"/>
       <c r="U90" s="84"/>
       <c r="V90" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),75.0)</f>
-        <v>75</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W90" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12000.0)</f>
-        <v>12000</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="X90" s="84"/>
       <c r="Y90" s="84"/>
@@ -6989,17 +7031,32 @@
       <c r="A91" s="84"/>
       <c r="B91" s="89" t="str">
         <f>IF(OR(E91=Report!$B$1, F91=Report!$B$1, G91=Report!$B$1, H91=Report!$B$1), D91, "")</f>
-        <v/>
+        <v>Hřebík Martin</v>
       </c>
       <c r="C91" s="84" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D91" s="84"/>
-      <c r="E91" s="84"/>
-      <c r="F91" s="84"/>
-      <c r="G91" s="84"/>
-      <c r="H91" s="84"/>
+      <c r="D91" s="84" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Hřebík Martin")</f>
+        <v>Hřebík Martin</v>
+      </c>
+      <c r="E91" s="84" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Výroba")</f>
+        <v>Výroba</v>
+      </c>
+      <c r="F91" s="84" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chodov")</f>
+        <v>Chodov</v>
+      </c>
+      <c r="G91" s="84" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Prosek")</f>
+        <v>Prosek</v>
+      </c>
+      <c r="H91" s="84" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
+        <v>Libuš</v>
+      </c>
       <c r="I91" s="84"/>
       <c r="J91" s="84"/>
       <c r="K91" s="84"/>
@@ -7018,8 +7075,8 @@
         <v>0</v>
       </c>
       <c r="W91" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),44995.2)</f>
+        <v>44995.2</v>
       </c>
       <c r="X91" s="84"/>
       <c r="Y91" s="84"/>
@@ -7046,8 +7103,14 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D92" s="84"/>
-      <c r="E92" s="84"/>
+      <c r="D92" s="84" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Eszenyiová Patrícia")</f>
+        <v>Eszenyiová Patrícia</v>
+      </c>
+      <c r="E92" s="84" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
+        <v>Libuš</v>
+      </c>
       <c r="F92" s="84"/>
       <c r="G92" s="84"/>
       <c r="H92" s="84"/>
@@ -7091,29 +7154,32 @@
       <c r="A93" s="84"/>
       <c r="B93" s="89" t="str">
         <f>IF(OR(E93=Report!$B$1, F93=Report!$B$1, G93=Report!$B$1, H93=Report!$B$1), D93, "")</f>
-        <v>Chlubna Tomáš</v>
+        <v/>
       </c>
       <c r="C93" s="84" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
       <c r="D93" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chlubna Tomáš")</f>
-        <v>Chlubna Tomáš</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Reischl Jan")</f>
+        <v>Reischl Jan</v>
       </c>
       <c r="E93" s="84" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Malešice")</f>
+        <v>Malešice</v>
+      </c>
+      <c r="F93" s="84" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chodov")</f>
         <v>Chodov</v>
       </c>
-      <c r="F93" s="84" t="str">
+      <c r="G93" s="84" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
         <v>Libuš</v>
       </c>
-      <c r="G93" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Výroba")</f>
-        <v>Výroba</v>
-      </c>
-      <c r="H93" s="84"/>
+      <c r="H93" s="84" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Prosek")</f>
+        <v>Prosek</v>
+      </c>
       <c r="I93" s="84"/>
       <c r="J93" s="84"/>
       <c r="K93" s="84"/>
@@ -7128,12 +7194,12 @@
       <c r="T93" s="84"/>
       <c r="U93" s="84"/>
       <c r="V93" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),78.5)</f>
-        <v>78.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W93" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12976.678)</f>
-        <v>12976.678</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="X93" s="84"/>
       <c r="Y93" s="84"/>
@@ -7161,21 +7227,15 @@
         <v>0</v>
       </c>
       <c r="D94" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Vychivskyi Volodymyr")</f>
-        <v>Vychivskyi Volodymyr</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Mikešová Adéla")</f>
+        <v>Mikešová Adéla</v>
       </c>
       <c r="E94" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Malešice")</f>
-        <v>Malešice</v>
-      </c>
-      <c r="F94" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Prosek")</f>
-        <v>Prosek</v>
-      </c>
-      <c r="G94" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Zličín")</f>
-        <v>Zličín</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bolevec")</f>
+        <v>Bolevec</v>
+      </c>
+      <c r="F94" s="84"/>
+      <c r="G94" s="84"/>
       <c r="H94" s="84"/>
       <c r="I94" s="84"/>
       <c r="J94" s="84"/>
@@ -7191,12 +7251,12 @@
       <c r="T94" s="84"/>
       <c r="U94" s="84"/>
       <c r="V94" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),112.0)</f>
-        <v>112</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W94" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17942.896)</f>
-        <v>17942.896</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="X94" s="84"/>
       <c r="Y94" s="84"/>
@@ -7223,8 +7283,14 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D95" s="84"/>
-      <c r="E95" s="84"/>
+      <c r="D95" s="84" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chyský David")</f>
+        <v>Chyský David</v>
+      </c>
+      <c r="E95" s="84" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chodov")</f>
+        <v>Chodov</v>
+      </c>
       <c r="F95" s="84"/>
       <c r="G95" s="84"/>
       <c r="H95" s="84"/>
@@ -7268,32 +7334,26 @@
       <c r="A96" s="84"/>
       <c r="B96" s="89" t="str">
         <f>IF(OR(E96=Report!$B$1, F96=Report!$B$1, G96=Report!$B$1, H96=Report!$B$1), D96, "")</f>
-        <v>Hřebík Martin</v>
+        <v/>
       </c>
       <c r="C96" s="84" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
       <c r="D96" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Hřebík Martin")</f>
-        <v>Hřebík Martin</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Kalina Filip")</f>
+        <v>Kalina Filip</v>
       </c>
       <c r="E96" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Výroba")</f>
-        <v>Výroba</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Malešice")</f>
+        <v>Malešice</v>
       </c>
       <c r="F96" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chodov")</f>
-        <v>Chodov</v>
-      </c>
-      <c r="G96" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Prosek")</f>
-        <v>Prosek</v>
-      </c>
-      <c r="H96" s="84" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
         <v>Libuš</v>
       </c>
+      <c r="G96" s="84"/>
+      <c r="H96" s="84"/>
       <c r="I96" s="84"/>
       <c r="J96" s="84"/>
       <c r="K96" s="84"/>
@@ -7308,12 +7368,12 @@
       <c r="T96" s="84"/>
       <c r="U96" s="84"/>
       <c r="V96" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),65.0)</f>
-        <v>65</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W96" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),44995.2)</f>
-        <v>44995.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="X96" s="84"/>
       <c r="Y96" s="84"/>
@@ -7341,12 +7401,12 @@
         <v>0</v>
       </c>
       <c r="D97" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Eszenyiová Patrícia")</f>
-        <v>Eszenyiová Patrícia</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Kaločai Rudolf")</f>
+        <v>Kaločai Rudolf</v>
       </c>
       <c r="E97" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
-        <v>Libuš</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bolevec")</f>
+        <v>Bolevec</v>
       </c>
       <c r="F97" s="84"/>
       <c r="G97" s="84"/>
@@ -7365,12 +7425,12 @@
       <c r="T97" s="84"/>
       <c r="U97" s="84"/>
       <c r="V97" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.75)</f>
-        <v>31.75</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W97" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5248.529)</f>
-        <v>5248.529</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="X97" s="84"/>
       <c r="Y97" s="84"/>
@@ -7398,25 +7458,19 @@
         <v>0</v>
       </c>
       <c r="D98" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Reischl Jan")</f>
-        <v>Reischl Jan</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Dušek Sam")</f>
+        <v>Dušek Sam</v>
       </c>
       <c r="E98" s="84" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
+        <v>Libuš</v>
+      </c>
+      <c r="F98" s="84" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Malešice")</f>
         <v>Malešice</v>
       </c>
-      <c r="F98" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chodov")</f>
-        <v>Chodov</v>
-      </c>
-      <c r="G98" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
-        <v>Libuš</v>
-      </c>
-      <c r="H98" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Prosek")</f>
-        <v>Prosek</v>
-      </c>
+      <c r="G98" s="84"/>
+      <c r="H98" s="84"/>
       <c r="I98" s="84"/>
       <c r="J98" s="84"/>
       <c r="K98" s="84"/>
@@ -7431,12 +7485,12 @@
       <c r="T98" s="84"/>
       <c r="U98" s="84"/>
       <c r="V98" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.0)</f>
-        <v>12</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W98" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1697.28)</f>
-        <v>1697.28</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="X98" s="84"/>
       <c r="Y98" s="84"/>
@@ -7464,12 +7518,12 @@
         <v>0</v>
       </c>
       <c r="D99" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Mikešová Adéla")</f>
-        <v>Mikešová Adéla</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Banga Adam")</f>
+        <v>Banga Adam</v>
       </c>
       <c r="E99" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bolevec")</f>
-        <v>Bolevec</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Zličín")</f>
+        <v>Zličín</v>
       </c>
       <c r="F99" s="84"/>
       <c r="G99" s="84"/>
@@ -7521,12 +7575,12 @@
         <v>0</v>
       </c>
       <c r="D100" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Pražák Aleš")</f>
-        <v>Pražák Aleš</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Vopatová Anna")</f>
+        <v>Vopatová Anna</v>
       </c>
       <c r="E100" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chodov")</f>
-        <v>Chodov</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bolevec")</f>
+        <v>Bolevec</v>
       </c>
       <c r="F100" s="84"/>
       <c r="G100" s="84"/>
@@ -7578,12 +7632,12 @@
         <v>0</v>
       </c>
       <c r="D101" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chyský David")</f>
-        <v>Chyský David</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Vopatová Šárka")</f>
+        <v>Vopatová Šárka</v>
       </c>
       <c r="E101" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chodov")</f>
-        <v>Chodov</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bolevec")</f>
+        <v>Bolevec</v>
       </c>
       <c r="F101" s="84"/>
       <c r="G101" s="84"/>
@@ -7634,8 +7688,14 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D102" s="84"/>
-      <c r="E102" s="84"/>
+      <c r="D102" s="84" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Richterová Monika")</f>
+        <v>Richterová Monika</v>
+      </c>
+      <c r="E102" s="84" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Malešice")</f>
+        <v>Malešice</v>
+      </c>
       <c r="F102" s="84"/>
       <c r="G102" s="84"/>
       <c r="H102" s="84"/>
@@ -7685,9 +7745,18 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D103" s="84"/>
-      <c r="E103" s="84"/>
-      <c r="F103" s="84"/>
+      <c r="D103" s="84" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Serin David")</f>
+        <v>Serin David</v>
+      </c>
+      <c r="E103" s="84" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
+        <v>Libuš</v>
+      </c>
+      <c r="F103" s="84" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Malešice")</f>
+        <v>Malešice</v>
+      </c>
       <c r="G103" s="84"/>
       <c r="H103" s="84"/>
       <c r="I103" s="84"/>
@@ -7737,12 +7806,12 @@
         <v>0</v>
       </c>
       <c r="D104" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Kulinič Michail")</f>
-        <v>Kulinič Michail</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Fabera Tomáš")</f>
+        <v>Fabera Tomáš</v>
       </c>
       <c r="E104" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Prosek")</f>
-        <v>Prosek</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chodov")</f>
+        <v>Chodov</v>
       </c>
       <c r="F104" s="84"/>
       <c r="G104" s="84"/>
@@ -7794,17 +7863,14 @@
         <v>0</v>
       </c>
       <c r="D105" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Kalina Filip")</f>
-        <v>Kalina Filip</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Hendrych Rostislav")</f>
+        <v>Hendrych Rostislav</v>
       </c>
       <c r="E105" s="84" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Malešice")</f>
         <v>Malešice</v>
       </c>
-      <c r="F105" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
-        <v>Libuš</v>
-      </c>
+      <c r="F105" s="84"/>
       <c r="G105" s="84"/>
       <c r="H105" s="84"/>
       <c r="I105" s="84"/>
@@ -7821,12 +7887,12 @@
       <c r="T105" s="84"/>
       <c r="U105" s="84"/>
       <c r="V105" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),33.5)</f>
-        <v>33.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W105" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5123.222)</f>
-        <v>5123.222</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="X105" s="84"/>
       <c r="Y105" s="84"/>
@@ -7853,8 +7919,14 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D106" s="84"/>
-      <c r="E106" s="84"/>
+      <c r="D106" s="84" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Světlík František")</f>
+        <v>Světlík František</v>
+      </c>
+      <c r="E106" s="84" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bolevec")</f>
+        <v>Bolevec</v>
+      </c>
       <c r="F106" s="84"/>
       <c r="G106" s="84"/>
       <c r="H106" s="84"/>
@@ -7905,8 +7977,8 @@
         <v>0</v>
       </c>
       <c r="D107" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Kaločai Rudolf")</f>
-        <v>Kaločai Rudolf</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Ženíšek Lukáš")</f>
+        <v>Ženíšek Lukáš</v>
       </c>
       <c r="E107" s="84" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bolevec")</f>
@@ -7929,12 +8001,12 @@
       <c r="T107" s="84"/>
       <c r="U107" s="84"/>
       <c r="V107" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),74.5)</f>
-        <v>74.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W107" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10430.0)</f>
-        <v>10430</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="X107" s="84"/>
       <c r="Y107" s="84"/>
@@ -7962,17 +8034,14 @@
         <v>0</v>
       </c>
       <c r="D108" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Dušek Sam")</f>
-        <v>Dušek Sam</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Roth Stanislav st.")</f>
+        <v>Roth Stanislav st.</v>
       </c>
       <c r="E108" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
-        <v>Libuš</v>
-      </c>
-      <c r="F108" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Malešice")</f>
-        <v>Malešice</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bolevec")</f>
+        <v>Bolevec</v>
+      </c>
+      <c r="F108" s="84"/>
       <c r="G108" s="84"/>
       <c r="H108" s="84"/>
       <c r="I108" s="84"/>
@@ -7989,12 +8058,12 @@
       <c r="T108" s="84"/>
       <c r="U108" s="84"/>
       <c r="V108" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),113.5)</f>
-        <v>113.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W108" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18148.783)</f>
-        <v>18148.783</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29728.0)</f>
+        <v>29728</v>
       </c>
       <c r="X108" s="84"/>
       <c r="Y108" s="84"/>
@@ -8022,12 +8091,12 @@
         <v>0</v>
       </c>
       <c r="D109" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Kačena Stanislav")</f>
-        <v>Kačena Stanislav</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Vaníková Anna")</f>
+        <v>Vaníková Anna</v>
       </c>
       <c r="E109" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Prosek")</f>
-        <v>Prosek</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Zličín")</f>
+        <v>Zličín</v>
       </c>
       <c r="F109" s="84"/>
       <c r="G109" s="84"/>
@@ -8079,8 +8148,8 @@
         <v>0</v>
       </c>
       <c r="D110" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Cieslar Marek")</f>
-        <v>Cieslar Marek</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Břicháč Pavel")</f>
+        <v>Břicháč Pavel</v>
       </c>
       <c r="E110" s="84" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
@@ -8136,8 +8205,8 @@
         <v>0</v>
       </c>
       <c r="D111" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Banga Adam")</f>
-        <v>Banga Adam</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Čerešňák Michal")</f>
+        <v>Čerešňák Michal</v>
       </c>
       <c r="E111" s="84" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Zličín")</f>
@@ -8193,14 +8262,17 @@
         <v>0</v>
       </c>
       <c r="D112" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Vopatová Anna")</f>
-        <v>Vopatová Anna</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Weindling Josef")</f>
+        <v>Weindling Josef</v>
       </c>
       <c r="E112" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bolevec")</f>
-        <v>Bolevec</v>
-      </c>
-      <c r="F112" s="84"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
+        <v>Libuš</v>
+      </c>
+      <c r="F112" s="84" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Malešice")</f>
+        <v>Malešice</v>
+      </c>
       <c r="G112" s="84"/>
       <c r="H112" s="84"/>
       <c r="I112" s="84"/>
@@ -8217,12 +8289,12 @@
       <c r="T112" s="84"/>
       <c r="U112" s="84"/>
       <c r="V112" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29.0)</f>
-        <v>29</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W112" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4101.76)</f>
-        <v>4101.76</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="X112" s="84"/>
       <c r="Y112" s="84"/>
@@ -8250,12 +8322,12 @@
         <v>0</v>
       </c>
       <c r="D113" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Vopatová Šárka")</f>
-        <v>Vopatová Šárka</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Fux Vojtěch")</f>
+        <v>Fux Vojtěch</v>
       </c>
       <c r="E113" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bolevec")</f>
-        <v>Bolevec</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chodov")</f>
+        <v>Chodov</v>
       </c>
       <c r="F113" s="84"/>
       <c r="G113" s="84"/>
@@ -8274,12 +8346,12 @@
       <c r="T113" s="84"/>
       <c r="U113" s="84"/>
       <c r="V113" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.0)</f>
-        <v>7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W113" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),990.08)</f>
-        <v>990.08</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="X113" s="84"/>
       <c r="Y113" s="84"/>
@@ -8307,12 +8379,12 @@
         <v>0</v>
       </c>
       <c r="D114" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Richterová Monika")</f>
-        <v>Richterová Monika</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Kumar Jatinder")</f>
+        <v>Kumar Jatinder</v>
       </c>
       <c r="E114" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Malešice")</f>
-        <v>Malešice</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
+        <v>Libuš</v>
       </c>
       <c r="F114" s="84"/>
       <c r="G114" s="84"/>
@@ -8364,17 +8436,14 @@
         <v>0</v>
       </c>
       <c r="D115" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Serin David")</f>
-        <v>Serin David</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Stehlíková Magdaléna")</f>
+        <v>Stehlíková Magdaléna</v>
       </c>
       <c r="E115" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
-        <v>Libuš</v>
-      </c>
-      <c r="F115" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Malešice")</f>
-        <v>Malešice</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bolevec")</f>
+        <v>Bolevec</v>
+      </c>
+      <c r="F115" s="84"/>
       <c r="G115" s="84"/>
       <c r="H115" s="84"/>
       <c r="I115" s="84"/>
@@ -8391,12 +8460,12 @@
       <c r="T115" s="84"/>
       <c r="U115" s="84"/>
       <c r="V115" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),13.0)</f>
-        <v>13</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W115" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2149.004)</f>
-        <v>2149.004</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="X115" s="84"/>
       <c r="Y115" s="84"/>
@@ -8424,14 +8493,17 @@
         <v>0</v>
       </c>
       <c r="D116" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Fabera Tomáš")</f>
-        <v>Fabera Tomáš</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Dragoun Alfréd")</f>
+        <v>Dragoun Alfréd</v>
       </c>
       <c r="E116" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chodov")</f>
-        <v>Chodov</v>
-      </c>
-      <c r="F116" s="84"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Zličín")</f>
+        <v>Zličín</v>
+      </c>
+      <c r="F116" s="84" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Malešice")</f>
+        <v>Malešice</v>
+      </c>
       <c r="G116" s="84"/>
       <c r="H116" s="84"/>
       <c r="I116" s="84"/>
@@ -8448,12 +8520,12 @@
       <c r="T116" s="84"/>
       <c r="U116" s="84"/>
       <c r="V116" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
-        <v>4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W116" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),611.728)</f>
-        <v>611.728</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="X116" s="84"/>
       <c r="Y116" s="84"/>
@@ -8480,14 +8552,8 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D117" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Hendrych Rostislav")</f>
-        <v>Hendrych Rostislav</v>
-      </c>
-      <c r="E117" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Malešice")</f>
-        <v>Malešice</v>
-      </c>
+      <c r="D117" s="84"/>
+      <c r="E117" s="84"/>
       <c r="F117" s="84"/>
       <c r="G117" s="84"/>
       <c r="H117" s="84"/>
@@ -8505,12 +8571,12 @@
       <c r="T117" s="84"/>
       <c r="U117" s="84"/>
       <c r="V117" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27.0)</f>
-        <v>27</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W117" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4463.316)</f>
-        <v>4463.316</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="X117" s="84"/>
       <c r="Y117" s="84"/>
@@ -8588,14 +8654,8 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D119" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Světlík František")</f>
-        <v>Světlík František</v>
-      </c>
-      <c r="E119" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bolevec")</f>
-        <v>Bolevec</v>
-      </c>
+      <c r="D119" s="84"/>
+      <c r="E119" s="84"/>
       <c r="F119" s="84"/>
       <c r="G119" s="84"/>
       <c r="H119" s="84"/>
@@ -8613,12 +8673,12 @@
       <c r="T119" s="84"/>
       <c r="U119" s="84"/>
       <c r="V119" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),57.5)</f>
-        <v>57.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W119" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8132.8)</f>
-        <v>8132.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="X119" s="84"/>
       <c r="Y119" s="84"/>
@@ -8645,14 +8705,8 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D120" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Ženíšek Lukáš")</f>
-        <v>Ženíšek Lukáš</v>
-      </c>
-      <c r="E120" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bolevec")</f>
-        <v>Bolevec</v>
-      </c>
+      <c r="D120" s="84"/>
+      <c r="E120" s="84"/>
       <c r="F120" s="84"/>
       <c r="G120" s="84"/>
       <c r="H120" s="84"/>
@@ -8703,10 +8757,7 @@
         <v>0</v>
       </c>
       <c r="D121" s="84"/>
-      <c r="E121" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chodov")</f>
-        <v>Chodov</v>
-      </c>
+      <c r="E121" s="84"/>
       <c r="F121" s="84"/>
       <c r="G121" s="84"/>
       <c r="H121" s="84"/>
@@ -8756,14 +8807,8 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D122" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Roth Stanislav st.")</f>
-        <v>Roth Stanislav st.</v>
-      </c>
-      <c r="E122" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bolevec")</f>
-        <v>Bolevec</v>
-      </c>
+      <c r="D122" s="84"/>
+      <c r="E122" s="84"/>
       <c r="F122" s="84"/>
       <c r="G122" s="84"/>
       <c r="H122" s="84"/>
@@ -8785,8 +8830,8 @@
         <v>0</v>
       </c>
       <c r="W122" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29728.0)</f>
-        <v>29728</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="X122" s="84"/>
       <c r="Y122" s="84"/>
@@ -8915,14 +8960,8 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D125" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Vaníková Anna")</f>
-        <v>Vaníková Anna</v>
-      </c>
-      <c r="E125" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Zličín")</f>
-        <v>Zličín</v>
-      </c>
+      <c r="D125" s="84"/>
+      <c r="E125" s="84"/>
       <c r="F125" s="84"/>
       <c r="G125" s="84"/>
       <c r="H125" s="84"/>
@@ -8940,12 +8979,12 @@
       <c r="T125" s="84"/>
       <c r="U125" s="84"/>
       <c r="V125" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),24.0)</f>
-        <v>24</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W125" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3967.392)</f>
-        <v>3967.392</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="X125" s="84"/>
       <c r="Y125" s="84"/>
@@ -8972,14 +9011,8 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D126" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Břicháč Pavel")</f>
-        <v>Břicháč Pavel</v>
-      </c>
-      <c r="E126" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
-        <v>Libuš</v>
-      </c>
+      <c r="D126" s="84"/>
+      <c r="E126" s="84"/>
       <c r="F126" s="84"/>
       <c r="G126" s="84"/>
       <c r="H126" s="84"/>
@@ -8997,12 +9030,12 @@
       <c r="T126" s="84"/>
       <c r="U126" s="84"/>
       <c r="V126" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49.5)</f>
-        <v>49.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W126" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7570.134)</f>
-        <v>7570.134</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="X126" s="84"/>
       <c r="Y126" s="84"/>
@@ -9029,14 +9062,8 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D127" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Čerešňák Michal")</f>
-        <v>Čerešňák Michal</v>
-      </c>
-      <c r="E127" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Zličín")</f>
-        <v>Zličín</v>
-      </c>
+      <c r="D127" s="84"/>
+      <c r="E127" s="84"/>
       <c r="F127" s="84"/>
       <c r="G127" s="84"/>
       <c r="H127" s="84"/>
@@ -9054,12 +9081,12 @@
       <c r="T127" s="84"/>
       <c r="U127" s="84"/>
       <c r="V127" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),63.0)</f>
-        <v>63</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W127" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10710.0)</f>
-        <v>10710</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="X127" s="84"/>
       <c r="Y127" s="84"/>
@@ -9086,18 +9113,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D128" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Weindling Josef")</f>
-        <v>Weindling Josef</v>
-      </c>
-      <c r="E128" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
-        <v>Libuš</v>
-      </c>
-      <c r="F128" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Malešice")</f>
-        <v>Malešice</v>
-      </c>
+      <c r="D128" s="84"/>
+      <c r="E128" s="84"/>
+      <c r="F128" s="84"/>
       <c r="G128" s="84"/>
       <c r="H128" s="84"/>
       <c r="I128" s="84"/>
@@ -9114,12 +9132,12 @@
       <c r="T128" s="84"/>
       <c r="U128" s="84"/>
       <c r="V128" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),43.5)</f>
-        <v>43.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W128" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6652.5419999999995)</f>
-        <v>6652.542</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="X128" s="84"/>
       <c r="Y128" s="84"/>
@@ -9146,14 +9164,8 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D129" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Fux Vojtěch")</f>
-        <v>Fux Vojtěch</v>
-      </c>
-      <c r="E129" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chodov")</f>
-        <v>Chodov</v>
-      </c>
+      <c r="D129" s="84"/>
+      <c r="E129" s="84"/>
       <c r="F129" s="84"/>
       <c r="G129" s="84"/>
       <c r="H129" s="84"/>
@@ -9171,12 +9183,12 @@
       <c r="T129" s="84"/>
       <c r="U129" s="84"/>
       <c r="V129" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50.5)</f>
-        <v>50.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W129" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10100.0)</f>
-        <v>10100</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="X129" s="84"/>
       <c r="Y129" s="84"/>
@@ -9203,13 +9215,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D130" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Kumar Jatinder")</f>
-        <v>Kumar Jatinder</v>
-      </c>
+      <c r="D130" s="84"/>
       <c r="E130" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
-        <v>Libuš</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chodov")</f>
+        <v>Chodov</v>
       </c>
       <c r="F130" s="84"/>
       <c r="G130" s="84"/>
@@ -9260,14 +9269,8 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D131" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Stehlíková Magdaléna")</f>
-        <v>Stehlíková Magdaléna</v>
-      </c>
-      <c r="E131" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bolevec")</f>
-        <v>Bolevec</v>
-      </c>
+      <c r="D131" s="84"/>
+      <c r="E131" s="84"/>
       <c r="F131" s="84"/>
       <c r="G131" s="84"/>
       <c r="H131" s="84"/>
@@ -9285,12 +9288,12 @@
       <c r="T131" s="84"/>
       <c r="U131" s="84"/>
       <c r="V131" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.0)</f>
-        <v>12</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W131" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1697.28)</f>
-        <v>1697.28</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="X131" s="84"/>
       <c r="Y131" s="84"/>
@@ -9317,14 +9320,8 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D132" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Dragoun Alfréd")</f>
-        <v>Dragoun Alfréd</v>
-      </c>
-      <c r="E132" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Zličín")</f>
-        <v>Zličín</v>
-      </c>
+      <c r="D132" s="84"/>
+      <c r="E132" s="84"/>
       <c r="F132" s="84"/>
       <c r="G132" s="84"/>
       <c r="H132" s="84"/>
@@ -9342,12 +9339,12 @@
       <c r="T132" s="84"/>
       <c r="U132" s="84"/>
       <c r="V132" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
-        <v>5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W132" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),826.54)</f>
-        <v>826.54</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="X132" s="84"/>
       <c r="Y132" s="84"/>
@@ -12540,12 +12537,12 @@
       <c r="T196" s="84"/>
       <c r="U196" s="84"/>
       <c r="V196" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1369.0)</f>
-        <v>1369</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W196" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),283819.30399999995)</f>
-        <v>283819.304</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),74723.2)</f>
+        <v>74723.2</v>
       </c>
       <c r="X196" s="84"/>
       <c r="Y196" s="84"/>
@@ -43935,7 +43932,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="94" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C1" s="94" t="s">
         <v>4</v>
@@ -43947,22 +43944,22 @@
         <v>8</v>
       </c>
       <c r="F1" s="94" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G1" s="94" t="s">
         <v>10</v>
       </c>
       <c r="H1" s="94" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I1" s="94" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J1" s="94" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K1" s="94" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2">
@@ -43970,22 +43967,22 @@
         <v>45528.0</v>
       </c>
       <c r="B2" s="94" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C2" s="94" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D2" s="96" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E2" s="96" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F2" s="96" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G2" s="96" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H2" s="97">
         <v>3728.0</v>
@@ -43996,22 +43993,22 @@
         <v>45528.0</v>
       </c>
       <c r="B3" s="94" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C3" s="94" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D3" s="96" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" s="96" t="s">
+        <v>37</v>
+      </c>
+      <c r="F3" s="96" t="s">
+        <v>33</v>
+      </c>
+      <c r="G3" s="96" t="s">
         <v>34</v>
-      </c>
-      <c r="E3" s="96" t="s">
-        <v>35</v>
-      </c>
-      <c r="F3" s="96" t="s">
-        <v>32</v>
-      </c>
-      <c r="G3" s="96" t="s">
-        <v>33</v>
       </c>
       <c r="H3" s="97">
         <v>3728.0</v>
@@ -44022,19 +44019,19 @@
         <v>45528.0</v>
       </c>
       <c r="B4" s="94" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C4" s="94" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D4" s="96" t="s">
+        <v>38</v>
+      </c>
+      <c r="E4" s="96" t="s">
         <v>36</v>
       </c>
-      <c r="E4" s="96" t="s">
-        <v>34</v>
-      </c>
       <c r="G4" s="96" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H4" s="97">
         <v>3728.0</v>
@@ -44045,7 +44042,7 @@
         <v>45528.0</v>
       </c>
       <c r="B5" s="94" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I5" s="97">
         <v>12.0</v>
@@ -44062,22 +44059,22 @@
         <v>45526.0</v>
       </c>
       <c r="B6" s="94" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C6" s="94" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D6" s="96" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E6" s="96" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F6" s="96" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G6" s="96" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H6" s="97">
         <v>3728.0</v>
@@ -44088,22 +44085,22 @@
         <v>45526.0</v>
       </c>
       <c r="B7" s="94" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" s="94" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" s="96" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" s="96" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="94" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="96" t="s">
+      <c r="F7" s="96" t="s">
+        <v>33</v>
+      </c>
+      <c r="G7" s="96" t="s">
         <v>34</v>
-      </c>
-      <c r="E7" s="96" t="s">
-        <v>35</v>
-      </c>
-      <c r="F7" s="96" t="s">
-        <v>32</v>
-      </c>
-      <c r="G7" s="96" t="s">
-        <v>33</v>
       </c>
       <c r="H7" s="97">
         <v>3728.0</v>
@@ -44114,19 +44111,19 @@
         <v>45526.0</v>
       </c>
       <c r="B8" s="94" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C8" s="94" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D8" s="96" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" s="96" t="s">
         <v>36</v>
       </c>
-      <c r="E8" s="96" t="s">
-        <v>34</v>
-      </c>
       <c r="G8" s="96" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H8" s="97">
         <v>3728.0</v>
@@ -44137,7 +44134,7 @@
         <v>45526.0</v>
       </c>
       <c r="B9" s="94" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I9" s="97">
         <v>12.0</v>
@@ -44154,22 +44151,22 @@
         <v>45526.0</v>
       </c>
       <c r="B10" s="94" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C10" s="94" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D10" s="96" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E10" s="96" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F10" s="96" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G10" s="96" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H10" s="97">
         <v>3728.0</v>
@@ -44180,22 +44177,22 @@
         <v>45526.0</v>
       </c>
       <c r="B11" s="94" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" s="94" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" s="96" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11" s="96" t="s">
         <v>37</v>
       </c>
-      <c r="C11" s="94" t="s">
-        <v>18</v>
-      </c>
-      <c r="D11" s="96" t="s">
+      <c r="F11" s="96" t="s">
+        <v>33</v>
+      </c>
+      <c r="G11" s="96" t="s">
         <v>34</v>
-      </c>
-      <c r="E11" s="96" t="s">
-        <v>35</v>
-      </c>
-      <c r="F11" s="96" t="s">
-        <v>32</v>
-      </c>
-      <c r="G11" s="96" t="s">
-        <v>33</v>
       </c>
       <c r="H11" s="97">
         <v>3728.0</v>
@@ -44206,19 +44203,19 @@
         <v>45526.0</v>
       </c>
       <c r="B12" s="94" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C12" s="94" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D12" s="96" t="s">
+        <v>38</v>
+      </c>
+      <c r="E12" s="96" t="s">
         <v>36</v>
       </c>
-      <c r="E12" s="96" t="s">
-        <v>34</v>
-      </c>
       <c r="G12" s="96" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H12" s="97">
         <v>3728.0</v>
@@ -44229,7 +44226,7 @@
         <v>45526.0</v>
       </c>
       <c r="B13" s="94" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I13" s="97">
         <v>12.0</v>
@@ -44246,7 +44243,7 @@
         <v>45532.0</v>
       </c>
       <c r="B14" s="94" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15">
@@ -44254,7 +44251,7 @@
         <v>45533.0</v>
       </c>
       <c r="B15" s="94" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16">
@@ -44262,7 +44259,7 @@
         <v>45534.0</v>
       </c>
       <c r="B16" s="94" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17">
@@ -44270,7 +44267,7 @@
         <v>45535.0</v>
       </c>
       <c r="B17" s="94" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -44304,7 +44301,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="98" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -44508,7 +44505,7 @@
       <c r="Y19" s="100"/>
       <c r="Z19" s="100"/>
       <c r="AA19" s="94" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AB19" s="94">
         <v>-11.0</v>
@@ -44833,7 +44830,7 @@
       <c r="Y30" s="100"/>
       <c r="Z30" s="100"/>
       <c r="AA30" s="94" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AB30" s="94">
         <v>-8.0</v>
@@ -44954,7 +44951,7 @@
       <c r="Y34" s="100"/>
       <c r="Z34" s="100"/>
       <c r="AA34" s="94" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="AB34" s="94">
         <v>0.0</v>
@@ -45073,7 +45070,7 @@
       <c r="Y38" s="100"/>
       <c r="Z38" s="100"/>
       <c r="AA38" s="94" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AB38" s="94">
         <v>-12.0</v>
@@ -45107,7 +45104,7 @@
       <c r="Y39" s="100"/>
       <c r="Z39" s="100"/>
       <c r="AA39" s="94" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="AB39" s="94">
         <v>0.0</v>
@@ -45199,7 +45196,7 @@
       <c r="Y42" s="100"/>
       <c r="Z42" s="100"/>
       <c r="AA42" s="94" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AB42" s="94">
         <v>6.0</v>
@@ -45378,7 +45375,7 @@
       <c r="Y48" s="100"/>
       <c r="Z48" s="100"/>
       <c r="AA48" s="94" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="AB48" s="94">
         <v>-13.0</v>
@@ -45499,7 +45496,7 @@
       <c r="Y52" s="100"/>
       <c r="Z52" s="100"/>
       <c r="AA52" s="94" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AB52" s="94">
         <v>5.0</v>
@@ -45707,7 +45704,7 @@
       <c r="Y59" s="100"/>
       <c r="Z59" s="100"/>
       <c r="AA59" s="94" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AB59" s="94">
         <v>-9.0</v>
@@ -45828,7 +45825,7 @@
       <c r="Y63" s="100"/>
       <c r="Z63" s="100"/>
       <c r="AA63" s="94" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="AB63" s="94">
         <v>-19.0</v>
@@ -46036,7 +46033,7 @@
       <c r="Y70" s="100"/>
       <c r="Z70" s="100"/>
       <c r="AA70" s="94" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="AB70" s="94">
         <v>-14.0</v>
@@ -46505,7 +46502,7 @@
       <c r="Y86" s="100"/>
       <c r="Z86" s="100"/>
       <c r="AA86" s="94" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="AB86" s="94">
         <v>-21.0</v>
@@ -46539,7 +46536,7 @@
       <c r="Y87" s="100"/>
       <c r="Z87" s="100"/>
       <c r="AA87" s="94" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="AB87" s="94">
         <v>-7.0</v>
@@ -46573,7 +46570,7 @@
       <c r="Y88" s="100"/>
       <c r="Z88" s="100"/>
       <c r="AA88" s="94" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="AB88" s="94">
         <v>-10.0</v>
@@ -46607,7 +46604,7 @@
       <c r="Y89" s="100"/>
       <c r="Z89" s="100"/>
       <c r="AA89" s="94" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="AB89" s="94">
         <v>-6.0</v>
@@ -46700,7 +46697,7 @@
       <c r="Y92" s="100"/>
       <c r="Z92" s="100"/>
       <c r="AA92" s="94" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="AB92" s="94">
         <v>-17.0</v>
@@ -46966,7 +46963,7 @@
       <c r="Y101" s="100"/>
       <c r="Z101" s="100"/>
       <c r="AA101" s="94" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="AB101" s="94">
         <v>-6.0</v>
@@ -47000,7 +46997,7 @@
       <c r="Y102" s="100"/>
       <c r="Z102" s="100"/>
       <c r="AA102" s="94" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="AB102" s="94">
         <v>1.0</v>
@@ -47092,7 +47089,7 @@
       <c r="Y105" s="100"/>
       <c r="Z105" s="100"/>
       <c r="AA105" s="94" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="AB105" s="94">
         <v>-2.0</v>
@@ -47155,7 +47152,7 @@
       <c r="Y107" s="100"/>
       <c r="Z107" s="100"/>
       <c r="AA107" s="94" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="AB107" s="94">
         <v>-12.0</v>
@@ -47247,7 +47244,7 @@
       <c r="Y110" s="100"/>
       <c r="Z110" s="100"/>
       <c r="AA110" s="94" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="AB110" s="94">
         <v>-14.0</v>
@@ -47281,7 +47278,7 @@
       <c r="Y111" s="100"/>
       <c r="Z111" s="100"/>
       <c r="AA111" s="94" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="AB111" s="94">
         <v>-6.0</v>
@@ -47315,7 +47312,7 @@
       <c r="Y112" s="100"/>
       <c r="Z112" s="100"/>
       <c r="AA112" s="94" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="AB112" s="94">
         <v>-11.0</v>
@@ -47378,7 +47375,7 @@
       <c r="Y114" s="100"/>
       <c r="Z114" s="100"/>
       <c r="AA114" s="94" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="AB114" s="94">
         <v>-1.0</v>
@@ -47470,7 +47467,7 @@
       <c r="Y117" s="100"/>
       <c r="Z117" s="100"/>
       <c r="AA117" s="94" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="AB117" s="94">
         <v>12.0</v>
@@ -47533,7 +47530,7 @@
       <c r="Y119" s="100"/>
       <c r="Z119" s="100"/>
       <c r="AA119" s="94" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="AB119" s="94">
         <v>-17.0</v>
@@ -47654,7 +47651,7 @@
       <c r="Y123" s="100"/>
       <c r="Z123" s="100"/>
       <c r="AA123" s="94" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="AB123" s="94">
         <v>-15.0</v>
@@ -47805,7 +47802,7 @@
       <c r="Y128" s="100"/>
       <c r="Z128" s="100"/>
       <c r="AA128" s="94" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="AB128" s="94">
         <v>-11.0</v>
@@ -48190,7 +48187,7 @@
       <c r="Y141" s="100"/>
       <c r="Z141" s="100"/>
       <c r="AA141" s="94" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AB141" s="94">
         <v>-10.0</v>

--- a/google_data/Pobočky/Výroba/Report Vyroba.xlsx
+++ b/google_data/Pobočky/Výroba/Report Vyroba.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="74">
   <si>
     <t>Výroba</t>
   </si>
@@ -54,7 +54,7 @@
     <t>Benzín / nafta</t>
   </si>
   <si>
-    <t>Koteliuk Maryna</t>
+    <t>Paziak Viktoriia</t>
   </si>
   <si>
     <t>06:00</t>
@@ -72,7 +72,7 @@
     <t>Ostatní</t>
   </si>
   <si>
-    <t>Paziak Viktoriia</t>
+    <t>Koteliuk Maryna</t>
   </si>
   <si>
     <t>Vyber datum    &lt;----------&gt;</t>
@@ -84,7 +84,13 @@
     <t>Počet dní</t>
   </si>
   <si>
+    <t>Ahurieva Viktoriia</t>
+  </si>
+  <si>
     <t>Hřebík Martin</t>
+  </si>
+  <si>
+    <t>Lažek Jaroslav</t>
   </si>
   <si>
     <t>Manažeři</t>
@@ -1396,7 +1402,7 @@
         <v>1</v>
       </c>
       <c r="D1" s="4">
-        <v>46204.0</v>
+        <v>46205.0</v>
       </c>
       <c r="E1" s="5"/>
       <c r="F1" s="6" t="s">
@@ -1425,7 +1431,7 @@
       <c r="A3" s="17"/>
       <c r="B3" s="18" t="str">
         <f>CHOOSE(WEEKDAY(D1), "Neděle", "Pondělí", "Úterý", "Středa", "Čtvrtek", "Pátek", "Sobota")</f>
-        <v>Středa</v>
+        <v>Čtvrtek</v>
       </c>
       <c r="C3" s="10"/>
       <c r="D3" s="10"/>
@@ -1764,7 +1770,7 @@
         <v>Výroba</v>
       </c>
       <c r="C1" s="62">
-        <v>46203.0</v>
+        <v>46174.0</v>
       </c>
       <c r="D1" s="63" t="s">
         <v>19</v>
@@ -1786,7 +1792,7 @@
       <c r="D2" s="12"/>
       <c r="E2" s="13"/>
       <c r="F2" s="65">
-        <v>43210.0</v>
+        <v>1237482.0</v>
       </c>
       <c r="H2" s="16"/>
     </row>
@@ -1794,7 +1800,7 @@
       <c r="A3" s="66"/>
       <c r="B3" s="67" t="str">
         <f>CHOOSE(WEEKDAY(C1), "Neděle", "Pondělí", "Úterý", "Středa", "Čtvrtek", "Pátek", "Sobota")</f>
-        <v>Úterý</v>
+        <v>Pondělí</v>
       </c>
       <c r="C3" s="10"/>
       <c r="D3" s="67" t="str">
@@ -1900,13 +1906,13 @@
     <row r="10" ht="18.75" customHeight="1">
       <c r="A10" s="71"/>
       <c r="B10" s="80" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C10" s="81">
-        <v>1.0</v>
+        <v>22.0</v>
       </c>
       <c r="D10" s="82">
-        <v>8.0</v>
+        <v>181.0</v>
       </c>
     </row>
     <row r="11" ht="18.75" customHeight="1">
@@ -1915,47 +1921,59 @@
         <v>16</v>
       </c>
       <c r="C11" s="81">
-        <v>1.0</v>
+        <v>22.0</v>
       </c>
       <c r="D11" s="82">
-        <v>8.0</v>
+        <v>181.0</v>
       </c>
     </row>
     <row r="12" ht="18.75" customHeight="1">
       <c r="A12" s="71"/>
       <c r="B12" s="80" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="C12" s="81">
-        <v>1.0</v>
+        <v>13.0</v>
       </c>
       <c r="D12" s="82">
-        <v>8.0</v>
+        <v>110.0</v>
       </c>
     </row>
     <row r="13" ht="18.75" customHeight="1">
       <c r="A13" s="71"/>
       <c r="B13" s="80" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C13" s="81">
-        <v>1.0</v>
+        <v>12.0</v>
       </c>
       <c r="D13" s="83">
-        <v>12.0</v>
+        <v>128.0</v>
       </c>
     </row>
     <row r="14" ht="18.75" customHeight="1">
       <c r="A14" s="71"/>
-      <c r="B14" s="80"/>
-      <c r="C14" s="81"/>
-      <c r="D14" s="83"/>
+      <c r="B14" s="80" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="81">
+        <v>2.0</v>
+      </c>
+      <c r="D14" s="83">
+        <v>20.0</v>
+      </c>
     </row>
     <row r="15" ht="18.75" customHeight="1">
       <c r="A15" s="71"/>
-      <c r="B15" s="80"/>
-      <c r="C15" s="81"/>
-      <c r="D15" s="83"/>
+      <c r="B15" s="80" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="81">
+        <v>2.0</v>
+      </c>
+      <c r="D15" s="83">
+        <v>18.0</v>
+      </c>
     </row>
     <row r="16" ht="18.75" customHeight="1">
       <c r="A16" s="71"/>
@@ -2156,10 +2174,10 @@
     </row>
     <row r="4">
       <c r="A4" s="88" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B4" s="88" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C4" s="84" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Manažer")</f>
@@ -43932,7 +43950,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="94" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C1" s="94" t="s">
         <v>4</v>
@@ -43944,16 +43962,16 @@
         <v>8</v>
       </c>
       <c r="F1" s="94" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G1" s="94" t="s">
         <v>10</v>
       </c>
       <c r="H1" s="94" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I1" s="94" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J1" s="94" t="s">
         <v>15</v>
@@ -43967,22 +43985,22 @@
         <v>45528.0</v>
       </c>
       <c r="B2" s="94" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C2" s="94" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D2" s="96" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E2" s="96" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F2" s="96" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G2" s="96" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H2" s="97">
         <v>3728.0</v>
@@ -43993,22 +44011,22 @@
         <v>45528.0</v>
       </c>
       <c r="B3" s="94" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C3" s="94" t="s">
+        <v>37</v>
+      </c>
+      <c r="D3" s="96" t="s">
+        <v>38</v>
+      </c>
+      <c r="E3" s="96" t="s">
+        <v>39</v>
+      </c>
+      <c r="F3" s="96" t="s">
         <v>35</v>
       </c>
-      <c r="D3" s="96" t="s">
+      <c r="G3" s="96" t="s">
         <v>36</v>
-      </c>
-      <c r="E3" s="96" t="s">
-        <v>37</v>
-      </c>
-      <c r="F3" s="96" t="s">
-        <v>33</v>
-      </c>
-      <c r="G3" s="96" t="s">
-        <v>34</v>
       </c>
       <c r="H3" s="97">
         <v>3728.0</v>
@@ -44019,19 +44037,19 @@
         <v>45528.0</v>
       </c>
       <c r="B4" s="94" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C4" s="94" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D4" s="96" t="s">
+        <v>40</v>
+      </c>
+      <c r="E4" s="96" t="s">
         <v>38</v>
       </c>
-      <c r="E4" s="96" t="s">
-        <v>36</v>
-      </c>
       <c r="G4" s="96" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H4" s="97">
         <v>3728.0</v>
@@ -44042,7 +44060,7 @@
         <v>45528.0</v>
       </c>
       <c r="B5" s="94" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I5" s="97">
         <v>12.0</v>
@@ -44059,22 +44077,22 @@
         <v>45526.0</v>
       </c>
       <c r="B6" s="94" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C6" s="94" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D6" s="96" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E6" s="96" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F6" s="96" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G6" s="96" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H6" s="97">
         <v>3728.0</v>
@@ -44085,22 +44103,22 @@
         <v>45526.0</v>
       </c>
       <c r="B7" s="94" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" s="94" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" s="96" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" s="96" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="94" t="s">
+      <c r="F7" s="96" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="96" t="s">
+      <c r="G7" s="96" t="s">
         <v>36</v>
-      </c>
-      <c r="E7" s="96" t="s">
-        <v>37</v>
-      </c>
-      <c r="F7" s="96" t="s">
-        <v>33</v>
-      </c>
-      <c r="G7" s="96" t="s">
-        <v>34</v>
       </c>
       <c r="H7" s="97">
         <v>3728.0</v>
@@ -44111,19 +44129,19 @@
         <v>45526.0</v>
       </c>
       <c r="B8" s="94" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C8" s="94" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D8" s="96" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" s="96" t="s">
         <v>38</v>
       </c>
-      <c r="E8" s="96" t="s">
-        <v>36</v>
-      </c>
       <c r="G8" s="96" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H8" s="97">
         <v>3728.0</v>
@@ -44134,7 +44152,7 @@
         <v>45526.0</v>
       </c>
       <c r="B9" s="94" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I9" s="97">
         <v>12.0</v>
@@ -44151,22 +44169,22 @@
         <v>45526.0</v>
       </c>
       <c r="B10" s="94" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C10" s="94" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D10" s="96" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E10" s="96" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F10" s="96" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G10" s="96" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H10" s="97">
         <v>3728.0</v>
@@ -44177,22 +44195,22 @@
         <v>45526.0</v>
       </c>
       <c r="B11" s="94" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" s="94" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" s="96" t="s">
+        <v>38</v>
+      </c>
+      <c r="E11" s="96" t="s">
         <v>39</v>
       </c>
-      <c r="C11" s="94" t="s">
+      <c r="F11" s="96" t="s">
         <v>35</v>
       </c>
-      <c r="D11" s="96" t="s">
+      <c r="G11" s="96" t="s">
         <v>36</v>
-      </c>
-      <c r="E11" s="96" t="s">
-        <v>37</v>
-      </c>
-      <c r="F11" s="96" t="s">
-        <v>33</v>
-      </c>
-      <c r="G11" s="96" t="s">
-        <v>34</v>
       </c>
       <c r="H11" s="97">
         <v>3728.0</v>
@@ -44203,19 +44221,19 @@
         <v>45526.0</v>
       </c>
       <c r="B12" s="94" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C12" s="94" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D12" s="96" t="s">
+        <v>40</v>
+      </c>
+      <c r="E12" s="96" t="s">
         <v>38</v>
       </c>
-      <c r="E12" s="96" t="s">
-        <v>36</v>
-      </c>
       <c r="G12" s="96" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H12" s="97">
         <v>3728.0</v>
@@ -44226,7 +44244,7 @@
         <v>45526.0</v>
       </c>
       <c r="B13" s="94" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I13" s="97">
         <v>12.0</v>
@@ -44243,7 +44261,7 @@
         <v>45532.0</v>
       </c>
       <c r="B14" s="94" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15">
@@ -44251,7 +44269,7 @@
         <v>45533.0</v>
       </c>
       <c r="B15" s="94" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16">
@@ -44259,7 +44277,7 @@
         <v>45534.0</v>
       </c>
       <c r="B16" s="94" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17">
@@ -44267,7 +44285,7 @@
         <v>45535.0</v>
       </c>
       <c r="B17" s="94" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -44301,7 +44319,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="98" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -44505,7 +44523,7 @@
       <c r="Y19" s="100"/>
       <c r="Z19" s="100"/>
       <c r="AA19" s="94" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="AB19" s="94">
         <v>-11.0</v>
@@ -44830,7 +44848,7 @@
       <c r="Y30" s="100"/>
       <c r="Z30" s="100"/>
       <c r="AA30" s="94" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AB30" s="94">
         <v>-8.0</v>
@@ -44951,7 +44969,7 @@
       <c r="Y34" s="100"/>
       <c r="Z34" s="100"/>
       <c r="AA34" s="94" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="AB34" s="94">
         <v>0.0</v>
@@ -45070,7 +45088,7 @@
       <c r="Y38" s="100"/>
       <c r="Z38" s="100"/>
       <c r="AA38" s="94" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AB38" s="94">
         <v>-12.0</v>
@@ -45104,7 +45122,7 @@
       <c r="Y39" s="100"/>
       <c r="Z39" s="100"/>
       <c r="AA39" s="94" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="AB39" s="94">
         <v>0.0</v>
@@ -45196,7 +45214,7 @@
       <c r="Y42" s="100"/>
       <c r="Z42" s="100"/>
       <c r="AA42" s="94" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AB42" s="94">
         <v>6.0</v>
@@ -45375,7 +45393,7 @@
       <c r="Y48" s="100"/>
       <c r="Z48" s="100"/>
       <c r="AA48" s="94" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AB48" s="94">
         <v>-13.0</v>
@@ -45496,7 +45514,7 @@
       <c r="Y52" s="100"/>
       <c r="Z52" s="100"/>
       <c r="AA52" s="94" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="AB52" s="94">
         <v>5.0</v>
@@ -45704,7 +45722,7 @@
       <c r="Y59" s="100"/>
       <c r="Z59" s="100"/>
       <c r="AA59" s="94" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="AB59" s="94">
         <v>-9.0</v>
@@ -45825,7 +45843,7 @@
       <c r="Y63" s="100"/>
       <c r="Z63" s="100"/>
       <c r="AA63" s="94" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="AB63" s="94">
         <v>-19.0</v>
@@ -46033,7 +46051,7 @@
       <c r="Y70" s="100"/>
       <c r="Z70" s="100"/>
       <c r="AA70" s="94" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="AB70" s="94">
         <v>-14.0</v>
@@ -46502,7 +46520,7 @@
       <c r="Y86" s="100"/>
       <c r="Z86" s="100"/>
       <c r="AA86" s="94" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="AB86" s="94">
         <v>-21.0</v>
@@ -46536,7 +46554,7 @@
       <c r="Y87" s="100"/>
       <c r="Z87" s="100"/>
       <c r="AA87" s="94" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="AB87" s="94">
         <v>-7.0</v>
@@ -46570,7 +46588,7 @@
       <c r="Y88" s="100"/>
       <c r="Z88" s="100"/>
       <c r="AA88" s="94" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="AB88" s="94">
         <v>-10.0</v>
@@ -46604,7 +46622,7 @@
       <c r="Y89" s="100"/>
       <c r="Z89" s="100"/>
       <c r="AA89" s="94" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="AB89" s="94">
         <v>-6.0</v>
@@ -46697,7 +46715,7 @@
       <c r="Y92" s="100"/>
       <c r="Z92" s="100"/>
       <c r="AA92" s="94" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="AB92" s="94">
         <v>-17.0</v>
@@ -46963,7 +46981,7 @@
       <c r="Y101" s="100"/>
       <c r="Z101" s="100"/>
       <c r="AA101" s="94" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="AB101" s="94">
         <v>-6.0</v>
@@ -46997,7 +47015,7 @@
       <c r="Y102" s="100"/>
       <c r="Z102" s="100"/>
       <c r="AA102" s="94" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="AB102" s="94">
         <v>1.0</v>
@@ -47089,7 +47107,7 @@
       <c r="Y105" s="100"/>
       <c r="Z105" s="100"/>
       <c r="AA105" s="94" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="AB105" s="94">
         <v>-2.0</v>
@@ -47152,7 +47170,7 @@
       <c r="Y107" s="100"/>
       <c r="Z107" s="100"/>
       <c r="AA107" s="94" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="AB107" s="94">
         <v>-12.0</v>
@@ -47244,7 +47262,7 @@
       <c r="Y110" s="100"/>
       <c r="Z110" s="100"/>
       <c r="AA110" s="94" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="AB110" s="94">
         <v>-14.0</v>
@@ -47278,7 +47296,7 @@
       <c r="Y111" s="100"/>
       <c r="Z111" s="100"/>
       <c r="AA111" s="94" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="AB111" s="94">
         <v>-6.0</v>
@@ -47312,7 +47330,7 @@
       <c r="Y112" s="100"/>
       <c r="Z112" s="100"/>
       <c r="AA112" s="94" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="AB112" s="94">
         <v>-11.0</v>
@@ -47375,7 +47393,7 @@
       <c r="Y114" s="100"/>
       <c r="Z114" s="100"/>
       <c r="AA114" s="94" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="AB114" s="94">
         <v>-1.0</v>
@@ -47467,7 +47485,7 @@
       <c r="Y117" s="100"/>
       <c r="Z117" s="100"/>
       <c r="AA117" s="94" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="AB117" s="94">
         <v>12.0</v>
@@ -47530,7 +47548,7 @@
       <c r="Y119" s="100"/>
       <c r="Z119" s="100"/>
       <c r="AA119" s="94" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="AB119" s="94">
         <v>-17.0</v>
@@ -47651,7 +47669,7 @@
       <c r="Y123" s="100"/>
       <c r="Z123" s="100"/>
       <c r="AA123" s="94" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AB123" s="94">
         <v>-15.0</v>
@@ -47802,7 +47820,7 @@
       <c r="Y128" s="100"/>
       <c r="Z128" s="100"/>
       <c r="AA128" s="94" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="AB128" s="94">
         <v>-11.0</v>
@@ -48187,7 +48205,7 @@
       <c r="Y141" s="100"/>
       <c r="Z141" s="100"/>
       <c r="AA141" s="94" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="AB141" s="94">
         <v>-10.0</v>

--- a/google_data/Pobočky/Výroba/Report Vyroba.xlsx
+++ b/google_data/Pobočky/Výroba/Report Vyroba.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="72">
   <si>
     <t>Výroba</t>
   </si>
@@ -54,25 +54,10 @@
     <t>Benzín / nafta</t>
   </si>
   <si>
-    <t>Paziak Viktoriia</t>
-  </si>
-  <si>
-    <t>06:00</t>
-  </si>
-  <si>
-    <t>14:00</t>
-  </si>
-  <si>
     <t>Suroviny</t>
   </si>
   <si>
-    <t>Kursheva Diana</t>
-  </si>
-  <si>
     <t>Ostatní</t>
-  </si>
-  <si>
-    <t>Koteliuk Maryna</t>
   </si>
   <si>
     <t>Vyber datum    &lt;----------&gt;</t>
@@ -84,6 +69,12 @@
     <t>Počet dní</t>
   </si>
   <si>
+    <t>Paziak Viktoriia</t>
+  </si>
+  <si>
+    <t>Kursheva Diana</t>
+  </si>
+  <si>
     <t>Ahurieva Viktoriia</t>
   </si>
   <si>
@@ -91,6 +82,9 @@
   </si>
   <si>
     <t>Lažek Jaroslav</t>
+  </si>
+  <si>
+    <t>Koteliuk Maryna</t>
   </si>
   <si>
     <t>Manažeři</t>
@@ -1402,7 +1396,7 @@
         <v>1</v>
       </c>
       <c r="D1" s="4">
-        <v>46205.0</v>
+        <v>46207.0</v>
       </c>
       <c r="E1" s="5"/>
       <c r="F1" s="6" t="s">
@@ -1431,7 +1425,7 @@
       <c r="A3" s="17"/>
       <c r="B3" s="18" t="str">
         <f>CHOOSE(WEEKDAY(D1), "Neděle", "Pondělí", "Úterý", "Středa", "Čtvrtek", "Pátek", "Sobota")</f>
-        <v>Čtvrtek</v>
+        <v>Sobota</v>
       </c>
       <c r="C3" s="10"/>
       <c r="D3" s="10"/>
@@ -1571,23 +1565,17 @@
         <f t="array" ref="A14">IF(ISBLANK(B14), 0, IF(ISNUMBER(MATCH(B14, HR!A:A, 0)), 0, IF(ISNUMBER(MATCH(B14, HR!B:B, 0)), INDEX(HR!V:V, MATCH(B14, HR!B:B, 0)) * (F14 * 24), 0)))</f>
         <v>0</v>
       </c>
-      <c r="B14" s="39" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" s="40" t="s">
-        <v>13</v>
-      </c>
-      <c r="D14" s="40" t="s">
-        <v>14</v>
-      </c>
+      <c r="B14" s="39"/>
+      <c r="C14" s="40"/>
+      <c r="D14" s="40"/>
       <c r="E14" s="41"/>
       <c r="F14" s="42" t="str">
         <f t="shared" ref="F14:F20" si="1">IF(OR(ISBLANK(B14), ISBLANK(D14), D14=0), "0:00", TEXT((IF(AND(TIMEVALUE(IF(ISBLANK(D14), "00:00", D14))&gt;=TIMEVALUE("00:00"), TIMEVALUE(IF(ISBLANK(D14), "00:00", D14))&lt;=TIMEVALUE("06:00")), TIMEVALUE(IF(ISBLANK(D14), "00:00", D14))+1, TIMEVALUE(IF(ISBLANK(D14), "00:00", D14))) - TIMEVALUE(IF(ISBLANK(C14), "00:00", C14)) - TIMEVALUE(IF(ISBLANK(E14), "00:00", E14))), "hh:mm"))
 </f>
-        <v>08:00</v>
+        <v>0:00</v>
       </c>
       <c r="G14" s="43" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H14" s="44"/>
       <c r="I14" s="45"/>
@@ -1599,22 +1587,16 @@
         <f t="array" ref="A15">IF(ISBLANK(B15), 0, IF(ISNUMBER(MATCH(B15, HR!A:A, 0)), 0, IF(ISNUMBER(MATCH(B15, HR!B:B, 0)), INDEX(HR!V:V, MATCH(B15, HR!B:B, 0)) * (F15 * 24), 0)))</f>
         <v>0</v>
       </c>
-      <c r="B15" s="47" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" s="40" t="s">
-        <v>13</v>
-      </c>
-      <c r="D15" s="40" t="s">
-        <v>14</v>
-      </c>
+      <c r="B15" s="47"/>
+      <c r="C15" s="40"/>
+      <c r="D15" s="40"/>
       <c r="E15" s="40"/>
       <c r="F15" s="42" t="str">
         <f t="shared" si="1"/>
-        <v>08:00</v>
+        <v>0:00</v>
       </c>
       <c r="G15" s="48" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H15" s="49"/>
       <c r="I15" s="50"/>
@@ -1626,19 +1608,13 @@
         <f t="array" ref="A16">IF(ISBLANK(B16), 0, IF(ISNUMBER(MATCH(B16, HR!A:A, 0)), 0, IF(ISNUMBER(MATCH(B16, HR!B:B, 0)), INDEX(HR!V:V, MATCH(B16, HR!B:B, 0)) * (F16 * 24), 0)))</f>
         <v>0</v>
       </c>
-      <c r="B16" s="39" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" s="40" t="s">
-        <v>13</v>
-      </c>
-      <c r="D16" s="40" t="s">
-        <v>14</v>
-      </c>
+      <c r="B16" s="39"/>
+      <c r="C16" s="40"/>
+      <c r="D16" s="40"/>
       <c r="E16" s="52"/>
       <c r="F16" s="53" t="str">
         <f t="shared" si="1"/>
-        <v>08:00</v>
+        <v>0:00</v>
       </c>
       <c r="G16" s="54"/>
       <c r="K16" s="16"/>
@@ -1773,7 +1749,7 @@
         <v>46174.0</v>
       </c>
       <c r="D1" s="63" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E1" s="62">
         <v>46203.0</v>
@@ -1823,7 +1799,7 @@
     <row r="5">
       <c r="A5" s="68"/>
       <c r="B5" s="69" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C5" s="10"/>
       <c r="D5" s="10"/>
@@ -1863,7 +1839,7 @@
       <c r="D7" s="19"/>
       <c r="E7" s="14"/>
       <c r="F7" s="74" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G7" s="44"/>
       <c r="H7" s="45"/>
@@ -1881,7 +1857,7 @@
       <c r="D8" s="8"/>
       <c r="E8" s="76"/>
       <c r="F8" s="77" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G8" s="49"/>
       <c r="H8" s="50"/>
@@ -1896,7 +1872,7 @@
         <v>6</v>
       </c>
       <c r="C9" s="79" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D9" s="79" t="s">
         <v>10</v>
@@ -1906,7 +1882,7 @@
     <row r="10" ht="18.75" customHeight="1">
       <c r="A10" s="71"/>
       <c r="B10" s="80" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C10" s="81">
         <v>22.0</v>
@@ -1918,7 +1894,7 @@
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="71"/>
       <c r="B11" s="80" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C11" s="81">
         <v>22.0</v>
@@ -1930,7 +1906,7 @@
     <row r="12" ht="18.75" customHeight="1">
       <c r="A12" s="71"/>
       <c r="B12" s="80" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C12" s="81">
         <v>13.0</v>
@@ -1942,7 +1918,7 @@
     <row r="13" ht="18.75" customHeight="1">
       <c r="A13" s="71"/>
       <c r="B13" s="80" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C13" s="81">
         <v>12.0</v>
@@ -1954,7 +1930,7 @@
     <row r="14" ht="18.75" customHeight="1">
       <c r="A14" s="71"/>
       <c r="B14" s="80" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C14" s="81">
         <v>2.0</v>
@@ -1966,7 +1942,7 @@
     <row r="15" ht="18.75" customHeight="1">
       <c r="A15" s="71"/>
       <c r="B15" s="80" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C15" s="81">
         <v>2.0</v>
@@ -2174,10 +2150,10 @@
     </row>
     <row r="4">
       <c r="A4" s="88" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B4" s="88" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C4" s="84" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Manažer")</f>
@@ -43950,7 +43926,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="94" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C1" s="94" t="s">
         <v>4</v>
@@ -43962,22 +43938,22 @@
         <v>8</v>
       </c>
       <c r="F1" s="94" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G1" s="94" t="s">
         <v>10</v>
       </c>
       <c r="H1" s="94" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I1" s="94" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J1" s="94" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K1" s="94" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2">
@@ -43985,22 +43961,22 @@
         <v>45528.0</v>
       </c>
       <c r="B2" s="94" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="94" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" s="96" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="94" t="s">
+      <c r="E2" s="96" t="s">
         <v>32</v>
       </c>
-      <c r="D2" s="96" t="s">
+      <c r="F2" s="96" t="s">
         <v>33</v>
       </c>
-      <c r="E2" s="96" t="s">
+      <c r="G2" s="96" t="s">
         <v>34</v>
-      </c>
-      <c r="F2" s="96" t="s">
-        <v>35</v>
-      </c>
-      <c r="G2" s="96" t="s">
-        <v>36</v>
       </c>
       <c r="H2" s="97">
         <v>3728.0</v>
@@ -44011,22 +43987,22 @@
         <v>45528.0</v>
       </c>
       <c r="B3" s="94" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C3" s="94" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" s="96" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" s="96" t="s">
         <v>37</v>
       </c>
-      <c r="D3" s="96" t="s">
-        <v>38</v>
-      </c>
-      <c r="E3" s="96" t="s">
-        <v>39</v>
-      </c>
       <c r="F3" s="96" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G3" s="96" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H3" s="97">
         <v>3728.0</v>
@@ -44037,19 +44013,19 @@
         <v>45528.0</v>
       </c>
       <c r="B4" s="94" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C4" s="94" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D4" s="96" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E4" s="96" t="s">
+        <v>36</v>
+      </c>
+      <c r="G4" s="96" t="s">
         <v>38</v>
-      </c>
-      <c r="G4" s="96" t="s">
-        <v>40</v>
       </c>
       <c r="H4" s="97">
         <v>3728.0</v>
@@ -44060,7 +44036,7 @@
         <v>45528.0</v>
       </c>
       <c r="B5" s="94" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I5" s="97">
         <v>12.0</v>
@@ -44077,22 +44053,22 @@
         <v>45526.0</v>
       </c>
       <c r="B6" s="94" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C6" s="94" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="96" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="96" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="96" t="s">
+      <c r="F6" s="96" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="96" t="s">
+      <c r="G6" s="96" t="s">
         <v>34</v>
-      </c>
-      <c r="F6" s="96" t="s">
-        <v>35</v>
-      </c>
-      <c r="G6" s="96" t="s">
-        <v>36</v>
       </c>
       <c r="H6" s="97">
         <v>3728.0</v>
@@ -44103,22 +44079,22 @@
         <v>45526.0</v>
       </c>
       <c r="B7" s="94" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C7" s="94" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" s="96" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" s="96" t="s">
         <v>37</v>
       </c>
-      <c r="D7" s="96" t="s">
-        <v>38</v>
-      </c>
-      <c r="E7" s="96" t="s">
-        <v>39</v>
-      </c>
       <c r="F7" s="96" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G7" s="96" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H7" s="97">
         <v>3728.0</v>
@@ -44129,19 +44105,19 @@
         <v>45526.0</v>
       </c>
       <c r="B8" s="94" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C8" s="94" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D8" s="96" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E8" s="96" t="s">
+        <v>36</v>
+      </c>
+      <c r="G8" s="96" t="s">
         <v>38</v>
-      </c>
-      <c r="G8" s="96" t="s">
-        <v>40</v>
       </c>
       <c r="H8" s="97">
         <v>3728.0</v>
@@ -44152,7 +44128,7 @@
         <v>45526.0</v>
       </c>
       <c r="B9" s="94" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I9" s="97">
         <v>12.0</v>
@@ -44169,22 +44145,22 @@
         <v>45526.0</v>
       </c>
       <c r="B10" s="94" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C10" s="94" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" s="96" t="s">
+        <v>31</v>
+      </c>
+      <c r="E10" s="96" t="s">
         <v>32</v>
       </c>
-      <c r="D10" s="96" t="s">
+      <c r="F10" s="96" t="s">
         <v>33</v>
       </c>
-      <c r="E10" s="96" t="s">
+      <c r="G10" s="96" t="s">
         <v>34</v>
-      </c>
-      <c r="F10" s="96" t="s">
-        <v>35</v>
-      </c>
-      <c r="G10" s="96" t="s">
-        <v>36</v>
       </c>
       <c r="H10" s="97">
         <v>3728.0</v>
@@ -44195,22 +44171,22 @@
         <v>45526.0</v>
       </c>
       <c r="B11" s="94" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C11" s="94" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" s="96" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11" s="96" t="s">
         <v>37</v>
       </c>
-      <c r="D11" s="96" t="s">
-        <v>38</v>
-      </c>
-      <c r="E11" s="96" t="s">
-        <v>39</v>
-      </c>
       <c r="F11" s="96" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G11" s="96" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H11" s="97">
         <v>3728.0</v>
@@ -44221,19 +44197,19 @@
         <v>45526.0</v>
       </c>
       <c r="B12" s="94" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C12" s="94" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D12" s="96" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E12" s="96" t="s">
+        <v>36</v>
+      </c>
+      <c r="G12" s="96" t="s">
         <v>38</v>
-      </c>
-      <c r="G12" s="96" t="s">
-        <v>40</v>
       </c>
       <c r="H12" s="97">
         <v>3728.0</v>
@@ -44244,7 +44220,7 @@
         <v>45526.0</v>
       </c>
       <c r="B13" s="94" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I13" s="97">
         <v>12.0</v>
@@ -44261,7 +44237,7 @@
         <v>45532.0</v>
       </c>
       <c r="B14" s="94" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15">
@@ -44269,7 +44245,7 @@
         <v>45533.0</v>
       </c>
       <c r="B15" s="94" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16">
@@ -44277,7 +44253,7 @@
         <v>45534.0</v>
       </c>
       <c r="B16" s="94" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17">
@@ -44285,7 +44261,7 @@
         <v>45535.0</v>
       </c>
       <c r="B17" s="94" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -44319,7 +44295,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="98" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -44523,7 +44499,7 @@
       <c r="Y19" s="100"/>
       <c r="Z19" s="100"/>
       <c r="AA19" s="94" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="AB19" s="94">
         <v>-11.0</v>
@@ -44848,7 +44824,7 @@
       <c r="Y30" s="100"/>
       <c r="Z30" s="100"/>
       <c r="AA30" s="94" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AB30" s="94">
         <v>-8.0</v>
@@ -44969,7 +44945,7 @@
       <c r="Y34" s="100"/>
       <c r="Z34" s="100"/>
       <c r="AA34" s="94" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AB34" s="94">
         <v>0.0</v>
@@ -45088,7 +45064,7 @@
       <c r="Y38" s="100"/>
       <c r="Z38" s="100"/>
       <c r="AA38" s="94" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AB38" s="94">
         <v>-12.0</v>
@@ -45122,7 +45098,7 @@
       <c r="Y39" s="100"/>
       <c r="Z39" s="100"/>
       <c r="AA39" s="94" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="AB39" s="94">
         <v>0.0</v>
@@ -45214,7 +45190,7 @@
       <c r="Y42" s="100"/>
       <c r="Z42" s="100"/>
       <c r="AA42" s="94" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AB42" s="94">
         <v>6.0</v>
@@ -45393,7 +45369,7 @@
       <c r="Y48" s="100"/>
       <c r="Z48" s="100"/>
       <c r="AA48" s="94" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="AB48" s="94">
         <v>-13.0</v>
@@ -45514,7 +45490,7 @@
       <c r="Y52" s="100"/>
       <c r="Z52" s="100"/>
       <c r="AA52" s="94" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="AB52" s="94">
         <v>5.0</v>
@@ -45722,7 +45698,7 @@
       <c r="Y59" s="100"/>
       <c r="Z59" s="100"/>
       <c r="AA59" s="94" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="AB59" s="94">
         <v>-9.0</v>
@@ -45843,7 +45819,7 @@
       <c r="Y63" s="100"/>
       <c r="Z63" s="100"/>
       <c r="AA63" s="94" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="AB63" s="94">
         <v>-19.0</v>
@@ -46051,7 +46027,7 @@
       <c r="Y70" s="100"/>
       <c r="Z70" s="100"/>
       <c r="AA70" s="94" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="AB70" s="94">
         <v>-14.0</v>
@@ -46520,7 +46496,7 @@
       <c r="Y86" s="100"/>
       <c r="Z86" s="100"/>
       <c r="AA86" s="94" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="AB86" s="94">
         <v>-21.0</v>
@@ -46554,7 +46530,7 @@
       <c r="Y87" s="100"/>
       <c r="Z87" s="100"/>
       <c r="AA87" s="94" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="AB87" s="94">
         <v>-7.0</v>
@@ -46588,7 +46564,7 @@
       <c r="Y88" s="100"/>
       <c r="Z88" s="100"/>
       <c r="AA88" s="94" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="AB88" s="94">
         <v>-10.0</v>
@@ -46622,7 +46598,7 @@
       <c r="Y89" s="100"/>
       <c r="Z89" s="100"/>
       <c r="AA89" s="94" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="AB89" s="94">
         <v>-6.0</v>
@@ -46715,7 +46691,7 @@
       <c r="Y92" s="100"/>
       <c r="Z92" s="100"/>
       <c r="AA92" s="94" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="AB92" s="94">
         <v>-17.0</v>
@@ -46981,7 +46957,7 @@
       <c r="Y101" s="100"/>
       <c r="Z101" s="100"/>
       <c r="AA101" s="94" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="AB101" s="94">
         <v>-6.0</v>
@@ -47015,7 +46991,7 @@
       <c r="Y102" s="100"/>
       <c r="Z102" s="100"/>
       <c r="AA102" s="94" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="AB102" s="94">
         <v>1.0</v>
@@ -47107,7 +47083,7 @@
       <c r="Y105" s="100"/>
       <c r="Z105" s="100"/>
       <c r="AA105" s="94" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="AB105" s="94">
         <v>-2.0</v>
@@ -47170,7 +47146,7 @@
       <c r="Y107" s="100"/>
       <c r="Z107" s="100"/>
       <c r="AA107" s="94" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="AB107" s="94">
         <v>-12.0</v>
@@ -47262,7 +47238,7 @@
       <c r="Y110" s="100"/>
       <c r="Z110" s="100"/>
       <c r="AA110" s="94" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="AB110" s="94">
         <v>-14.0</v>
@@ -47296,7 +47272,7 @@
       <c r="Y111" s="100"/>
       <c r="Z111" s="100"/>
       <c r="AA111" s="94" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="AB111" s="94">
         <v>-6.0</v>
@@ -47330,7 +47306,7 @@
       <c r="Y112" s="100"/>
       <c r="Z112" s="100"/>
       <c r="AA112" s="94" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="AB112" s="94">
         <v>-11.0</v>
@@ -47393,7 +47369,7 @@
       <c r="Y114" s="100"/>
       <c r="Z114" s="100"/>
       <c r="AA114" s="94" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="AB114" s="94">
         <v>-1.0</v>
@@ -47485,7 +47461,7 @@
       <c r="Y117" s="100"/>
       <c r="Z117" s="100"/>
       <c r="AA117" s="94" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="AB117" s="94">
         <v>12.0</v>
@@ -47548,7 +47524,7 @@
       <c r="Y119" s="100"/>
       <c r="Z119" s="100"/>
       <c r="AA119" s="94" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AB119" s="94">
         <v>-17.0</v>
@@ -47669,7 +47645,7 @@
       <c r="Y123" s="100"/>
       <c r="Z123" s="100"/>
       <c r="AA123" s="94" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="AB123" s="94">
         <v>-15.0</v>
@@ -47820,7 +47796,7 @@
       <c r="Y128" s="100"/>
       <c r="Z128" s="100"/>
       <c r="AA128" s="94" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="AB128" s="94">
         <v>-11.0</v>
@@ -48205,7 +48181,7 @@
       <c r="Y141" s="100"/>
       <c r="Z141" s="100"/>
       <c r="AA141" s="94" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="AB141" s="94">
         <v>-10.0</v>
